--- a/Results/Ammonia/ammonia photochemical ozone formation results.xlsx
+++ b/Results/Ammonia/ammonia photochemical ozone formation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005609532056932998</v>
+        <v>0.00560953205693296</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006266573222879762</v>
+        <v>0.006266573222879763</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00694096160643123</v>
+        <v>0.00694096160643122</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006725010928522116</v>
+        <v>0.006725010928522105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004790150964442051</v>
+        <v>0.004790150964442045</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006113950596601556</v>
+        <v>0.006113950596601546</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007631753488872705</v>
+        <v>0.007631753488872709</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005040611844953894</v>
+        <v>0.005040611844953886</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0104135640532007</v>
+        <v>0.01041356405320071</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007479548318020999</v>
+        <v>0.007479548318021005</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009322394818389751</v>
+        <v>0.009322394818389755</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006198326511753513</v>
+        <v>0.006198326511753546</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006769575827680849</v>
+        <v>0.006769575827680847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007729746298476829</v>
+        <v>0.00772974629847683</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007228393839891081</v>
+        <v>0.007228393839891076</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005293533875811012</v>
+        <v>0.005293533875811015</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006778512322358129</v>
+        <v>0.006778512322358119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008524789433497057</v>
+        <v>0.008524789433497061</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005543546524506824</v>
+        <v>0.005543546524506823</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01114026086010193</v>
+        <v>0.01114026086010191</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007999767626179941</v>
+        <v>0.007999767626179917</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01046872879280508</v>
+        <v>0.01046872879280509</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004487082037545115</v>
+        <v>0.002470364561882935</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00399688068215591</v>
+        <v>0.002105557357597575</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005278560487266059</v>
+        <v>0.003261843011603901</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004058034858597389</v>
+        <v>0.002116320910763257</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004058034858597391</v>
+        <v>0.002116320910763257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004783534361578798</v>
+        <v>0.00276962105990855</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005688900139591163</v>
+        <v>0.003672182663929002</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004127667591461158</v>
+        <v>0.002128437326728273</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005032842377410381</v>
+        <v>0.003016124901748216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004215690036004099</v>
+        <v>0.002198972560341932</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006693596941576848</v>
+        <v>0.004676879465914687</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08729084693089119</v>
+        <v>0.01704382710414363</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05361788743366224</v>
+        <v>0.01083885449854037</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1723066281508197</v>
+        <v>0.0326587827610989</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05361788794115045</v>
+        <v>0.01083885500602862</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05361788794115045</v>
+        <v>0.01083885500602862</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1237858373822451</v>
+        <v>0.02371402627805633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.242145109279447</v>
+        <v>0.04528847524704149</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05361771931863545</v>
+        <v>0.01083868638351353</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1546685540830351</v>
+        <v>0.02935201001923442</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06135038320436794</v>
+        <v>0.01225467850348598</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3723775316582928</v>
+        <v>0.02150161160014404</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00846894611175009</v>
+        <v>0.002709086076057352</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005369982760613814</v>
+        <v>0.002347223322096679</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006790606102840388</v>
+        <v>0.003527960132170457</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005215584913727657</v>
+        <v>0.002320049719362261</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005481169728870257</v>
+        <v>0.002366792646574073</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008765398435783773</v>
+        <v>0.003470429133171225</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009850118204855061</v>
+        <v>0.004404557039447007</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008109531665666124</v>
+        <v>0.002367158840902682</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006554049471045023</v>
+        <v>0.003283857348777193</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005507204570848245</v>
+        <v>0.002426279117242817</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008149547675618053</v>
+        <v>0.004933126793717436</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006864847094422958</v>
+        <v>0.002888851209625838</v>
       </c>
       <c r="C7" t="n">
-        <v>0.006505600763365872</v>
+        <v>0.002547092089498025</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007656163834710863</v>
+        <v>0.003680301198486727</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006503090651964838</v>
+        <v>0.00254665072806414</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006503090651964838</v>
+        <v>0.00254665072806414</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007161299418456653</v>
+        <v>0.00318810770765144</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008066665196469024</v>
+        <v>0.004090669311671897</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00650543264833901</v>
+        <v>0.002546923974471162</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007410607434288234</v>
+        <v>0.003434611549491109</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006593455092881943</v>
+        <v>0.002617459208084819</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009071361998454703</v>
+        <v>0.005095366113657579</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009472916096184066</v>
+        <v>0.003347871351448536</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01300391450256264</v>
+        <v>0.003690795301399383</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01496304441641308</v>
+        <v>0.004966312173897927</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01193969046766683</v>
+        <v>0.003503492290442938</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009235629406928616</v>
+        <v>0.003027577546331813</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01366105228898856</v>
+        <v>0.004332064206666418</v>
       </c>
       <c r="H8" t="n">
-        <v>0.014566418067001</v>
+        <v>0.005234625810686869</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01300518551887092</v>
+        <v>0.003690880473486125</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0139111251267065</v>
+        <v>0.004578702657157345</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009129234069332451</v>
+        <v>0.003063756305521807</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01963630408197365</v>
+        <v>0.006954795910281419</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01503872275887583</v>
+        <v>0.004327453318774339</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01791259663800703</v>
+        <v>0.004554723352556312</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01906332254430081</v>
+        <v>0.005687961120495843</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02164354611564701</v>
+        <v>0.005211370875233136</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01791259377219451</v>
+        <v>0.004554723266343613</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01856829529309781</v>
+        <v>0.005195738970709725</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01947366107111019</v>
+        <v>0.006098300574730179</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01791242852298018</v>
+        <v>0.004554555237529448</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01881760330892939</v>
+        <v>0.005442242812549394</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01392937522127035</v>
+        <v>0.00429539282793405</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02047835787309587</v>
+        <v>0.007102997376715864</v>
       </c>
     </row>
   </sheetData>
@@ -914,34 +914,34 @@
         <v>0.004214070108580392</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005608942464180849</v>
+        <v>0.005608942464180847</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004381725966520352</v>
+        <v>0.004381725966520351</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006024757395119091</v>
+        <v>0.006024757395119089</v>
       </c>
       <c r="F2" t="n">
         <v>0.004225983470465614</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004534042279068773</v>
+        <v>0.004534042279068774</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004345101583019135</v>
+        <v>0.004345101583019134</v>
       </c>
       <c r="I2" t="n">
         <v>0.004490917126256501</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008855723879750362</v>
+        <v>0.008855723879750359</v>
       </c>
       <c r="K2" t="n">
         <v>0.006751568012499925</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004288880882199177</v>
+        <v>0.004288880882199176</v>
       </c>
     </row>
     <row r="3">
@@ -954,28 +954,28 @@
         <v>0.004602501940363396</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006038724672096344</v>
+        <v>0.006038724672096339</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004795340906800697</v>
+        <v>0.004795340906800696</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006454840393410675</v>
+        <v>0.006454840393410673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004656066468757197</v>
+        <v>0.004656066468757195</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004970536218460473</v>
+        <v>0.004970536218460468</v>
       </c>
       <c r="H3" t="n">
         <v>0.004753516958551311</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004921177375315579</v>
+        <v>0.004921177375315574</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009392872867510794</v>
+        <v>0.009392872867510785</v>
       </c>
       <c r="K3" t="n">
         <v>0.007176203461396228</v>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003120458996146079</v>
+        <v>0.001553806010804656</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003169376444048036</v>
+        <v>0.001698241546236003</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003220123299510053</v>
+        <v>0.001653470314168631</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00321404347164674</v>
+        <v>0.001706103431653886</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003214043471646741</v>
+        <v>0.001706103431653886</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00330870465770181</v>
+        <v>0.001743670202355447</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003198431042950583</v>
+        <v>0.001631778057609159</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003272887301729395</v>
+        <v>0.001716436777974343</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003709019846381376</v>
+        <v>0.002142366861039952</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003263737903880396</v>
+        <v>0.001697084918538974</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003165033966172938</v>
+        <v>0.001598380980831515</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009127251040729381</v>
+        <v>0.002611001404922794</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02321414146648777</v>
+        <v>0.005226120171069215</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01757325421719352</v>
+        <v>0.004179621341992712</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02321414205945271</v>
+        <v>0.005226120764034163</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02321414205945271</v>
+        <v>0.005226120764034163</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02602762226842964</v>
+        <v>0.005742199680177147</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01755091677492428</v>
+        <v>0.004157815532748929</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02321411394329014</v>
+        <v>0.005226092647871595</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06575004027306389</v>
+        <v>0.01306158639696913</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02066370219006691</v>
+        <v>0.004759478616313905</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01658287708214818</v>
+        <v>0.003651732556633109</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005823218545698111</v>
+        <v>0.002029491688948261</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004270080145577412</v>
+        <v>0.001891965396655458</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004224983242329127</v>
+        <v>0.00213592244493487</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00414354875523886</v>
+        <v>0.001869696360679653</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004295479424825359</v>
+        <v>0.001896436158381986</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006011464207253842</v>
+        <v>0.001923485091895464</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006011711035708864</v>
+        <v>0.002126915333651664</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004294562816015536</v>
+        <v>0.001896251667514359</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00645508026512042</v>
+        <v>0.002625673492119176</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004291086427261635</v>
+        <v>0.00187789825767429</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004187808206053308</v>
+        <v>0.001778389246075067</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004667443461124824</v>
+        <v>0.001826075275165594</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00481989928990575</v>
+        <v>0.001988733565532899</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004766973783002349</v>
+        <v>0.001925715997788081</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004817640324469206</v>
+        <v>0.00198833647622133</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004817640324469207</v>
+        <v>0.00198833647622133</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00485568912268055</v>
+        <v>0.002015939466716384</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004745415507929326</v>
+        <v>0.001904047321970098</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00481987176670814</v>
+        <v>0.00198870604233528</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005256004311360117</v>
+        <v>0.002414636125400891</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004810722368859142</v>
+        <v>0.001969354182899912</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004712018431151682</v>
+        <v>0.001870650245192454</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006469182161585828</v>
+        <v>0.002143181284728459</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009266091405556957</v>
+        <v>0.002771263373647289</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009763429739784786</v>
+        <v>0.002805092241416797</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008542580601739413</v>
+        <v>0.002643925961468506</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006704242536146148</v>
+        <v>0.002320378463677268</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009303359854897409</v>
+        <v>0.002798729511344918</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009193086240146236</v>
+        <v>0.002686837366598641</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009267542498924988</v>
+        <v>0.002771496086963816</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009704195040422758</v>
+        <v>0.003197517689473789</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006563311523866899</v>
+        <v>0.002277809872509879</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01192358641536462</v>
+        <v>0.00313988620353644</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008007773995096085</v>
+        <v>0.002413973445958948</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009737385383752751</v>
+        <v>0.002854211113360289</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00968459500965696</v>
+        <v>0.002791217328989484</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01155739072145058</v>
+        <v>0.003174532539662521</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009737385679890539</v>
+        <v>0.002854211654083649</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009773175216527557</v>
+        <v>0.002881417014543774</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009662901601776326</v>
+        <v>0.002769524869797487</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009737357860555143</v>
+        <v>0.002854183590162672</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01017349040520712</v>
+        <v>0.003280113673228282</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008814398821587473</v>
+        <v>0.002674001234761892</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009629504524998682</v>
+        <v>0.002736127793019843</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00533958539417173</v>
+        <v>0.005339585394171729</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004044384436271782</v>
+        <v>0.004044384436271783</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005965775985002121</v>
+        <v>0.005965775985002122</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004674161521944107</v>
+        <v>0.004674161521944106</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004674161521944107</v>
+        <v>0.004674161521944106</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005858899410801701</v>
+        <v>0.005858899410801698</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006563285437131881</v>
+        <v>0.00656328543713188</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005494082305449504</v>
+        <v>0.005494082305449503</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007788447324991216</v>
+        <v>0.00778844732499122</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006356189131810766</v>
+        <v>0.006356189131810767</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006254252811520095</v>
+        <v>0.006254252811520096</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005741496396397642</v>
+        <v>0.005741496396397641</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00448837745813874</v>
+        <v>0.004488377458138744</v>
       </c>
       <c r="D3" t="n">
         <v>0.006461745290842705</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005099339648110969</v>
+        <v>0.005099339648110968</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005099339648110969</v>
+        <v>0.005099339648110968</v>
       </c>
       <c r="G3" t="n">
         <v>0.006338815091096573</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007149475405595198</v>
+        <v>0.007149475405595196</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005919186023346131</v>
+        <v>0.005919186023346132</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008381495485484201</v>
+        <v>0.008381495485484197</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006786629334205829</v>
+        <v>0.006786629334205828</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006793526424050794</v>
+        <v>0.006793526424050793</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003367706668163734</v>
+        <v>0.001709287210665048</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003308524512028438</v>
+        <v>0.001837209279773378</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003739950440466262</v>
+        <v>0.002081530982967574</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003356182587737105</v>
+        <v>0.001783134236381737</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003356182587737105</v>
+        <v>0.001783134236381737</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003672173682990183</v>
+        <v>0.002017250591690977</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004095020695926209</v>
+        <v>0.002436601238427528</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003432422704886146</v>
+        <v>0.001796492671857877</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004124148301557427</v>
+        <v>0.002465728844058743</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003480613415187839</v>
+        <v>0.001822193957689156</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003911413688654221</v>
+        <v>0.002252994231155524</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02153444015255335</v>
+        <v>0.00490663228659247</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03819689771490854</v>
+        <v>0.007977562930208109</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05705934668904945</v>
+        <v>0.01146574467186888</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03014239370480305</v>
+        <v>0.006497507367440047</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03014239370480305</v>
+        <v>0.006497507367440047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05234065423769168</v>
+        <v>0.01058290312290457</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1032479471895325</v>
+        <v>0.01988751620674264</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03014232110156359</v>
+        <v>0.00649743476420058</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09914573090658189</v>
+        <v>0.01918952729192343</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03203451527316252</v>
+        <v>0.006847680657461592</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08469636037439701</v>
+        <v>0.01647114477080376</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006365101116914616</v>
+        <v>0.001889842674124523</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004502653924300087</v>
+        <v>0.002047376055194376</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004796675615755258</v>
+        <v>0.002267512171103376</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004273499478117504</v>
+        <v>0.001944582008213866</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00445521363479617</v>
+        <v>0.001976563699616016</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006669568131741063</v>
+        <v>0.002544792011812594</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007282130592640186</v>
+        <v>0.00299753257720972</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006429817153637011</v>
+        <v>0.002324034091979493</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007164947922813266</v>
+        <v>0.003000909574499834</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004467941187016573</v>
+        <v>0.001995963644589413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004950289260115143</v>
+        <v>0.0024358363307419</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005273628213589409</v>
+        <v>0.002044729400842339</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005438704933819083</v>
+        <v>0.002212121031977033</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005645737674597856</v>
+        <v>0.002416949534357235</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005334801455112099</v>
+        <v>0.002131371155152779</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005334801455112099</v>
+        <v>0.002131371155152779</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005578095228415862</v>
+        <v>0.002352692781868268</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00600094224135189</v>
+        <v>0.002772043428604818</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005338344250311806</v>
+        <v>0.002131934862035168</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006030069846983101</v>
+        <v>0.002801171034236034</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005386534960613516</v>
+        <v>0.002157636147866446</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005817335234079889</v>
+        <v>0.002588436421332813</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007433602048446526</v>
+        <v>0.002424884793717278</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0107915030060015</v>
+        <v>0.003154213487580691</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01166394002578258</v>
+        <v>0.003476153142426342</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009817528658800544</v>
+        <v>0.002920331138726881</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007597606114383648</v>
+        <v>0.002529624773026589</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01093355785171115</v>
+        <v>0.003295254198460866</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01135640486465154</v>
+        <v>0.003714604845198189</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01069380687360707</v>
+        <v>0.003074496278627765</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01138616047043345</v>
+        <v>0.003743842978855327</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007487150951147186</v>
+        <v>0.002527344560197066</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0145107530946149</v>
+        <v>0.004118477956496288</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009940427954844263</v>
+        <v>0.002866086150852587</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01218962701089457</v>
+        <v>0.003400283311104139</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01239679501989285</v>
+        <v>0.00360513562069084</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01449437102372067</v>
+        <v>0.003743455390492643</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01208933752506542</v>
+        <v>0.003320169497022937</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01232901730549134</v>
+        <v>0.003540855060995373</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01275186431842737</v>
+        <v>0.00396020570773192</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01208926632738728</v>
+        <v>0.003320097141162271</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01278099192405858</v>
+        <v>0.003989333313363133</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00951317475435527</v>
+        <v>0.003133269933703095</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01256825731115538</v>
+        <v>0.003776598700459917</v>
       </c>
     </row>
   </sheetData>
@@ -1706,10 +1706,10 @@
         <v>0.00517851526772536</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003842016476047976</v>
+        <v>0.003842016476047975</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005675296797283016</v>
+        <v>0.005675296797283015</v>
       </c>
       <c r="E2" t="n">
         <v>0.00447720097754379</v>
@@ -1718,19 +1718,19 @@
         <v>0.00447720097754379</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005549003184058154</v>
+        <v>0.005549003184058151</v>
       </c>
       <c r="H2" t="n">
         <v>0.005830698701002409</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005298735605459842</v>
+        <v>0.005298735605459843</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007301463488907247</v>
+        <v>0.007301463488907245</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006100925016083928</v>
+        <v>0.006100925016083929</v>
       </c>
       <c r="L2" t="n">
         <v>0.005507829469702769</v>
@@ -1746,10 +1746,10 @@
         <v>0.005559221470303776</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004259072304539454</v>
+        <v>0.004259072304539449</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006130623137278909</v>
+        <v>0.006130623137278908</v>
       </c>
       <c r="E3" t="n">
         <v>0.004876027958809208</v>
@@ -1761,19 +1761,19 @@
         <v>0.005985359320427152</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006309807233416044</v>
+        <v>0.006309807233416045</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005697549429141992</v>
+        <v>0.00569754942914199</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007823694037675848</v>
+        <v>0.007823694037675842</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006496610514382985</v>
+        <v>0.006496610514382986</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005937993536960631</v>
+        <v>0.00593799353696063</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003141817705038699</v>
+        <v>0.001592634405304134</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003116767857226086</v>
+        <v>0.00170777711975056</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003437133273941658</v>
+        <v>0.001887949974207099</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00324043873613235</v>
+        <v>0.001669084479288609</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00324043873613235</v>
+        <v>0.001669084479288609</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003358386583045146</v>
+        <v>0.001812227766537396</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00352948567222171</v>
+        <v>0.001980302372487147</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003189891678823877</v>
+        <v>0.001660141687892772</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003701912396032746</v>
+        <v>0.002152729096298184</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003201099547589569</v>
+        <v>0.001651916247854998</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003337645114300172</v>
+        <v>0.001788461814565618</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01276280446234893</v>
+        <v>0.003285928065415447</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02642061540771544</v>
+        <v>0.0058092542664124</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03958815015776368</v>
+        <v>0.008250528911283467</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01918316885775339</v>
+        <v>0.004475004965489735</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01918316885775339</v>
+        <v>0.004475004965489735</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03358793457148204</v>
+        <v>0.007132628183673125</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0540894184730441</v>
+        <v>0.01087885049721421</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01918311241435815</v>
+        <v>0.004474948522094469</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06715163446598194</v>
+        <v>0.01331988012009884</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0179612300407521</v>
+        <v>0.004249699200575247</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03475809719190227</v>
+        <v>0.007318461350258701</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005904906457047467</v>
+        <v>0.002078938023022593</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004226475776223607</v>
+        <v>0.001903085712435824</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004445537665908077</v>
+        <v>0.00237901257699529</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00402363916406474</v>
+        <v>0.001806927753857792</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004179697658761499</v>
+        <v>0.001834394048775593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004341108455551739</v>
+        <v>0.001985186815161366</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006450826892744602</v>
+        <v>0.002494458424513167</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004172613551330492</v>
+        <v>0.00183310073651674</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004805277807886116</v>
+        <v>0.002346921407732128</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004163178198864083</v>
+        <v>0.001821242089561807</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004317122155137921</v>
+        <v>0.001960849772818956</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004840990760877887</v>
+        <v>0.001891688861511376</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004983679062666261</v>
+        <v>0.002036353490127606</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005136178692244253</v>
+        <v>0.00218698196620802</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004886604784609151</v>
+        <v>0.001958809702250621</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004886604784609151</v>
+        <v>0.001958809702250621</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005057559638884337</v>
+        <v>0.002111282222744637</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005228658728060902</v>
+        <v>0.002279356828694388</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004889064734663073</v>
+        <v>0.001959196144100013</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005401085451871937</v>
+        <v>0.002451783552505425</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004900272603428764</v>
+        <v>0.001950970704062238</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005036818170139367</v>
+        <v>0.00208751627077286</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006821853487741823</v>
+        <v>0.00224032069955033</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009856738739005966</v>
+        <v>0.002894011988520268</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01061111292223496</v>
+        <v>0.003150570385465075</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008970880410080033</v>
+        <v>0.002677642208438427</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006960290400084225</v>
+        <v>0.002323778368596612</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009932301534227968</v>
+        <v>0.002969236791676201</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01010340062341205</v>
+        <v>0.003137311397627264</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009763806630006717</v>
+        <v>0.002817150713031578</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01027639607273044</v>
+        <v>0.003309838217127063</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006827380039477276</v>
+        <v>0.002290141610968942</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01293445883477776</v>
+        <v>0.003477501020217435</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008487577924885697</v>
+        <v>0.00253348819889909</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01035050094688709</v>
+        <v>0.002980914136632269</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01050312924521048</v>
+        <v>0.003131565258411745</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01224105740295678</v>
+        <v>0.003253193356066052</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01025594227526224</v>
+        <v>0.002903813095484965</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01042438152310516</v>
+        <v>0.003055842869249301</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01059548061228173</v>
+        <v>0.003223917475199051</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0102558866188839</v>
+        <v>0.002903756790604677</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01076790733609276</v>
+        <v>0.003396344199010088</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009270384168597486</v>
+        <v>0.002720110335364269</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01040364005436021</v>
+        <v>0.003032076917277521</v>
       </c>
     </row>
   </sheetData>
@@ -2099,34 +2099,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00505164225204665</v>
+        <v>0.005051642252046649</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003705169264145185</v>
+        <v>0.003705169264145184</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005400572252123096</v>
+        <v>0.005400572252123092</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004277660685849307</v>
+        <v>0.004277660685849304</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004277660685849307</v>
+        <v>0.004277660685849304</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005302759357478926</v>
+        <v>0.005302759357478924</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00540008658642863</v>
+        <v>0.005400086586428629</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005089064617486832</v>
+        <v>0.005089064617486829</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006662766548165424</v>
+        <v>0.006662766548165421</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005947319268945908</v>
+        <v>0.005947319268945903</v>
       </c>
       <c r="L2" t="n">
         <v>0.005182718070867678</v>
@@ -2139,34 +2139,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005441203339445538</v>
+        <v>0.005441203339445535</v>
       </c>
       <c r="C3" t="n">
         <v>0.004127479665823787</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005842545120165212</v>
+        <v>0.005842545120165205</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004672906292899277</v>
+        <v>0.004672906292899274</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004672906292899277</v>
+        <v>0.004672906292899274</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005730040029444337</v>
+        <v>0.005730040029444331</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005842402637516462</v>
+        <v>0.00584240263751646</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005484306418843501</v>
+        <v>0.005484306418843492</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00713455741932672</v>
+        <v>0.007134557419326718</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006345711533225959</v>
+        <v>0.006345711533225962</v>
       </c>
       <c r="L3" t="n">
         <v>0.005591961139221301</v>
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003000803991672806</v>
+        <v>0.001513835104872388</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002987240694956609</v>
+        <v>0.001619188237468775</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003208228091299933</v>
+        <v>0.001721259204499518</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003028073765668339</v>
+        <v>0.001537172090157985</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003028073765668339</v>
+        <v>0.001537172090157985</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003147036926008609</v>
+        <v>0.001662577567557157</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003207953258453648</v>
+        <v>0.001720984371653227</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003003796944729062</v>
+        <v>0.001532857816037389</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003326235386105967</v>
+        <v>0.00183926649930555</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003035754128660001</v>
+        <v>0.001548785241859587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003078795834176244</v>
+        <v>0.001591826947375824</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007513512720938299</v>
+        <v>0.002308071836919458</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01983548105433612</v>
+        <v>0.004584478524651835</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02641858562051299</v>
+        <v>0.005806282107505876</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009474496185188358</v>
+        <v>0.002671742429845711</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009474496185188358</v>
+        <v>0.002671742429845711</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02162892854021249</v>
+        <v>0.00491539047403131</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02954456586576772</v>
+        <v>0.006356228165423942</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009474445755991488</v>
+        <v>0.002671692000648637</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03909140157520383</v>
+        <v>0.00813393571447844</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01060221630920192</v>
+        <v>0.002880482578419027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01637745553768233</v>
+        <v>0.003932391042510306</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005670528216027648</v>
+        <v>0.001682211492154171</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004057500095244394</v>
+        <v>0.001807553890898702</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004174305507646062</v>
+        <v>0.001891288828855002</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003809626687743</v>
+        <v>0.001674725403697779</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003964291943123917</v>
+        <v>0.001701946488497318</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004103720949839</v>
+        <v>0.002132449028497563</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006019169650198592</v>
+        <v>0.002215758453919353</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003960480968559453</v>
+        <v>0.002002729276977794</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004395848873235672</v>
+        <v>0.002313247600247204</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003984000235365206</v>
+        <v>0.001715676555735384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00402658232934456</v>
+        <v>0.001758637369621574</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004620558847130124</v>
+        <v>0.001798911957888156</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004749264127038292</v>
+        <v>0.001929304359834755</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004827855283154991</v>
+        <v>0.002006313588721409</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004620797249307389</v>
+        <v>0.001817491421759518</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004620797249307389</v>
+        <v>0.001817491421759518</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004766791781465925</v>
+        <v>0.001947654420572927</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004827708113910967</v>
+        <v>0.002006061224668995</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004623551800186382</v>
+        <v>0.001817934669053157</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004945990241563281</v>
+        <v>0.002124343352321319</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004655508984117321</v>
+        <v>0.001833862094875357</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00469855068963357</v>
+        <v>0.001876903800391592</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006547288179077953</v>
+        <v>0.002138016318473502</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009464395541848721</v>
+        <v>0.00275916748434054</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01012369490970665</v>
+        <v>0.002938381357943996</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008575769621804395</v>
+        <v>0.002513566555547235</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006637185130197203</v>
+        <v>0.002172375686873148</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009483900418263514</v>
+        <v>0.002777865536150715</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009544816750715812</v>
+        <v>0.002836272340248062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009340660436983977</v>
+        <v>0.002648145784630946</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009663647263272183</v>
+        <v>0.002954650983642977</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006530405588344891</v>
+        <v>0.002163843895431369</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0123304438337284</v>
+        <v>0.003220116986473946</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007658166331064585</v>
+        <v>0.002333530872163733</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009308612138456154</v>
+        <v>0.002731749605496163</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00938733194134035</v>
+        <v>0.002808781476213776</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01093900672912433</v>
+        <v>0.002929496284181785</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009182949678367603</v>
+        <v>0.002620430244923306</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009326139792883787</v>
+        <v>0.002750099666234334</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009387056125328823</v>
+        <v>0.002808506470330403</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009182899811604237</v>
+        <v>0.002620379914714567</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009505338252981147</v>
+        <v>0.002926788597982729</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008297383166314176</v>
+        <v>0.002299066137643465</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009257898701051414</v>
+        <v>0.002679349046053001</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005067808253407179</v>
+        <v>0.005067808253407154</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00348773485644312</v>
+        <v>0.003487734856443119</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005473895547739862</v>
+        <v>0.005473895547739843</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004410902721960417</v>
+        <v>0.004410902721960379</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004410902721960423</v>
+        <v>0.004410902721960379</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00549345851304855</v>
+        <v>0.00549345851304853</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006154238381557882</v>
+        <v>0.006154238381557877</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00519000320892346</v>
+        <v>0.005190003208923435</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007634459964123252</v>
+        <v>0.007634459964123251</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00616821322124523</v>
+        <v>0.006168213221245189</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006024080258895033</v>
+        <v>0.006024080258895032</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005434723062172378</v>
+        <v>0.005434723062172356</v>
       </c>
       <c r="C3" t="n">
         <v>0.003848622446546617</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005901807571384572</v>
+        <v>0.005901807571384547</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004796234195019327</v>
+        <v>0.004796234195019343</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004796234195019327</v>
+        <v>0.004796234195019343</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005924309033945612</v>
+        <v>0.005924309033945588</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006684800755820492</v>
+        <v>0.006684800755820486</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005575317131551395</v>
+        <v>0.005575317131551393</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008204084866213469</v>
+        <v>0.008204084866213488</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006570574362204861</v>
+        <v>0.006570574362204876</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006534596437063733</v>
+        <v>0.006534596437063732</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003110154024992939</v>
+        <v>0.001555423204308675</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002849179801346291</v>
+        <v>0.001490980966779914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003351555714095403</v>
+        <v>0.001796824893411138</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003087048149048317</v>
+        <v>0.001611414240647117</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003087048149048316</v>
+        <v>0.001611414240647117</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003359091197868821</v>
+        <v>0.001807733726191595</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003755875463518248</v>
+        <v>0.002201144642833982</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003156623447004551</v>
+        <v>0.001623606680318559</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003912396537596989</v>
+        <v>0.002357665716912724</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003250435912963387</v>
+        <v>0.001695705092279123</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003678549079500093</v>
+        <v>0.002123818258815833</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009611882818280489</v>
+        <v>0.002699727465726751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00733867544838458</v>
+        <v>0.002281132196377136</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03280622274014306</v>
+        <v>0.006980846261905361</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01658034426171429</v>
+        <v>0.003986234343608123</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01658034426171429</v>
+        <v>0.003986234343608123</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03487080422946388</v>
+        <v>0.007353795189700402</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08120363573050307</v>
+        <v>0.01583195037596337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0165802801686288</v>
+        <v>0.003986170250522634</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09165058507288663</v>
+        <v>0.01779958681545</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02308616220432401</v>
+        <v>0.005186792900641754</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07411803050785117</v>
+        <v>0.01452116692302935</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005925566147122591</v>
+        <v>0.001723478586130507</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00395445926510521</v>
+        <v>0.001685510151347403</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004319155790346016</v>
+        <v>0.001967122505908479</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003936052224643245</v>
+        <v>0.001760838957142157</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004108590601834653</v>
+        <v>0.001791205711363294</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004313951327030517</v>
+        <v>0.001975789108013428</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006751135203259185</v>
+        <v>0.002728310354171882</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005972035569134196</v>
+        <v>0.001791662062140391</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006766230828529161</v>
+        <v>0.002859940549395155</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004179002479751688</v>
+        <v>0.001859132807148313</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004647134234383865</v>
+        <v>0.002294289245151661</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004901093363811448</v>
+        <v>0.001870628526232759</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00487562482937641</v>
+        <v>0.001847635289780645</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005142363075581765</v>
+        <v>0.002112006987324889</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00494540173404228</v>
+        <v>0.00193848446983379</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00494540173404228</v>
+        <v>0.00193848446983379</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005150030536687329</v>
+        <v>0.002122939048115679</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005546814802336751</v>
+        <v>0.002516349964758062</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00494756278582306</v>
+        <v>0.001938812002242643</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0057033358764155</v>
+        <v>0.002672871038836807</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0050413752517819</v>
+        <v>0.002010910414203205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005469488418318608</v>
+        <v>0.002439023580739916</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006989036384250173</v>
+        <v>0.002238106495838757</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0100141409844132</v>
+        <v>0.002752014128166648</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01091521859962878</v>
+        <v>0.003128029554051737</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009251580022293013</v>
+        <v>0.002696371844459226</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007131063035052712</v>
+        <v>0.002323160856727216</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01028991429104035</v>
+        <v>0.003027558583980036</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01068669855669349</v>
+        <v>0.003420969500623073</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01008744654017608</v>
+        <v>0.002843431538106999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01084381941963592</v>
+        <v>0.003577596137541254</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007072626906705853</v>
+        <v>0.00236841070353267</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0137973794636843</v>
+        <v>0.003904732396782181</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009174586303933401</v>
+        <v>0.002622763279618702</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01108190987882617</v>
+        <v>0.002939941452565026</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01134878097925805</v>
+        <v>0.003204336532453009</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01338431246717107</v>
+        <v>0.003423732750816482</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01115391083537207</v>
+        <v>0.003031182065746939</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01135631558613707</v>
+        <v>0.00321524521090006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01175309985178651</v>
+        <v>0.003608656127542445</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01115384783527281</v>
+        <v>0.003031118165027025</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01190962092586526</v>
+        <v>0.003765177201621187</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008813929806144618</v>
+        <v>0.002674880012173256</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01167577346776836</v>
+        <v>0.003531329743524298</v>
       </c>
     </row>
   </sheetData>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004943304675346899</v>
+        <v>0.004943304675346901</v>
       </c>
       <c r="C2" t="n">
         <v>0.003447380104733104</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004981275135256882</v>
+        <v>0.004981275135256888</v>
       </c>
       <c r="E2" t="n">
         <v>0.004281044914659889</v>
@@ -2906,22 +2906,22 @@
         <v>0.004281044914659889</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005021373487761048</v>
+        <v>0.005021373487761047</v>
       </c>
       <c r="H2" t="n">
         <v>0.005023615075437527</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005016188901730169</v>
+        <v>0.005016188901730174</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006679212059289705</v>
+        <v>0.006679212059289709</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005879657737884041</v>
+        <v>0.005879657737884042</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005084756541674728</v>
+        <v>0.005084756541674727</v>
       </c>
     </row>
     <row r="3">
@@ -2931,34 +2931,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005299879264447157</v>
+        <v>0.005299879264447156</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003803579681274235</v>
+        <v>0.003803579681274234</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005343553158900714</v>
+        <v>0.005343553158900715</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004648636278079667</v>
+        <v>0.004648636278079666</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004648636278079667</v>
+        <v>0.004648636278079666</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0053896745706292</v>
+        <v>0.005389674570629202</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005392675530807061</v>
+        <v>0.005392675530807064</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0053839140070958</v>
+        <v>0.005383914007095804</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007107643419976722</v>
+        <v>0.007107643419976724</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006241779916835504</v>
+        <v>0.006241779916835507</v>
       </c>
       <c r="L3" t="n">
         <v>0.005462560132382503</v>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002933378520009439</v>
+        <v>0.001487530489179724</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002761928325112377</v>
+        <v>0.001457110225165136</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002955950349481055</v>
+        <v>0.001510102318651341</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003019272763847022</v>
+        <v>0.001538574132327059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003019272763847035</v>
+        <v>0.001538574132327059</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002976642502250081</v>
+        <v>0.001533385637218465</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002981154801245683</v>
+        <v>0.001535306770415968</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002956715590944983</v>
+        <v>0.001527545387790316</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003217757832552821</v>
+        <v>0.001771909801723108</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002955333580796624</v>
+        <v>0.001509485549966913</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003017487928807259</v>
+        <v>0.001571639897977546</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006377174963751509</v>
+        <v>0.002093638659994068</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006306256429915669</v>
+        <v>0.002080911968230383</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008313783937977453</v>
+        <v>0.00245308102511708</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01030410198992186</v>
+        <v>0.002820704069168872</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01030410198992186</v>
+        <v>0.002820704069168872</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01074253543943755</v>
+        <v>0.002900182786757334</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01169845311319936</v>
+        <v>0.003069551265006355</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01030407931739077</v>
+        <v>0.002820681396637772</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03394533813965471</v>
+        <v>0.007179963906468926</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008280886491430597</v>
+        <v>0.002446782857159649</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01574194898990056</v>
+        <v>0.003811145032594979</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003851669883536595</v>
+        <v>0.001649149768284753</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003805024055767357</v>
+        <v>0.001640695072765642</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005542160702222521</v>
+        <v>0.0016711926331697</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003749345668928992</v>
+        <v>0.001667066962925235</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003883427204204139</v>
+        <v>0.00169066531300579</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003894933865777237</v>
+        <v>0.001985523644251762</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005689301828604333</v>
+        <v>0.0020119406446484</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003875006954472148</v>
+        <v>0.001979683394823612</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004241945001103046</v>
+        <v>0.001952166742411207</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003867594865093134</v>
+        <v>0.001670043535133098</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003928898663015365</v>
+        <v>0.001732048186328976</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004469765730911536</v>
+        <v>0.001757934636833281</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004467476265549999</v>
+        <v>0.001757286661055623</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00449221267406451</v>
+        <v>0.001780484486312935</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004491842446867254</v>
+        <v>0.001797746395134268</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004491842446867254</v>
+        <v>0.001797746395134268</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004513029713152182</v>
+        <v>0.001803789784872021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004517542012147783</v>
+        <v>0.001805710918069525</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004493102801847084</v>
+        <v>0.001797949535443872</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00475414504345492</v>
+        <v>0.002042313949376664</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004491720791698726</v>
+        <v>0.001779889697620469</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004553875139709362</v>
+        <v>0.001842044045631102</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00634021316275999</v>
+        <v>0.002087133383054811</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009024162418256921</v>
+        <v>0.002559263419586444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009606694630367214</v>
+        <v>0.00268063330574466</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008315030464570033</v>
+        <v>0.002470627482603881</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006448049016940785</v>
+        <v>0.002142038749601626</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00907026402179047</v>
+        <v>0.002605863018846243</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009074776320791712</v>
+        <v>0.002607784152044738</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009050337110485371</v>
+        <v>0.002600022769418093</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009311907378016201</v>
+        <v>0.002844480115912829</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00631225977837305</v>
+        <v>0.002100304557538949</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01191768300217227</v>
+        <v>0.003138074222401901</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007714135996690678</v>
+        <v>0.002328943800516338</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009261244465315883</v>
+        <v>0.002600989859642726</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009286106706176016</v>
+        <v>0.002624209831392747</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01107486658045345</v>
+        <v>0.002956358636367376</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009286893424418755</v>
+        <v>0.002641675362610412</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009306797912918064</v>
+        <v>0.002647492983459124</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009311310211913658</v>
+        <v>0.002649414116656628</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009286871001612974</v>
+        <v>0.002641652734030975</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00954791324322081</v>
+        <v>0.002886017147963769</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008387762141452686</v>
+        <v>0.002280222387396912</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009347643339475246</v>
+        <v>0.002685747244218205</v>
       </c>
     </row>
   </sheetData>
@@ -3287,34 +3287,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004849297473742722</v>
+        <v>0.00484929747374272</v>
       </c>
       <c r="C2" t="n">
         <v>0.003436117462972618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004879278794945533</v>
+        <v>0.004879278794945534</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004231235843215652</v>
+        <v>0.00423123584321565</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004231235843215651</v>
+        <v>0.00423123584321565</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004876461940096511</v>
+        <v>0.004876461940096509</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00488485122122035</v>
+        <v>0.004884851221220349</v>
       </c>
       <c r="I2" t="n">
         <v>0.00489245420218542</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006153565144867229</v>
+        <v>0.006153565144867227</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005830099027621436</v>
+        <v>0.005830099027621434</v>
       </c>
       <c r="L2" t="n">
         <v>0.004867900415207412</v>
@@ -3333,31 +3333,31 @@
         <v>0.003815527102984975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005262714315248974</v>
+        <v>0.005262714315248975</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00461671980717006</v>
+        <v>0.004616719807170059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00461671980717006</v>
+        <v>0.004616719807170059</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005259474348662874</v>
+        <v>0.005259474348662873</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005269500203182577</v>
+        <v>0.005269500203182576</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005278126660733378</v>
+        <v>0.005278126660733376</v>
       </c>
       <c r="J3" t="n">
         <v>0.00654785584710986</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006209173687870596</v>
+        <v>0.006209173687870597</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005249610738655873</v>
+        <v>0.005249610738655872</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002884759470858178</v>
+        <v>0.001471385225896203</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002739651375155503</v>
+        <v>0.001448308103341556</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002902582095896906</v>
+        <v>0.001489207850934929</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00293080389844392</v>
+        <v>0.001500854966145969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00293080389844392</v>
+        <v>0.001500854966145969</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00289834614201866</v>
+        <v>0.001487082534356488</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002905927648568212</v>
+        <v>0.001492553403606237</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002894297649664998</v>
+        <v>0.001494414335824881</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00294554240581944</v>
+        <v>0.001532168160857466</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002885323619667743</v>
+        <v>0.001471949374705768</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002895854179346984</v>
+        <v>0.001482479934385007</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005957100605224295</v>
+        <v>0.002012117262614625</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00619948212326323</v>
+        <v>0.002057238311709025</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00746814219923641</v>
+        <v>0.002292746424768623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008254482517301612</v>
+        <v>0.002437822397987861</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008254482517301612</v>
+        <v>0.002437822397987861</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007458297930471207</v>
+        <v>0.002289634044775417</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00846915754256993</v>
+        <v>0.002471681859645026</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008254463669521516</v>
+        <v>0.002437803550207772</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01188414914479618</v>
+        <v>0.003105362938392858</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005896124780221189</v>
+        <v>0.002001850376091849</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007522475649499261</v>
+        <v>0.002296765308719515</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005438126857278692</v>
+        <v>0.001920777883471133</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003782987738757016</v>
+        <v>0.001631935302340416</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003825028580581121</v>
+        <v>0.001651558431359638</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003697129209596153</v>
+        <v>0.001635728220177935</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00383238727446166</v>
+        <v>0.001659533639465274</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005451713528439172</v>
+        <v>0.001936475191931406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005586000707474957</v>
+        <v>0.001964246259417906</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003826375071936147</v>
+        <v>0.001658459961255708</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005517120663554668</v>
+        <v>0.001984765931766417</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003818809001364918</v>
+        <v>0.001636242800994254</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003816756465925997</v>
+        <v>0.001644558735944673</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004352900457636021</v>
+        <v>0.001729778038168974</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004354111463146698</v>
+        <v>0.001732453077288336</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004370597535793603</v>
+        <v>0.001747578566956739</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004360950436171975</v>
+        <v>0.001752560755422213</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004360950436171975</v>
+        <v>0.001752560755422213</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004366487128796499</v>
+        <v>0.001745475346629249</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004374068635346053</v>
+        <v>0.001750946215879008</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00436243863644284</v>
+        <v>0.001752807148097656</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004413683392597284</v>
+        <v>0.001790560973130237</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004353464606445585</v>
+        <v>0.00173034218697854</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004363995166124826</v>
+        <v>0.001740872746657779</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006179388130525977</v>
+        <v>0.002051239866855732</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008778521603022461</v>
+        <v>0.002511149257687024</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00933476836218027</v>
+        <v>0.002621272627666591</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008076200527960568</v>
+        <v>0.002406444768033868</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006270495810879446</v>
+        <v>0.002088640739549644</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008791674994672623</v>
+        <v>0.002524308406803257</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008799256501227702</v>
+        <v>0.002529779276053989</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008787626502318962</v>
+        <v>0.002531640208271665</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008839381972868633</v>
+        <v>0.002569483919037317</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006131680089533915</v>
+        <v>0.002043308110306247</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01150374267892877</v>
+        <v>0.002997468302102277</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007201024027619744</v>
+        <v>0.002231047783769927</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008615866265691382</v>
+        <v>0.002482521918471875</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008632478749356558</v>
+        <v>0.002497669656479373</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01025551324090639</v>
+        <v>0.002790003803433977</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008624212050308163</v>
+        <v>0.00250289479544442</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008628241931341185</v>
+        <v>0.002495544187812786</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008635823437890733</v>
+        <v>0.002501015057062545</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008624193438987522</v>
+        <v>0.002502875989281193</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008675438195141973</v>
+        <v>0.002540629814313777</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007796156284538892</v>
+        <v>0.002330407357997087</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008625749968669503</v>
+        <v>0.002490941587841316</v>
       </c>
     </row>
   </sheetData>
@@ -3689,31 +3689,31 @@
         <v>0.003462714554770451</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005032975828326629</v>
+        <v>0.005032975828326631</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004340707496837081</v>
+        <v>0.004340707496837075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004340707496837081</v>
+        <v>0.004340707496837076</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005142469360124434</v>
+        <v>0.005142469360124435</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005861064857460776</v>
+        <v>0.005861064857460775</v>
       </c>
       <c r="I2" t="n">
         <v>0.005045641214855366</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006589813774277906</v>
+        <v>0.006589813774277904</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005987269709662389</v>
+        <v>0.005987269709662388</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005721075825400468</v>
+        <v>0.005721075825400464</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005313708490555464</v>
+        <v>0.005313708490555453</v>
       </c>
       <c r="C3" t="n">
         <v>0.003818178014885213</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005404556500693519</v>
+        <v>0.005404556500693513</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004714257283806413</v>
+        <v>0.004714257283806416</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004714257283806413</v>
+        <v>0.004714257283806407</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005530496743777779</v>
+        <v>0.00553049674377777</v>
       </c>
       <c r="H3" t="n">
         <v>0.006357468312132637</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005419284989142766</v>
+        <v>0.005419284989142759</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007003222950783232</v>
+        <v>0.007003222950783233</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006362681354346143</v>
+        <v>0.006362681354346144</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006195970776046745</v>
+        <v>0.006195970776046743</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003036037340812632</v>
+        <v>0.00152395866677483</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002793417786253056</v>
+        <v>0.001468483013353355</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003082990007121166</v>
+        <v>0.001570911333083362</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003005859972039355</v>
+        <v>0.001563757828946689</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003005859972039356</v>
+        <v>0.001563757828946689</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003144409284865021</v>
+        <v>0.001635354680345674</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003575123971241175</v>
+        <v>0.002063045297203376</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003067088837007694</v>
+        <v>0.001574504595944638</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003248529885812284</v>
+        <v>0.001736451211774476</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00309815140735924</v>
+        <v>0.001586072733321432</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003491945846919723</v>
+        <v>0.001979867172881926</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008304425256599935</v>
+        <v>0.002451194934929071</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006717775166415375</v>
+        <v>0.002159169908519366</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01266816871573929</v>
+        <v>0.003257902776659015</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01351024687115809</v>
+        <v>0.00341252991317384</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01351024687115809</v>
+        <v>0.00341252991317384</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01947015267397429</v>
+        <v>0.00450868550125945</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0680455269802072</v>
+        <v>0.0134098361652976</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01351021105419443</v>
+        <v>0.003412494096210178</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03009782408772579</v>
+        <v>0.006461926965705773</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01418646226622345</v>
+        <v>0.003537615433906894</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06004194652553307</v>
+        <v>0.01193266723838754</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005738636684493772</v>
+        <v>0.001683568973699547</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003861637056644403</v>
+        <v>0.001656489603923501</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003983601279348887</v>
+        <v>0.001729418916136539</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003819169320904278</v>
+        <v>0.001706900273571283</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003972296447818538</v>
+        <v>0.001733850647762159</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005847008628546155</v>
+        <v>0.002111012162256156</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006452009158243584</v>
+        <v>0.002569377087372191</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003973965585812171</v>
+        <v>0.002050162077855116</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005984300725316811</v>
+        <v>0.002217946876918243</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003981819043773499</v>
+        <v>0.001741598236487612</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004408802352242664</v>
+        <v>0.002141233916944382</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004731621517400821</v>
+        <v>0.001822381480237317</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004713759838121027</v>
+        <v>0.001806463212650738</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004778442761174004</v>
+        <v>0.001869311016179761</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004760915899142832</v>
+        <v>0.001872647670443149</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004760915899142832</v>
+        <v>0.001872647670443149</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004839993461453212</v>
+        <v>0.00193377749380816</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00527070814782936</v>
+        <v>0.002361468110665858</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004762673013595882</v>
+        <v>0.001872927409407124</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004944114062400468</v>
+        <v>0.002034874025236966</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004793735583947424</v>
+        <v>0.001884495546783918</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005187530023507919</v>
+        <v>0.002278289986344414</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006754796922223166</v>
+        <v>0.002178460349556604</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009666958901471144</v>
+        <v>0.002678226243076617</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01034051431893882</v>
+        <v>0.002848235605041953</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008914379199183534</v>
+        <v>0.002603657207289264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006877801315071461</v>
+        <v>0.00224521950162777</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009794171174688454</v>
+        <v>0.002805712766612896</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01022488586106828</v>
+        <v>0.003233403383471242</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009716850726831126</v>
+        <v>0.002744862682211857</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009898867796649651</v>
+        <v>0.002906910677739594</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006762466116597286</v>
+        <v>0.002230992118652775</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01320338472962458</v>
+        <v>0.003689080406976439</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008714867898553139</v>
+        <v>0.002523432839521401</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01051480245649194</v>
+        <v>0.002827446707951712</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01057961732469639</v>
+        <v>0.002890317733827256</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01266144900039552</v>
+        <v>0.003263141488729088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01056375046076026</v>
+        <v>0.002893946547753804</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01064103607982412</v>
+        <v>0.002954760989109134</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01107175076620027</v>
+        <v>0.003382451605966835</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0105637156319668</v>
+        <v>0.002893910904708098</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01074515668077137</v>
+        <v>0.003055857520537937</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009498808923548921</v>
+        <v>0.002720109144692865</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01098857264187883</v>
+        <v>0.003299273481645387</v>
       </c>
     </row>
   </sheetData>
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004726070270741788</v>
+        <v>0.004726070270741785</v>
       </c>
       <c r="C2" t="n">
         <v>0.003440964527070963</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004750055622727638</v>
+        <v>0.004750055622727635</v>
       </c>
       <c r="E2" t="n">
         <v>0.004254526807034784</v>
@@ -4094,19 +4094,19 @@
         <v>0.004254526807034784</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00475097800694838</v>
+        <v>0.004750978006948376</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004756056531907018</v>
+        <v>0.00475605653190702</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004782856583677693</v>
+        <v>0.004782856583677697</v>
       </c>
       <c r="J2" t="n">
         <v>0.006277659741393635</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005827844647039355</v>
+        <v>0.005827844647039356</v>
       </c>
       <c r="L2" t="n">
         <v>0.004740826527434698</v>
@@ -4119,19 +4119,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00507887742246108</v>
+        <v>0.005078877422461081</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003793109574023498</v>
+        <v>0.003793109574023499</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005106465545795503</v>
+        <v>0.005106465545795504</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004615933238198689</v>
+        <v>0.004615933238198686</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004615933238198689</v>
+        <v>0.004615933238198686</v>
       </c>
       <c r="G3" t="n">
         <v>0.005107526478720674</v>
@@ -4140,10 +4140,10 @@
         <v>0.005113764263532342</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005144424664773488</v>
+        <v>0.005144424664773487</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006644101488878696</v>
+        <v>0.006644101488878691</v>
       </c>
       <c r="K3" t="n">
         <v>0.00618271700034735</v>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002903014038846809</v>
+        <v>0.00148083443048259</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00273489235207294</v>
+        <v>0.001450028350057123</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002917272314256818</v>
+        <v>0.001495092705892599</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002983147657393089</v>
+        <v>0.001522980630952575</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00298314765739309</v>
+        <v>0.001522980630952575</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002914789076965732</v>
+        <v>0.001495107470439884</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002920873647610004</v>
+        <v>0.001498694039245787</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002917513756879947</v>
+        <v>0.001511414328366272</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002956974116443561</v>
+        <v>0.001534794508079338</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002911187250571845</v>
+        <v>0.001489007642207636</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002911822827342115</v>
+        <v>0.001489643218977895</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006531152340848527</v>
+        <v>0.002119386768174829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006347944327669298</v>
+        <v>0.002085925494316407</v>
       </c>
       <c r="D5" t="n">
-        <v>0.007692811896026481</v>
+        <v>0.002335587667729753</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009561295339132329</v>
+        <v>0.002680734616665261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009561295339132329</v>
+        <v>0.002680734616665261</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007899541523818413</v>
+        <v>0.002372423896332128</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00874910127631035</v>
+        <v>0.002524462096338811</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009561277455444739</v>
+        <v>0.002680716732977681</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01180499026248539</v>
+        <v>0.003092045341344573</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007152775208288041</v>
+        <v>0.002235527118720585</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007916414485065805</v>
+        <v>0.002370451345964513</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005443993466160054</v>
+        <v>0.001641300525885986</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003771572238130334</v>
+        <v>0.001632484009014569</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003828498392105058</v>
+        <v>0.001655465933991987</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003707994039337411</v>
+        <v>0.001650553593483509</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003837780495950873</v>
+        <v>0.001673396009723703</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003826528260334484</v>
+        <v>0.00165557356584328</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005597157885937132</v>
+        <v>0.001969720062639058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003829252940248686</v>
+        <v>0.001958626705150136</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003966002348256572</v>
+        <v>0.001985010187531651</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0038183236322169</v>
+        <v>0.001648663644512052</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003814376712902483</v>
+        <v>0.00164849270197578</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004376291234390203</v>
+        <v>0.0017401312154932</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004372966504906929</v>
+        <v>0.001738329399393715</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004390424516812129</v>
+        <v>0.001754367492137428</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004390035260282317</v>
+        <v>0.001770592847719367</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004390035260282317</v>
+        <v>0.001770592847719368</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004388066272509108</v>
+        <v>0.001754404255450496</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004394150843153406</v>
+        <v>0.001757990824256399</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004390790952423341</v>
+        <v>0.001770711113376884</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004430251311986953</v>
+        <v>0.00179409129308995</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004384464446115251</v>
+        <v>0.001748304427218246</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004385100022885509</v>
+        <v>0.001748940003988506</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006199078723321694</v>
+        <v>0.002060941811806798</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008798480123570927</v>
+        <v>0.002517219792058078</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009355848595973678</v>
+        <v>0.002628282125334457</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008104459889061166</v>
+        <v>0.00242433157884209</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006295714264367537</v>
+        <v>0.002105992350620966</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008813657125749483</v>
+        <v>0.002533308241400225</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008819741696399454</v>
+        <v>0.002536894810207127</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008816381805663701</v>
+        <v>0.002549615099326612</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008856353686006199</v>
+        <v>0.002573085306696275</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00615890352673233</v>
+        <v>0.002060605703714614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01152953662859572</v>
+        <v>0.003006360839780036</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007584248577710905</v>
+        <v>0.002304731704858298</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009096878146212097</v>
+        <v>0.00256973784375835</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009114462031182805</v>
+        <v>0.002585798090161474</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01086410013572913</v>
+        <v>0.002910028259623853</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009114720274448887</v>
+        <v>0.002602137405706872</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009111977913814295</v>
+        <v>0.002585812699815129</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009118062484458575</v>
+        <v>0.002589399268621036</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009114702593728508</v>
+        <v>0.002602119557741521</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009154162953292135</v>
+        <v>0.002625499737454586</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007199518801275832</v>
+        <v>0.002425123359768103</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00910901166419069</v>
+        <v>0.002580348448353145</v>
       </c>
     </row>
   </sheetData>
@@ -4481,7 +4481,7 @@
         <v>0.003430084195289831</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004737709769026976</v>
+        <v>0.004737709769026977</v>
       </c>
       <c r="E2" t="n">
         <v>0.004214554884374767</v>
@@ -4493,19 +4493,19 @@
         <v>0.004734487290613027</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004744117339110703</v>
+        <v>0.004744117339110702</v>
       </c>
       <c r="I2" t="n">
         <v>0.004750238105053214</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006115403710903918</v>
+        <v>0.006115403710903917</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005821978044494508</v>
+        <v>0.005821978044494504</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004731752104254247</v>
+        <v>0.004731752104254246</v>
       </c>
     </row>
     <row r="3">
@@ -4521,7 +4521,7 @@
         <v>0.003801984832671861</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005112633311182721</v>
+        <v>0.005112633311182722</v>
       </c>
       <c r="E3" t="n">
         <v>0.004591429670424241</v>
@@ -4530,22 +4530,22 @@
         <v>0.004591429670424241</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00510892679347229</v>
+        <v>0.005108926793472289</v>
       </c>
       <c r="H3" t="n">
         <v>0.005120358699719267</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005127299983745974</v>
+        <v>0.005127299983745973</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006498239065118839</v>
+        <v>0.006498239065118843</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006195389936254151</v>
+        <v>0.006195389936254146</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005105764331151098</v>
+        <v>0.005105764331151097</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002861599604279843</v>
+        <v>0.001467063585606025</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002717250928369873</v>
+        <v>0.00144255332762119</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002873591024099643</v>
+        <v>0.001479055005425822</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002903288084208422</v>
+        <v>0.001490644792659001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002903288084208424</v>
+        <v>0.001490644792659001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002869275190020397</v>
+        <v>0.001476716942090027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002877432504676842</v>
+        <v>0.001482896486003025</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002865993132848304</v>
+        <v>0.001484065096770635</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002904902696259081</v>
+        <v>0.001510366677585263</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002867608538511194</v>
+        <v>0.001473072519837377</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0028700835562794</v>
+        <v>0.001475547537605581</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006096307225744025</v>
+        <v>0.002036372123898864</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006160687298709259</v>
+        <v>0.002048598125517003</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00706439096629625</v>
+        <v>0.002216635791255768</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007812094213777024</v>
+        <v>0.00235459466678166</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007812094213777024</v>
+        <v>0.00235459466678166</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007020272886077441</v>
+        <v>0.002207292532637347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008064981940085925</v>
+        <v>0.002395905181687791</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007812075057849173</v>
+        <v>0.002354575510853845</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01033273521585858</v>
+        <v>0.002817665193951039</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006531276479451604</v>
+        <v>0.002117878073948941</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007399614656072923</v>
+        <v>0.002272745006849545</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005405708983581458</v>
+        <v>0.001631900459038723</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003763304153901675</v>
+        <v>0.001626658694317197</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003800142253640437</v>
+        <v>0.001642128020941373</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003673705744928116</v>
+        <v>0.001626238300210939</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003808432492559731</v>
+        <v>0.001649950207665617</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005413384569322013</v>
+        <v>0.001924480190420859</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005546115400071057</v>
+        <v>0.001952584673047352</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003802566282427195</v>
+        <v>0.001931828345101468</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005465603028184665</v>
+        <v>0.001692724312407936</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003807433367071761</v>
+        <v>0.00163848168876775</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003795435921325103</v>
+        <v>0.001638409552971107</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004278083154010797</v>
+        <v>0.001716364689007808</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004277430067966212</v>
+        <v>0.001717144854702243</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00428994888467153</v>
+        <v>0.001728333987535729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004281200387439243</v>
+        <v>0.001733157356713544</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004281200387439243</v>
+        <v>0.001733157356713544</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004285758739751352</v>
+        <v>0.00172601804549181</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004293916054407799</v>
+        <v>0.001732197589404809</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00428247668257926</v>
+        <v>0.00173336620017242</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004321386245990036</v>
+        <v>0.001759667780987045</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004284092088242152</v>
+        <v>0.00172237362323916</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004286567106010356</v>
+        <v>0.001724848641007365</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006061628587171833</v>
+        <v>0.00203026868354323</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008587914594501488</v>
+        <v>0.002475790127261651</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009125247291622646</v>
+        <v>0.002579346502547826</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00790175780562039</v>
+        <v>0.002370375458860596</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006145462186627082</v>
+        <v>0.002061267431592705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008596832080859478</v>
+        <v>0.002484766949415482</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008604989395521671</v>
+        <v>0.00249094649332949</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008593550023687391</v>
+        <v>0.002492115104096089</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008632956314127279</v>
+        <v>0.002518504108867368</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006020687393333761</v>
+        <v>0.002028014395279137</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01123785469101911</v>
+        <v>0.00294827524933964</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007126210765654689</v>
+        <v>0.002217635145940945</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008520087958051342</v>
+        <v>0.002463852639311108</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008532733304077115</v>
+        <v>0.002475064041304875</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01013441259605504</v>
+        <v>0.002763322699847863</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008525153516969664</v>
+        <v>0.002480093103463551</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008528416629836475</v>
+        <v>0.002472725830100678</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008536573944492918</v>
+        <v>0.002478905374013675</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00852513457266438</v>
+        <v>0.002480073984781285</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008564044136075154</v>
+        <v>0.002506375565595912</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007685972560516708</v>
+        <v>0.002321104583115196</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00852922499609547</v>
+        <v>0.002471556425616231</v>
       </c>
     </row>
   </sheetData>
@@ -4871,16 +4871,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005280403820565806</v>
+        <v>0.005280403820565809</v>
       </c>
       <c r="C2" t="n">
         <v>0.005886323706809309</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005648940344967726</v>
+        <v>0.005648940344967725</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006336794036752893</v>
+        <v>0.006336794036752892</v>
       </c>
       <c r="F2" t="n">
         <v>0.004428860775266491</v>
@@ -4889,19 +4889,19 @@
         <v>0.005660358970538639</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007077795166288719</v>
+        <v>0.007077795166288723</v>
       </c>
       <c r="I2" t="n">
         <v>0.004692794885719106</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01039165889324858</v>
+        <v>0.01039165889324857</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007232873959828853</v>
+        <v>0.007232873959828854</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008899240051106755</v>
+        <v>0.008899240051106753</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005821417777390424</v>
+        <v>0.005821417777390423</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006338674246175454</v>
+        <v>0.006338674246175457</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006245311122563669</v>
+        <v>0.00624531112256367</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006789588572497684</v>
+        <v>0.006789588572497683</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004881655311011284</v>
+        <v>0.004881655311011283</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006258444907331374</v>
+        <v>0.006258444907331376</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007889206631395626</v>
+        <v>0.007889206631395635</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005145095397334579</v>
+        <v>0.00514509539733458</v>
       </c>
       <c r="J3" t="n">
         <v>0.01112434948851016</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007719772869755654</v>
+        <v>0.007719772869755655</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009983666795755941</v>
+        <v>0.009983666795755942</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004015114555967343</v>
+        <v>0.002226957179440171</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003431116094171643</v>
+        <v>0.001836484689416322</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004234193903507056</v>
+        <v>0.002446036526979884</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00348727481500059</v>
+        <v>0.001846369407033545</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003487274815000591</v>
+        <v>0.001846369407033545</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004236905960792821</v>
+        <v>0.002452107069646315</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005083300782080926</v>
+        <v>0.003295143405553753</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003639968439290734</v>
+        <v>0.001873115534279627</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004773691228223213</v>
+        <v>0.002985533851696036</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003800949634621385</v>
+        <v>0.002012792258094211</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006165706838992376</v>
+        <v>0.004377549462465199</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06529579553660271</v>
+        <v>0.01301235697359019</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03211786987349044</v>
+        <v>0.006885353327218602</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08808564121591014</v>
+        <v>0.01720389117399583</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03211787082349633</v>
+        <v>0.006885354277224543</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03211787082349633</v>
+        <v>0.006885354277224543</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09083296291552637</v>
+        <v>0.01769301301109497</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1923376893324695</v>
+        <v>0.03625191561184248</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0321177155437837</v>
+        <v>0.006885198997511891</v>
       </c>
       <c r="J5" t="n">
-        <v>0.149371952114272</v>
+        <v>0.02843482762974092</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04622140126627423</v>
+        <v>0.009478791704809799</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09231762541905662</v>
+        <v>0.01954028705039561</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007401807720526162</v>
+        <v>0.002823015173172723</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004674486864222479</v>
+        <v>0.002055317943759499</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005430077748401859</v>
+        <v>0.002656512082540882</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004539376592890343</v>
+        <v>0.002031539318938779</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004778327989835057</v>
+        <v>0.002073594764573167</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005388387492670599</v>
+        <v>0.003048165063378862</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006279397036204994</v>
+        <v>0.003918333095224285</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007026661603849554</v>
+        <v>0.002469173528012177</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008204197964786775</v>
+        <v>0.00358930303405964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004892492618856411</v>
+        <v>0.002204903822278598</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007405714354128051</v>
+        <v>0.00459579078394651</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00605309756028705</v>
+        <v>0.002585642186256868</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005678105773317151</v>
+        <v>0.002231954870803036</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006272031293860674</v>
+        <v>0.002804695905738689</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005675393965709648</v>
+        <v>0.002231478375471586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005675393965709648</v>
+        <v>0.002231478375471586</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006274888965112527</v>
+        <v>0.002810792076463011</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007121283786400628</v>
+        <v>0.003653828412370451</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00567795144361044</v>
+        <v>0.002231800541096322</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006811674232542916</v>
+        <v>0.003344218858512732</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00583893263894109</v>
+        <v>0.002371477264910906</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008203689843312066</v>
+        <v>0.004736234469281888</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008324434293419957</v>
+        <v>0.002985397449122145</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01132125988224439</v>
+        <v>0.003225149988592503</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01261661833542312</v>
+        <v>0.003921343219003014</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01039877336707967</v>
+        <v>0.003062793145608147</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008054849071831184</v>
+        <v>0.002650262471879753</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01191979816527527</v>
+        <v>0.003804296090308251</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01276619298656346</v>
+        <v>0.004647332426215707</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0113228606437732</v>
+        <v>0.003225304554941565</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0124572464312403</v>
+        <v>0.004337839560099437</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008047603532011748</v>
+        <v>0.00276020333998499</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0173725775739413</v>
+        <v>0.006349958701128514</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01170980852873193</v>
+        <v>0.003581223311308503</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0137394177793187</v>
+        <v>0.003650745776171444</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01433348972410429</v>
+        <v>0.004223512581773559</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01651427458656203</v>
+        <v>0.00413912135440484</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01373941593988661</v>
+        <v>0.00365074623523628</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01433620097111408</v>
+        <v>0.004229582981831417</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01518259579240218</v>
+        <v>0.005072619317738861</v>
       </c>
       <c r="I9" t="n">
-        <v>0.013739263449612</v>
+        <v>0.003650591446464734</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01487298623854447</v>
+        <v>0.004763009763881141</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01250700970098428</v>
+        <v>0.003545058821471333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0162650018493136</v>
+        <v>0.006155025374650297</v>
       </c>
     </row>
   </sheetData>
@@ -5267,25 +5267,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00502705632348817</v>
+        <v>0.005027056323488171</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00594810929349463</v>
+        <v>0.005948109293494631</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005593578136858725</v>
+        <v>0.005593578136858716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006398924261967094</v>
+        <v>0.006398924261967098</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004491539262972773</v>
+        <v>0.004491539262972774</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00557855508083208</v>
+        <v>0.005578555080832073</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006619719014042881</v>
+        <v>0.00661971901404288</v>
       </c>
       <c r="I2" t="n">
         <v>0.004757493958766106</v>
@@ -5294,7 +5294,7 @@
         <v>0.009987074550363266</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007220547161965526</v>
+        <v>0.007220547161965529</v>
       </c>
       <c r="L2" t="n">
         <v>0.008544988099380625</v>
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005530299176462778</v>
+        <v>0.005530299176462781</v>
       </c>
       <c r="C3" t="n">
         <v>0.006410520755129601</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006181916616479012</v>
+        <v>0.006181916616478996</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006861723853017888</v>
+        <v>0.006861723853017892</v>
       </c>
       <c r="F3" t="n">
         <v>0.004954338854023565</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006164636990031697</v>
+        <v>0.006164636990031696</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007362547158186775</v>
+        <v>0.007362547158186773</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00521992844973553</v>
+        <v>0.005219928449735531</v>
       </c>
       <c r="J3" t="n">
         <v>0.01066023969189983</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007706390765298222</v>
+        <v>0.007706390765298226</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009576500489734571</v>
+        <v>0.009576500489734574</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003779981676801551</v>
+        <v>0.002062161248528063</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003445595218341485</v>
+        <v>0.001871421105955653</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004116754889284781</v>
+        <v>0.002398934461011287</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003495090606906665</v>
+        <v>0.001880132904978562</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003495090606906666</v>
+        <v>0.001880132904978562</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004104312737697924</v>
+        <v>0.002389385852468339</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004726551847768186</v>
+        <v>0.003008731419494695</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003597582391008259</v>
+        <v>0.001898060152088229</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004452463650872756</v>
+        <v>0.002734643222599249</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003711122659861689</v>
+        <v>0.001993302231588193</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005870649956363486</v>
+        <v>0.004152829528089988</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04886268988541377</v>
+        <v>0.009996717850249602</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03335233102332873</v>
+        <v>0.00713500657911212</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07847533987091374</v>
+        <v>0.01548604534686402</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03335233176444839</v>
+        <v>0.007135007320231832</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03335233176444839</v>
+        <v>0.007135007320231832</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07973559597234509</v>
+        <v>0.01570049162963862</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1523354728905302</v>
+        <v>0.02898790138224992</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03335219668338729</v>
+        <v>0.007134872239170738</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1170518643757779</v>
+        <v>0.02255213764279939</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04091413644893582</v>
+        <v>0.008541032622985672</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2806826623849884</v>
+        <v>0.02032421571234697</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004914225825732563</v>
+        <v>0.002624083118800366</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004640022796303537</v>
+        <v>0.002081640358537879</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005290617959758464</v>
+        <v>0.00260553436029513</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004508736908137659</v>
+        <v>0.002058534653028528</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004723191834489836</v>
+        <v>0.002096278719861993</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005238556886628928</v>
+        <v>0.002951307722740639</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008040109141410214</v>
+        <v>0.003591917500015639</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004731826539939263</v>
+        <v>0.00245998202236053</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005727475843344082</v>
+        <v>0.003302016382864361</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004808691008960283</v>
+        <v>0.002186474259982822</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007082348636976527</v>
+        <v>0.004366088494722324</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005611203820868106</v>
+        <v>0.00238445634413739</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005428938875016196</v>
+        <v>0.002220489587638939</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005947841244772075</v>
+        <v>0.002721205657830789</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005425934714164734</v>
+        <v>0.002219961466014588</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005425934714164734</v>
+        <v>0.002219961466014588</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005935534881764478</v>
+        <v>0.002711680948077666</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006557773991834752</v>
+        <v>0.003331026515104015</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005428804535074813</v>
+        <v>0.002220355247697554</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006283685794939293</v>
+        <v>0.003056938318208572</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005542344803928244</v>
+        <v>0.002315597327197516</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007701872100430038</v>
+        <v>0.004475124623699322</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007667859334251916</v>
+        <v>0.002746427712531558</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01053029819568858</v>
+        <v>0.003118328823215631</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01168322505149411</v>
+        <v>0.003730633202344175</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00969721754080019</v>
+        <v>0.002971707239429011</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00758046291279378</v>
+        <v>0.002599158426918578</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01103900586453289</v>
+        <v>0.003609891836177857</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01166124497460354</v>
+        <v>0.004229237403204277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01053227551784323</v>
+        <v>0.003118566135797745</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01138775555948379</v>
+        <v>0.003955254591900785</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007542404156205127</v>
+        <v>0.002667607771290842</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01598799660698592</v>
+        <v>0.005933482528950893</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01027360440242313</v>
+        <v>0.00320503884204466</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01213810781527874</v>
+        <v>0.003401303314726781</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01265714691305314</v>
+        <v>0.003902043449049764</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01450003395760432</v>
+        <v>0.003817002924206215</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01213810636801732</v>
+        <v>0.003401303670691414</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01264470382202703</v>
+        <v>0.003892494675165511</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0132669429320973</v>
+        <v>0.00451184024219186</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01213797347533737</v>
+        <v>0.003401168974785396</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01299285473520184</v>
+        <v>0.004237752045296415</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009674266790235793</v>
+        <v>0.003042815592847137</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01441104104069257</v>
+        <v>0.005655938350787165</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00490528841559433</v>
+        <v>0.004905288415594327</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006058861675269682</v>
+        <v>0.006058861675269684</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005360346369003518</v>
+        <v>0.005360346369003523</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006478968521201695</v>
+        <v>0.006478968521201701</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004667220307162464</v>
+        <v>0.004667220307162465</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005418935960736337</v>
+        <v>0.005418935960736336</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006004101161263641</v>
+        <v>0.006004101161263639</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00493160498880202</v>
+        <v>0.004931604988802024</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009516912242328392</v>
+        <v>0.009516912242328389</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007095600557859395</v>
+        <v>0.007095600557859399</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008107417710892467</v>
+        <v>0.008107417710892476</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005400919135584973</v>
+        <v>0.005400919135584971</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006558148058799144</v>
+        <v>0.006558148058799148</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005924330046976611</v>
+        <v>0.005924330046976614</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006978607783911094</v>
+        <v>0.006978607783911096</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005166859569871855</v>
+        <v>0.00516685956987186</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005991720214266701</v>
+        <v>0.005991720214266711</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006665102295281533</v>
+        <v>0.006665102295281529</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005431105983287951</v>
+        <v>0.005431105983287957</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01015275572535625</v>
+        <v>0.01015275572535624</v>
       </c>
       <c r="K3" t="n">
         <v>0.007573881719717381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009083894237247795</v>
+        <v>0.009083894237247786</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003719503407934578</v>
+        <v>0.001993301993741551</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003593760411351728</v>
+        <v>0.001984242763879736</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003990016078795181</v>
+        <v>0.002263814664602151</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003641663269133012</v>
+        <v>0.001992674189227638</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003641663269133013</v>
+        <v>0.001992674189227637</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004021950470613842</v>
+        <v>0.00229813423798305</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004372605459603615</v>
+        <v>0.002646404045410585</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003716993171129241</v>
+        <v>0.002005858675665301</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004274407396547397</v>
+        <v>0.002548205982354361</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003650841049387875</v>
+        <v>0.001924639635194839</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005622496731008193</v>
+        <v>0.003896295316815156</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04162800295346975</v>
+        <v>0.008665197877603349</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04206910353515454</v>
+        <v>0.008755903116976077</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06454529355164201</v>
+        <v>0.01292154344207315</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04206910416916434</v>
+        <v>0.008755903750985864</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04206910416916434</v>
+        <v>0.008755903750985864</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06987062934355792</v>
+        <v>0.0138875016568229</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1106841693609624</v>
+        <v>0.02135723919066311</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04206901487760879</v>
+        <v>0.008755814459430317</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09932846668408565</v>
+        <v>0.01927772032631051</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03362590533223611</v>
+        <v>0.007200250920389687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2496782051746562</v>
+        <v>0.04685009977014758</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004871499874995863</v>
+        <v>0.002196053370845705</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004813142221207768</v>
+        <v>0.002198853961251503</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007185061023916595</v>
+        <v>0.002826142571896488</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004679811397086843</v>
+        <v>0.002175388258757464</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004870179331703433</v>
+        <v>0.002208893015068433</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005173946937675117</v>
+        <v>0.002500885615087201</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007653873277970802</v>
+        <v>0.003223907178313947</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006883322437080867</v>
+        <v>0.002563132623453144</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007472796044341078</v>
+        <v>0.002775638839420336</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004770992109206856</v>
+        <v>0.002121786220654722</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00684257417487511</v>
+        <v>0.004111028945772192</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005505818374903657</v>
+        <v>0.002307693426224544</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005503396795644031</v>
+        <v>0.002320338765694015</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005776194653448812</v>
+        <v>0.002578182092037757</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005500259821265242</v>
+        <v>0.002319787180630417</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005500259821265242</v>
+        <v>0.002319787180630417</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005808265437582906</v>
+        <v>0.002612525670466034</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006158920426572687</v>
+        <v>0.002960795477893574</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005503308138098314</v>
+        <v>0.002320250108148296</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006060722363516464</v>
+        <v>0.002862597414837353</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005437156016356942</v>
+        <v>0.002239031067677833</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007408811697977254</v>
+        <v>0.004210686749298156</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0075126029394725</v>
+        <v>0.002660887507674841</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01048425379081814</v>
+        <v>0.003196969592094533</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01137659864653996</v>
+        <v>0.003563853189480833</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009670465717090793</v>
+        <v>0.003053743414318696</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007602736471324739</v>
+        <v>0.002689823069035815</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01079137306309021</v>
+        <v>0.003489552607803059</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01114202805208058</v>
+        <v>0.003837822415230703</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01048641576360562</v>
+        <v>0.003197277045485317</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01104441491703921</v>
+        <v>0.003739727299504537</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007388653852495249</v>
+        <v>0.002582494684977081</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01550093763218746</v>
+        <v>0.005634900906001883</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009598118777956995</v>
+        <v>0.00302793829325921</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01146791132306027</v>
+        <v>0.003370093316831065</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01174084664090027</v>
+        <v>0.003627960836140879</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01362840627409013</v>
+        <v>0.003750340948575993</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01146791031679883</v>
+        <v>0.003370093662153134</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01177277996499915</v>
+        <v>0.003662280221603093</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01212343495398893</v>
+        <v>0.004010550029030633</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01146782266551455</v>
+        <v>0.00337000465928535</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01202523689093269</v>
+        <v>0.003912351965974409</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01031690277644389</v>
+        <v>0.003097866492799447</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0133733262253935</v>
+        <v>0.005260441300435213</v>
       </c>
     </row>
   </sheetData>
@@ -6062,31 +6062,31 @@
         <v>0.004380173271440389</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005566585002042165</v>
+        <v>0.005566585002042167</v>
       </c>
       <c r="D2" t="n">
         <v>0.004597529070083085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006011353518484907</v>
+        <v>0.006011353518484908</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00412054149867583</v>
+        <v>0.004120541498675828</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00471207463514745</v>
+        <v>0.004712074635147448</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005127242433658249</v>
+        <v>0.00512724243365825</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004381323376938896</v>
+        <v>0.004381323376938895</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00974619755052226</v>
+        <v>0.009746197550522254</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006893758349445706</v>
+        <v>0.006893758349445705</v>
       </c>
       <c r="L2" t="n">
         <v>0.005724799571937498</v>
@@ -6099,16 +6099,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00478254440511834</v>
+        <v>0.004782544405118338</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005968815051281454</v>
+        <v>0.005968815051281455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005032548598675483</v>
+        <v>0.005032548598675482</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006413957528932645</v>
+        <v>0.006413957528932646</v>
       </c>
       <c r="F3" t="n">
         <v>0.004523145509123562</v>
@@ -6120,16 +6120,16 @@
         <v>0.005642160048318158</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00478383919956745</v>
+        <v>0.004783839199567448</v>
       </c>
       <c r="J3" t="n">
         <v>0.01038343755143208</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007327925468741681</v>
+        <v>0.007327925468741678</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006329079372884515</v>
+        <v>0.006329079372884518</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003291083681594377</v>
+        <v>0.001663975869578228</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003089245989318813</v>
+        <v>0.001629211095296829</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003420292493740994</v>
+        <v>0.001793184681724847</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003142284027507206</v>
+        <v>0.001638546553484322</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003142284027507205</v>
+        <v>0.001638546553484322</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003485650583658976</v>
+        <v>0.001860795912965135</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003735125331037174</v>
+        <v>0.002108017519021022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003274621295051074</v>
+        <v>0.001661782111294549</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004220597289377332</v>
+        <v>0.002593489477361184</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003416919011125945</v>
+        <v>0.001789811199109796</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004090228982444835</v>
+        <v>0.002463121170428687</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01824484372009469</v>
+        <v>0.004295837622093263</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01834835314983384</v>
+        <v>0.004314813940995255</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02915546014331747</v>
+        <v>0.006322574163507336</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01834835407643204</v>
+        <v>0.004314814867593454</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01834835407643204</v>
+        <v>0.004314814867593454</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03681435168709862</v>
+        <v>0.007726647275385781</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0632569738618539</v>
+        <v>0.01258386280368029</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01834828635658832</v>
+        <v>0.004314747147749737</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1155273541607592</v>
+        <v>0.02218347858057396</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02936951452962388</v>
+        <v>0.006357467985615113</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04450155497559097</v>
+        <v>0.02076902782551178</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004322324116250123</v>
+        <v>0.001845474185094171</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004238762931413041</v>
+        <v>0.001831526076009144</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004453399991396868</v>
+        <v>0.002313578296087444</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004110165293914923</v>
+        <v>0.001808893655449036</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00429443667361438</v>
+        <v>0.001841325418100405</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006388448913084782</v>
+        <v>0.002042294228481078</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006779695967049602</v>
+        <v>0.002643861948055683</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00617741962447688</v>
+        <v>0.001843280426810492</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007174999541686089</v>
+        <v>0.003113464270949987</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004429789272699382</v>
+        <v>0.001968076364180771</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005149026335909255</v>
+        <v>0.00264946950362868</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005026409057556197</v>
+        <v>0.001969393134092573</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005010013464258418</v>
+        <v>0.001967266169054414</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00515547629745652</v>
+        <v>0.002098577029523979</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005007046956405012</v>
+        <v>0.001966744827191961</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005007046956405012</v>
+        <v>0.001966744827191961</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0052209759596208</v>
+        <v>0.002166213177479482</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005470450706998998</v>
+        <v>0.002413434783535372</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005009946671012906</v>
+        <v>0.001967199375808895</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005955922665339155</v>
+        <v>0.00289890674187553</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005152244387087768</v>
+        <v>0.002095228463624143</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005825554358406658</v>
+        <v>0.002768538434943037</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007037126996235839</v>
+        <v>0.002323279489382619</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009974166794246557</v>
+        <v>0.002840957150394556</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01073470325238707</v>
+        <v>0.003080520968270992</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009166049343165629</v>
+        <v>0.002698729243295497</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007112732018354394</v>
+        <v>0.002337345396086915</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0101872148250866</v>
+        <v>0.00304027121306529</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0104366895724649</v>
+        <v>0.003287492819121197</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009976185536478692</v>
+        <v>0.002841257411394701</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01092274237034472</v>
+        <v>0.003773067005219782</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007108062007681638</v>
+        <v>0.002439452362983449</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01387908196375922</v>
+        <v>0.004185959285804643</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009624931402913711</v>
+        <v>0.002778733062490001</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01161060633500972</v>
+        <v>0.003128970508011828</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0117562116577414</v>
+        <v>0.003260306446639163</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0139209536649163</v>
+        <v>0.003535592399388985</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01161060617244639</v>
+        <v>0.003128971242917596</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01182156883037211</v>
+        <v>0.003327917516436896</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01207104357775031</v>
+        <v>0.003575139122492783</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01161053954176421</v>
+        <v>0.003128903714766311</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01255651553609047</v>
+        <v>0.004060611080832946</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009231872860302441</v>
+        <v>0.003052771547163383</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01242614722915798</v>
+        <v>0.003930242773900448</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004305967035824681</v>
+        <v>0.004305967035824685</v>
       </c>
       <c r="C2" t="n">
         <v>0.005626711243270317</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004395659889581688</v>
+        <v>0.004395659889581694</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006070509885878601</v>
+        <v>0.006070509885878598</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004184019262661555</v>
+        <v>0.004184019262661554</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00452135115546375</v>
+        <v>0.004521351155463754</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004284117233039636</v>
+        <v>0.004284117233039637</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004445420388494731</v>
+        <v>0.004445420388494737</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00909672422713559</v>
+        <v>0.009096724227135589</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006857725989516548</v>
+        <v>0.006857725989516545</v>
       </c>
       <c r="L2" t="n">
         <v>0.004187412669728938</v>
@@ -6495,34 +6495,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004697322866359495</v>
+        <v>0.004697322866359499</v>
       </c>
       <c r="C3" t="n">
         <v>0.006038767944092673</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004800488227998733</v>
+        <v>0.004800488227998738</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006482878780858428</v>
+        <v>0.006482878780858435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004596388157641379</v>
+        <v>0.004596388157641382</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004945059220630394</v>
+        <v>0.004945059220630404</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004672512030061244</v>
+        <v>0.004672512030061242</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004857867494028764</v>
+        <v>0.004857867494028763</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009638638732070838</v>
+        <v>0.009638638732070834</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007287211017931079</v>
+        <v>0.007287211017931075</v>
       </c>
       <c r="L3" t="n">
         <v>0.004560963996834945</v>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003155383273484979</v>
+        <v>0.001605298698362245</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003104208422026841</v>
+        <v>0.001664816016674017</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003208701874434901</v>
+        <v>0.001658617299312176</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003149733597924564</v>
+        <v>0.001672829017706385</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003149733597924566</v>
+        <v>0.001672829017706385</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003281464307677175</v>
+        <v>0.001732991227983434</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003142485038082362</v>
+        <v>0.001592400462959637</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003226202120309336</v>
+        <v>0.001686260535163116</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003751232090207033</v>
+        <v>0.002201147515084296</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003306282831611832</v>
+        <v>0.001756198256489102</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003085032123441387</v>
+        <v>0.001534947548318658</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01408970780473521</v>
+        <v>0.003529739805434501</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02079648856371676</v>
+        <v>0.004778657304738773</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01788635394395339</v>
+        <v>0.004241884049549723</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02079648925560726</v>
+        <v>0.004778657996629291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02079648925560726</v>
+        <v>0.004778657996629291</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02479604627456843</v>
+        <v>0.005519557633638384</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01373345719162979</v>
+        <v>0.003456411551883648</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02079645655850777</v>
+        <v>0.00477862529952974</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06823156328902832</v>
+        <v>0.01354968574458361</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02628198871862144</v>
+        <v>0.005799922470691447</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01593673182380075</v>
+        <v>0.003796846683325568</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004159846598967533</v>
+        <v>0.002076904827208112</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004195242436853509</v>
+        <v>0.001856838002243022</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004205763865929357</v>
+        <v>0.001834098171554906</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004071142694566312</v>
+        <v>0.001834997017836608</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004225476240509852</v>
+        <v>0.001862159721775488</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004285927633159729</v>
+        <v>0.001909776772310433</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005916849969711364</v>
+        <v>0.001767136775430016</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004230665445791899</v>
+        <v>0.001863046079490116</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004872645428187268</v>
+        <v>0.002678433647229687</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004318132992673628</v>
+        <v>0.001934283883871002</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004088958047737633</v>
+        <v>0.001711638510037378</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004678184465597011</v>
+        <v>0.001873311706721707</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004749035317630402</v>
+        <v>0.001954305548731614</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004731370126978151</v>
+        <v>0.001926606910307659</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004746753039319328</v>
+        <v>0.001953904437868826</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004746753039319328</v>
+        <v>0.001953904437868826</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0048042654997892</v>
+        <v>0.002001004236342895</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004665286230194392</v>
+        <v>0.001860413471319096</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004749003312421358</v>
+        <v>0.001954273543522575</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005274033282319048</v>
+        <v>0.002469160523443755</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00482908402372386</v>
+        <v>0.002024211264848563</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004607833315553417</v>
+        <v>0.001802960556678118</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006459321561739937</v>
+        <v>0.002186791833944236</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009141705739795784</v>
+        <v>0.002727415538843545</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009667514835337952</v>
+        <v>0.002795368374271505</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008427194369249321</v>
+        <v>0.002601662108426561</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006611719943970406</v>
+        <v>0.002282138611308845</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00919844574879114</v>
+        <v>0.002774379955976618</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009059466479195968</v>
+        <v>0.002633789190952759</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009143183561423298</v>
+        <v>0.002727649263156299</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009668727064560196</v>
+        <v>0.003242626624927091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006561682502223372</v>
+        <v>0.002329148595412142</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01173155563242202</v>
+        <v>0.00305673567765328</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00838133879590712</v>
+        <v>0.002525066865324684</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01012106840204601</v>
+        <v>0.00289978336646559</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01010353734761536</v>
+        <v>0.002872108336016505</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01204692055669993</v>
+        <v>0.00323873391396583</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01012106884171455</v>
+        <v>0.002899784013965037</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0101762985842048</v>
+        <v>0.00294648205407687</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01003731931461001</v>
+        <v>0.002805891289053073</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01012103639683698</v>
+        <v>0.002899751361256551</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01064606636673466</v>
+        <v>0.003414638341177733</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009194932097080472</v>
+        <v>0.00279260052159573</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009979866399969032</v>
+        <v>0.002748438374412093</v>
       </c>
     </row>
   </sheetData>
@@ -6851,13 +6851,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004406457150995709</v>
+        <v>0.00440645715099571</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005610968070847913</v>
+        <v>0.005610968070847916</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004313290766972738</v>
+        <v>0.004313290766972739</v>
       </c>
       <c r="E2" t="n">
         <v>0.006024896801616726</v>
@@ -6869,16 +6869,16 @@
         <v>0.004462748560761938</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004281432861896107</v>
+        <v>0.004281432861896109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004496891079829959</v>
+        <v>0.00449689107982996</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008719762602058412</v>
+        <v>0.008719762602058411</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00677574020733586</v>
+        <v>0.006775740207335863</v>
       </c>
       <c r="L2" t="n">
         <v>0.004263718273717256</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004824524641493136</v>
+        <v>0.004824524641493137</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006042394016706649</v>
+        <v>0.006042394016706653</v>
       </c>
       <c r="D3" t="n">
         <v>0.004717364000508408</v>
@@ -6903,22 +6903,22 @@
         <v>0.006456616764553687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004663485364213689</v>
+        <v>0.00466348536421369</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004889271423454701</v>
+        <v>0.004889271423454704</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004681029564756784</v>
+        <v>0.004681029564756785</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00492877706150823</v>
+        <v>0.004928777061508231</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009239119496469252</v>
+        <v>0.009239119496469253</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007205035178907027</v>
+        <v>0.007205035178907028</v>
       </c>
       <c r="L3" t="n">
         <v>0.004660340655784526</v>
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003217184039378874</v>
+        <v>0.001665978221700066</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003159617371705076</v>
+        <v>0.001700367405665681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003161800571871775</v>
+        <v>0.00161059475419298</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003203793602925544</v>
+        <v>0.001708142905622427</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003203793602925544</v>
+        <v>0.001708142905622427</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003248815046388533</v>
+        <v>0.00169911867379291</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00314293976769909</v>
+        <v>0.001591733950020264</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003259651331723951</v>
+        <v>0.001717959384895871</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003618045508893235</v>
+        <v>0.002066839691214418</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003261617754933312</v>
+        <v>0.001710411937254471</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003132421500148328</v>
+        <v>0.001581215682469506</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01941143508099836</v>
+        <v>0.004516166389581054</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02386810029131879</v>
+        <v>0.005345060379768516</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01443508332288175</v>
+        <v>0.003594692507619691</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02386810087785288</v>
+        <v>0.005345060966302604</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02386810087785288</v>
+        <v>0.005345060966302604</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02246173803249498</v>
+        <v>0.005080593101024808</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01411703562672989</v>
+        <v>0.003523174810743978</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02386808330389439</v>
+        <v>0.005345043392344141</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05721931147887546</v>
+        <v>0.01150066245081314</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02220750985677928</v>
+        <v>0.005044888929111161</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01878577001805276</v>
+        <v>0.003412442682697936</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004240540057771994</v>
+        <v>0.001846088879961301</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004258587855883421</v>
+        <v>0.001893786209833017</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005879095798391281</v>
+        <v>0.001786224950562277</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004132814610461418</v>
+        <v>0.001871650602062756</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004279515414602326</v>
+        <v>0.001897469943451652</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004272171064781563</v>
+        <v>0.002174703970336009</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005925154605484773</v>
+        <v>0.002081403758817222</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004283007350117051</v>
+        <v>0.001898070043157109</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004755633111661002</v>
+        <v>0.002545940267194476</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004291754200237087</v>
+        <v>0.00189171595064552</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004151307502872024</v>
+        <v>0.001760539617977192</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004715437491803583</v>
+        <v>0.001929670827897964</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004757921771573051</v>
+        <v>0.001981668978518183</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004659920512072393</v>
+        <v>0.001874263862239575</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004755789151188568</v>
+        <v>0.00198129412063662</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004755789151188568</v>
+        <v>0.00198129412063662</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004747068498813267</v>
+        <v>0.00196281127999081</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004641193220123806</v>
+        <v>0.001855426556218165</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004757904784148639</v>
+        <v>0.00198165199109377</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005116298961317949</v>
+        <v>0.002330532297412318</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004759871207357909</v>
+        <v>0.00197410454345237</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004630674952573039</v>
+        <v>0.001844908288667403</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006471324471919648</v>
+        <v>0.002238706934723843</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009088411396445875</v>
+        <v>0.002743835148368798</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009526060941349302</v>
+        <v>0.002730704573151581</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008384022081081695</v>
+        <v>0.002619863112837659</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006594270849166544</v>
+        <v>0.002304866897727432</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009078930263680089</v>
+        <v>0.002725218946476206</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0089730549849902</v>
+        <v>0.002617834222703473</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009089766549015577</v>
+        <v>0.002744059657579167</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009448666974454633</v>
+        <v>0.003093029063592712</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006467908133796828</v>
+        <v>0.002274719040876708</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01165335777523623</v>
+        <v>0.003080900458758795</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008010283247063578</v>
+        <v>0.002509563677681526</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009599575527619818</v>
+        <v>0.002833800034965055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009501708829712187</v>
+        <v>0.002726418601526683</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01138456040385646</v>
+        <v>0.003147957854784482</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009599575878805847</v>
+        <v>0.002833800580077869</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00958872225485995</v>
+        <v>0.002814942336437678</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00948284697617047</v>
+        <v>0.002707557612665033</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009599558540195405</v>
+        <v>0.00283378304754064</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009957952717364596</v>
+        <v>0.003182663353859188</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008705298774325621</v>
+        <v>0.002662100242985071</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009472328708619703</v>
+        <v>0.002697039345114276</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00488238547485635</v>
+        <v>0.004882385474856351</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005809688305578519</v>
+        <v>0.005809688305578521</v>
       </c>
       <c r="D2" t="n">
         <v>0.00556977917030665</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00625687066698063</v>
+        <v>0.006256870666980632</v>
       </c>
       <c r="F2" t="n">
         <v>0.004358428203776073</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005459096615263735</v>
+        <v>0.005459096615263734</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00699560912879899</v>
+        <v>0.006995609128798992</v>
       </c>
       <c r="I2" t="n">
         <v>0.004623446243038076</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009843469134049269</v>
+        <v>0.009843469134049272</v>
       </c>
       <c r="K2" t="n">
         <v>0.007173523426027994</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008250973460343529</v>
+        <v>0.008250973460343531</v>
       </c>
     </row>
     <row r="3">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005361710034443896</v>
+        <v>0.005361710034443897</v>
       </c>
       <c r="C3" t="n">
         <v>0.006249744723667087</v>
@@ -7296,28 +7296,28 @@
         <v>0.00615235517738678</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006697347115030473</v>
+        <v>0.006697347115030474</v>
       </c>
       <c r="F3" t="n">
         <v>0.004798904651825921</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006025047311265231</v>
+        <v>0.006025047311265228</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007792707358569326</v>
+        <v>0.007792707358569324</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005063542816711827</v>
+        <v>0.005063542816711828</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01049533796495711</v>
+        <v>0.01049533796495712</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007650390833158115</v>
+        <v>0.007650390833158112</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009236139292198341</v>
+        <v>0.009236139292198338</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003723544655053727</v>
+        <v>0.001982135937500987</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00334093117650541</v>
+        <v>0.001788109534555412</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004132171079657251</v>
+        <v>0.002390762362104513</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00339640852389829</v>
+        <v>0.001797874329016418</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003396408523898291</v>
+        <v>0.001797874329016417</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00406256351519142</v>
+        <v>0.002324295453462982</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004979451256935146</v>
+        <v>0.00323804253938241</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003545484407934321</v>
+        <v>0.00182399872304432</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004406403349896706</v>
+        <v>0.002664994632343962</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003713820264279871</v>
+        <v>0.001972411546727127</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005725469796432558</v>
+        <v>0.003984061078879817</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04364766557395281</v>
+        <v>0.00900878118115263</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02908345051669633</v>
+        <v>0.006318792913879023</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08101489723886411</v>
+        <v>0.0159221220928038</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02908345146496425</v>
+        <v>0.006318793862146942</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02908345146496424</v>
+        <v>0.006318793862146942</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07775487352036929</v>
+        <v>0.01529414194409586</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1731504719083355</v>
+        <v>0.0328361420136485</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0290833143758621</v>
+        <v>0.006318656773044837</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1180285471765316</v>
+        <v>0.02266249183747318</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04308235971371342</v>
+        <v>0.008901274452282669</v>
       </c>
       <c r="L5" t="n">
-        <v>0.279322318586034</v>
+        <v>0.05213710620492738</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004845118250390017</v>
+        <v>0.002179532889210558</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004561610449461228</v>
+        <v>0.002002949085431503</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005306970734933603</v>
+        <v>0.00259752710031277</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004429176599982237</v>
+        <v>0.001979641509422269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004655234322863447</v>
+        <v>0.002019427668433775</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007330856897361585</v>
+        <v>0.002899515085608045</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008417478578202433</v>
+        <v>0.00384313534464669</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004667058003270609</v>
+        <v>0.002399218355189383</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007732469808725163</v>
+        <v>0.003250382325925787</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004787478708074221</v>
+        <v>0.002161375431811013</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006924195231091083</v>
+        <v>0.004195036754236524</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005653296981543409</v>
+        <v>0.002321772345122815</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005475372875258194</v>
+        <v>0.002163771271500341</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006061779353730357</v>
+        <v>0.002730373416501157</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005472458877025742</v>
+        <v>0.002163259189186975</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005472458877025741</v>
+        <v>0.002163259189186975</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005992315841681099</v>
+        <v>0.002663931861084811</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006909203583424828</v>
+        <v>0.003577678947004233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005475236734424001</v>
+        <v>0.00216363513066615</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006336155676386387</v>
+        <v>0.003004631039965793</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005643572590769555</v>
+        <v>0.002312047954348958</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007655222122922235</v>
+        <v>0.004323697486501631</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007834691799451314</v>
+        <v>0.002705697830994268</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01088174416860098</v>
+        <v>0.003115292613976693</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01213940409669222</v>
+        <v>0.003800035365466376</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009999380129317292</v>
+        <v>0.002959997325273081</v>
       </c>
       <c r="F8" t="n">
-        <v>0.007757405181683497</v>
+        <v>0.002565409736627643</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01140066626596799</v>
+        <v>0.0036158015306015</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01231755400771196</v>
+        <v>0.004529548616520965</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0108835871587109</v>
+        <v>0.003115504800182838</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01174514028480882</v>
+        <v>0.003956612325889734</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007765025052073318</v>
+        <v>0.002685423585515247</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01643439750683792</v>
+        <v>0.00586883234569833</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01110078820481873</v>
+        <v>0.003280530795224141</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01323066299784421</v>
+        <v>0.003528702325679459</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01381721407769038</v>
+        <v>0.004095329920521966</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01589381208625021</v>
+        <v>0.003997417344071909</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01323066126397499</v>
+        <v>0.003528702801891248</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0137476059642671</v>
+        <v>0.004028862915263933</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01466449370601085</v>
+        <v>0.004942610001183358</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01323052685701002</v>
+        <v>0.003528566184845267</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01409144579897238</v>
+        <v>0.004369562094144912</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0120074654125413</v>
+        <v>0.003441641047199026</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01541051224550825</v>
+        <v>0.005688628540680759</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004263747667189553</v>
+        <v>0.00426374766718955</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005673119877198287</v>
+        <v>0.005673119877198286</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005388220668795612</v>
+        <v>0.005388220668795613</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006120045376031827</v>
+        <v>0.006120045376031826</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004224293443021156</v>
+        <v>0.004224293443021157</v>
       </c>
       <c r="G2" t="n">
         <v>0.004966596733715823</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004536039948473445</v>
+        <v>0.004536039948473444</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004490480454483008</v>
+        <v>0.004490480454483007</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009412013534916875</v>
+        <v>0.009412013534916873</v>
       </c>
       <c r="K2" t="n">
         <v>0.006780698084805773</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00947001210810231</v>
+        <v>0.009470012108102305</v>
       </c>
     </row>
     <row r="3">
@@ -7686,22 +7686,22 @@
         <v>0.004650072175038397</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006093213671883887</v>
+        <v>0.006093213671883885</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00594344906076591</v>
+        <v>0.005943449060765915</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006540482160939246</v>
+        <v>0.006540482160939244</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004644730227928574</v>
+        <v>0.004644730227928572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005458494196289122</v>
+        <v>0.005458494196289123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004963606677210692</v>
+        <v>0.004963606677210693</v>
       </c>
       <c r="I3" t="n">
         <v>0.004910802804667382</v>
@@ -7710,10 +7710,10 @@
         <v>0.01000024477497568</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007200577625279937</v>
+        <v>0.007200577625279939</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01063811888384228</v>
+        <v>0.01063811888384227</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003200686363077909</v>
+        <v>0.00158966879877007</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0031804384621739</v>
+        <v>0.001697346435791132</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003869137914569759</v>
+        <v>0.002258120350261934</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003227742166538675</v>
+        <v>0.00170567247493869</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003227742166538675</v>
+        <v>0.00170567247493869</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003615721022271307</v>
+        <v>0.002006993624745017</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003362689936642601</v>
+        <v>0.001751672372334783</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003318047132933871</v>
+        <v>0.001721494015698827</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003999749505434951</v>
+        <v>0.002388731941127123</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00333348327142268</v>
+        <v>0.001722465707114861</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006294618004789907</v>
+        <v>0.004683600440482077</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01043408086056021</v>
+        <v>0.002862746223428652</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02186946250239811</v>
+        <v>0.004986614649047352</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06544220092411594</v>
+        <v>0.01309497938122142</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02186946321504913</v>
+        <v>0.004986615361698401</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02186946321504913</v>
+        <v>0.004986615361698401</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0468645203154294</v>
+        <v>0.009618782259095579</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02628733647440861</v>
+        <v>0.005786410141118948</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02186937567471031</v>
+        <v>0.004986527821359554</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08785598072407354</v>
+        <v>0.01714742855563598</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02143414572007361</v>
+        <v>0.00490818228081528</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3310904921325746</v>
+        <v>0.007856971317048508</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004245760203396206</v>
+        <v>0.002107830261148198</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004299342233763516</v>
+        <v>0.001894273498523834</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004984403150185577</v>
+        <v>0.002454407030666677</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004172951489979882</v>
+        <v>0.001872029314962922</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004356596558717002</v>
+        <v>0.001904350846885517</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006559820256281771</v>
+        <v>0.002190926619644378</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006409094877978203</v>
+        <v>0.00228783963910457</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006262146366944324</v>
+        <v>0.002239655478076956</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006979427208413635</v>
+        <v>0.002595127359961904</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004349181470733337</v>
+        <v>0.00190122858922489</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007438747627999399</v>
+        <v>0.00488496725307581</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004844203457681815</v>
+        <v>0.00187892780585298</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004961651055225579</v>
+        <v>0.00201083985046953</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005512521198967286</v>
+        <v>0.002547355806748643</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004959091723249141</v>
+        <v>0.002010389995268589</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004959091723249141</v>
+        <v>0.002010389995268589</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005259238116875225</v>
+        <v>0.002296252631827927</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00500620703124653</v>
+        <v>0.002040931379417694</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004961564227537786</v>
+        <v>0.002010753022781737</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005643266600038862</v>
+        <v>0.002677990948210033</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004977000366026618</v>
+        <v>0.002011724714197771</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00793813509939382</v>
+        <v>0.004972859447564981</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006750414913557066</v>
+        <v>0.00221442102026912</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009661078696356436</v>
+        <v>0.002837939110830003</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01079337260462471</v>
+        <v>0.003476785649108144</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008896840397645484</v>
+        <v>0.002703433758207017</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006955011591889089</v>
+        <v>0.002361671890245762</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00996040375546111</v>
+        <v>0.003123657779735662</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009707372669832274</v>
+        <v>0.002868336527325406</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009662729866123675</v>
+        <v>0.002838158170689471</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01034498152252779</v>
+        <v>0.003505492770084179</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006831294113492473</v>
+        <v>0.002338080411983372</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01555886408762202</v>
+        <v>0.006314107742225445</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008950800487727459</v>
+        <v>0.002601688879224657</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01089328817741049</v>
+        <v>0.003054807978317222</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0114442935904473</v>
+        <v>0.003591347741992149</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01299934683725211</v>
+        <v>0.003425474887665324</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01089328813724342</v>
+        <v>0.003054808558472293</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01119087523906015</v>
+        <v>0.003340220759675621</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01093784415343142</v>
+        <v>0.003084899507265387</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01089320134972269</v>
+        <v>0.00305472115062943</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01157490372222378</v>
+        <v>0.003721959076057726</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009851202705027526</v>
+        <v>0.002651235758646802</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01386977222157872</v>
+        <v>0.006016827575412681</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia photochemical ozone formation results.xlsx
+++ b/Results/Ammonia/ammonia photochemical ozone formation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00560953205693296</v>
+        <v>0.003454784462611146</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006266573222879763</v>
+        <v>0.004442957941848742</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00694096160643122</v>
+        <v>0.003524854955369161</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006725010928522105</v>
+        <v>0.004826446001751193</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004790150964442045</v>
+        <v>0.003215933800998124</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006113950596601546</v>
+        <v>0.003481331008497992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007631753488872709</v>
+        <v>0.003560892633163869</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005040611844953886</v>
+        <v>0.003424858857142003</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01041356405320071</v>
+        <v>0.006737648106863639</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007479548318021005</v>
+        <v>0.005367309868422965</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009322394818389755</v>
+        <v>0.003652034288606678</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006198326511753546</v>
+        <v>0.003432275056466838</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006769575827680847</v>
+        <v>0.004902022727170187</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00772974629847683</v>
+        <v>0.00393182699747898</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007228393839891076</v>
+        <v>0.005533426336325822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005293533875811015</v>
+        <v>0.002874977100164779</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006778512322358119</v>
+        <v>0.003622803021137021</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008524789433497061</v>
+        <v>0.004198156840184526</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005543546524506823</v>
+        <v>0.003219713832165267</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01114026086010191</v>
+        <v>0.009118543230497505</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007999767626179917</v>
+        <v>0.006458566931047499</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01046872879280509</v>
+        <v>0.004841086695297498</v>
       </c>
     </row>
     <row r="4">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002470364561882935</v>
+        <v>0.002470364561882951</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002105557357597575</v>
+        <v>0.002105557357597574</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003261843011603901</v>
+        <v>0.003261843011603907</v>
       </c>
       <c r="E4" t="n">
         <v>0.002116320910763257</v>
@@ -610,22 +610,22 @@
         <v>0.002116320910763257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00276962105990855</v>
+        <v>0.002769621059908556</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003672182663929002</v>
+        <v>0.003672182663929001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002128437326728273</v>
+        <v>0.002128437326728274</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003016124901748216</v>
+        <v>0.00301612490174822</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002198972560341932</v>
+        <v>0.002198972560341933</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004676879465914687</v>
+        <v>0.004676879465914689</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01704382710414363</v>
+        <v>0.01704382710414378</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01083885449854037</v>
+        <v>0.01083885449854038</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0326587827610989</v>
+        <v>0.03265878276109899</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01083885500602862</v>
+        <v>0.01083885500602863</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01083885500602862</v>
+        <v>0.01083885500602863</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02371402627805633</v>
+        <v>0.0237140262780563</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04528847524704149</v>
+        <v>0.04528847524704142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01083868638351353</v>
+        <v>0.01083868638351352</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02935201001923442</v>
+        <v>0.02935201001923448</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01225467850348598</v>
+        <v>0.01225467850348603</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02150161160014404</v>
+        <v>0.06903725162731326</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002709086076057352</v>
+        <v>0.002709086076057361</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002347223322096679</v>
+        <v>0.002347223322096671</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003527960132170457</v>
+        <v>0.003527963038502984</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002320049719362261</v>
+        <v>0.002320049719362263</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002366792646574073</v>
+        <v>0.002366792646574072</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003470429133171225</v>
+        <v>0.003470429133171223</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004404557039447007</v>
+        <v>0.004404557039447002</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002367158840902682</v>
+        <v>0.002829245399990946</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003283857348777193</v>
+        <v>0.003721684481750814</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002426279117242817</v>
+        <v>0.002426279117242811</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004933126793717436</v>
+        <v>0.004933126793717438</v>
       </c>
     </row>
     <row r="7">
@@ -715,31 +715,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002888851209625838</v>
+        <v>0.002888851209625836</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002547092089498025</v>
+        <v>0.002547092089498024</v>
       </c>
       <c r="D7" t="n">
         <v>0.003680301198486727</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00254665072806414</v>
+        <v>0.002546650728064139</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00254665072806414</v>
+        <v>0.002546650728064139</v>
       </c>
       <c r="G7" t="n">
         <v>0.00318810770765144</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004090669311671897</v>
+        <v>0.004090669311671891</v>
       </c>
       <c r="I7" t="n">
         <v>0.002546923974471162</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003434611549491109</v>
+        <v>0.003434611549491108</v>
       </c>
       <c r="K7" t="n">
         <v>0.002617459208084819</v>
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003347871351448536</v>
+        <v>0.003347871351448542</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003690795301399383</v>
+        <v>0.003690795301403952</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004966312173897927</v>
+        <v>0.004966312173897924</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003503492290442938</v>
+        <v>0.003503492290442941</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003027577546331813</v>
+        <v>0.003027577546331812</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004332064206666418</v>
+        <v>0.004332064206666409</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005234625810686869</v>
+        <v>0.005234625810686863</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003690880473486125</v>
+        <v>0.003690880473486128</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004578702657157345</v>
+        <v>0.004578702657157344</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003063756305521807</v>
+        <v>0.003063756305521799</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006954795910281419</v>
+        <v>0.006954795910281395</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004327453318774339</v>
+        <v>0.004327453318774331</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004554723352556312</v>
+        <v>0.004554723352556308</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005687961120495843</v>
+        <v>0.005687961120495838</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005211370875233136</v>
+        <v>0.005211370875233132</v>
       </c>
       <c r="F9" t="n">
         <v>0.004554723266343613</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005195738970709725</v>
+        <v>0.005195738970709726</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006098300574730179</v>
+        <v>0.006098300574730174</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004554555237529448</v>
+        <v>0.004554555237529445</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005442242812549394</v>
+        <v>0.005442242812549391</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00429539282793405</v>
+        <v>0.003908581143685095</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007102997376715864</v>
+        <v>0.007102997376715858</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004214070108580392</v>
+        <v>0.003213115413401282</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005608942464180847</v>
+        <v>0.004156847184905985</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004381725966520351</v>
+        <v>0.003221938808213309</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006024757395119089</v>
+        <v>0.004503842104876532</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004225983470465614</v>
+        <v>0.003006604358193791</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004534042279068774</v>
+        <v>0.003229954913218172</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004345101583019134</v>
+        <v>0.003219161195152717</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004490917126256501</v>
+        <v>0.003227708714562873</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008855723879750359</v>
+        <v>0.006304679570605987</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006751568012499925</v>
+        <v>0.005137314336406864</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004288880882199176</v>
+        <v>0.003216640811789893</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004602501940363396</v>
+        <v>0.002815467118824121</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006038724672096339</v>
+        <v>0.004453556648075728</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004795340906800696</v>
+        <v>0.002878065564582597</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006454840393410673</v>
+        <v>0.005025678859507841</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004656066468757195</v>
+        <v>0.00255420946352497</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004970536218460468</v>
+        <v>0.002935202566838309</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004753516958551311</v>
+        <v>0.002864200377523772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004921177375315574</v>
+        <v>0.002919044937229363</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009392872867510785</v>
+        <v>0.008204611123757978</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007176203461396228</v>
+        <v>0.006060558153917169</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004688548540404911</v>
+        <v>0.002843697941458439</v>
       </c>
     </row>
     <row r="4">
@@ -991,28 +991,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001553806010804656</v>
+        <v>0.001553806010804658</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001698241546236003</v>
+        <v>0.001698241546236004</v>
       </c>
       <c r="D4" t="n">
         <v>0.001653470314168631</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001706103431653886</v>
+        <v>0.001706103431653887</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001706103431653886</v>
+        <v>0.001706103431653887</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001743670202355447</v>
+        <v>0.001743670202355449</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001631778057609159</v>
+        <v>0.001631778057609161</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001716436777974343</v>
+        <v>0.001716436777974344</v>
       </c>
       <c r="J4" t="n">
         <v>0.002142366861039952</v>
@@ -1021,7 +1021,7 @@
         <v>0.001697084918538974</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001598380980831515</v>
+        <v>0.001598380980831516</v>
       </c>
     </row>
     <row r="5">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002611001404922794</v>
+        <v>0.002611001404922791</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005226120171069215</v>
+        <v>0.005226120171069217</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004179621341992712</v>
+        <v>0.00417962134199271</v>
       </c>
       <c r="E5" t="n">
         <v>0.005226120764034163</v>
@@ -1046,22 +1046,22 @@
         <v>0.005226120764034163</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005742199680177147</v>
+        <v>0.005742199680177093</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004157815532748929</v>
+        <v>0.004157815532748936</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005226092647871595</v>
+        <v>0.005226092647871597</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01306158639696913</v>
+        <v>0.01306158639696915</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004759478616313905</v>
+        <v>0.0047594786163139</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003651732556633109</v>
+        <v>0.003651732556633113</v>
       </c>
     </row>
     <row r="6">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002029491688948261</v>
+        <v>0.001733620900344671</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001891965396655458</v>
+        <v>0.001891965396655454</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00213592244493487</v>
+        <v>0.002135922444934871</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001869696360679653</v>
+        <v>0.00186969636067965</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001896436158381986</v>
+        <v>0.001896436158381987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001923485091895464</v>
+        <v>0.002219355880499052</v>
       </c>
       <c r="H6" t="n">
         <v>0.002126915333651664</v>
@@ -1095,10 +1095,10 @@
         <v>0.001896251667514359</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002625673492119176</v>
+        <v>0.002343749730077664</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00187789825767429</v>
+        <v>0.001877898257674317</v>
       </c>
       <c r="L6" t="n">
         <v>0.001778389246075067</v>
@@ -1111,28 +1111,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001826075275165594</v>
+        <v>0.001826075275165595</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001988733565532899</v>
+        <v>0.0019887335655329</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001925715997788081</v>
+        <v>0.001925715997788082</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00198833647622133</v>
+        <v>0.001988336476221331</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00198833647622133</v>
+        <v>0.001988336476221331</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002015939466716384</v>
+        <v>0.002015939466716386</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001904047321970098</v>
+        <v>0.001904047321970099</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00198870604233528</v>
+        <v>0.001988706042335282</v>
       </c>
       <c r="J7" t="n">
         <v>0.002414636125400891</v>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002143181284728459</v>
+        <v>0.002143181284728461</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002771263373647289</v>
+        <v>0.002771263373650223</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002805092241416797</v>
+        <v>0.002805092241416796</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002643925961468506</v>
+        <v>0.002643925961468507</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002320378463677268</v>
+        <v>0.00232037846367727</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002798729511344918</v>
+        <v>0.00279872951134492</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002686837366598641</v>
+        <v>0.002686837366598644</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002771496086963816</v>
+        <v>0.002771496086963817</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003197517689473789</v>
+        <v>0.003197517689473788</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002277809872509879</v>
+        <v>0.00227780987250988</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00313988620353644</v>
+        <v>0.003139886203536439</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002413973445958948</v>
+        <v>0.00241397344595895</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002854211113360289</v>
+        <v>0.00285421111336029</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002791217328989484</v>
+        <v>0.002791217328989483</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003174532539662521</v>
+        <v>0.003174532539662522</v>
       </c>
       <c r="F9" t="n">
         <v>0.002854211654083649</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002881417014543774</v>
+        <v>0.002881417014543773</v>
       </c>
       <c r="H9" t="n">
         <v>0.002769524869797487</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002854183590162672</v>
+        <v>0.002854183590162673</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003280113673228282</v>
+        <v>0.00328011367322828</v>
       </c>
       <c r="K9" t="n">
         <v>0.002674001234761892</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002736127793019843</v>
+        <v>0.002736127793019842</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005339585394171729</v>
+        <v>0.003973851965676488</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004044384436271783</v>
+        <v>0.002674120978828744</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005965775985002122</v>
+        <v>0.004006807132757205</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004674161521944106</v>
+        <v>0.003298977804831883</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004674161521944106</v>
+        <v>0.003298983887389605</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005858899410801698</v>
+        <v>0.004001182430931012</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00656328543713188</v>
+        <v>0.004037780532377909</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005494082305449503</v>
+        <v>0.003982004057809714</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00778844732499122</v>
+        <v>0.005019996344401992</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006356189131810767</v>
+        <v>0.004671943737501419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006254252811520096</v>
+        <v>0.004021971559673266</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005741496396397641</v>
+        <v>0.004157128227565</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004488377458138744</v>
+        <v>0.002094228638832662</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006461745290842705</v>
+        <v>0.004391652729218086</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005099339648110968</v>
+        <v>0.003087772344788892</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005099339648110968</v>
+        <v>0.003087778427346615</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006338815091096573</v>
+        <v>0.004352058599196328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007149475405595196</v>
+        <v>0.004618853562103975</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005919186023346132</v>
+        <v>0.004215093294720152</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008381495485484197</v>
+        <v>0.006251761185833296</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006786629334205828</v>
+        <v>0.005364002720458622</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006793526424050793</v>
+        <v>0.004503290669655632</v>
       </c>
     </row>
     <row r="4">
@@ -1387,25 +1387,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001709287210665048</v>
+        <v>0.001709287210665049</v>
       </c>
       <c r="C4" t="n">
         <v>0.001837209279773378</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002081530982967574</v>
+        <v>0.002081530982967575</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001783134236381737</v>
+        <v>0.001783134236381738</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001783134236381737</v>
+        <v>0.001783134236381738</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002017250591690977</v>
+        <v>0.002017250591690979</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002436601238427528</v>
+        <v>0.002436601238427529</v>
       </c>
       <c r="I4" t="n">
         <v>0.001796492671857877</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00490663228659247</v>
+        <v>0.004906632286592478</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007977562930208109</v>
+        <v>0.007977562930208112</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01146574467186888</v>
+        <v>0.01146574467186887</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006497507367440047</v>
+        <v>0.006497507367440033</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006497507367440047</v>
+        <v>0.006497507367440033</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01058290312290457</v>
+        <v>0.01058290312290459</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01988751620674264</v>
+        <v>0.01988751620674263</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00649743476420058</v>
+        <v>0.006497434764200553</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01918952729192343</v>
+        <v>0.01918952729192341</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006847680657461592</v>
+        <v>0.006847680657461584</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01647114477080376</v>
+        <v>0.01647114477080374</v>
       </c>
     </row>
     <row r="6">
@@ -1467,28 +1467,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001889842674124523</v>
+        <v>0.002236828630786662</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002047376055194376</v>
+        <v>0.002047376055194377</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002267512171103376</v>
+        <v>0.002267514612810638</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001944582008213866</v>
+        <v>0.001944582008213865</v>
       </c>
       <c r="F6" t="n">
         <v>0.001976563699616016</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002544792011812594</v>
+        <v>0.002197806055150451</v>
       </c>
       <c r="H6" t="n">
         <v>0.00299753257720972</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002324034091979493</v>
+        <v>0.001977048135317351</v>
       </c>
       <c r="J6" t="n">
         <v>0.003000909574499834</v>
@@ -1497,7 +1497,7 @@
         <v>0.001995963644589413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0024358363307419</v>
+        <v>0.002435836330741901</v>
       </c>
     </row>
     <row r="7">
@@ -1507,22 +1507,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002044729400842339</v>
+        <v>0.00204472940084234</v>
       </c>
       <c r="C7" t="n">
         <v>0.002212121031977033</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002416949534357235</v>
+        <v>0.002416949534357237</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002131371155152779</v>
+        <v>0.002131371155152778</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002131371155152779</v>
+        <v>0.002131371155152778</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002352692781868268</v>
+        <v>0.002352692781868269</v>
       </c>
       <c r="H7" t="n">
         <v>0.002772043428604818</v>
@@ -1531,7 +1531,7 @@
         <v>0.002131934862035168</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002801171034236034</v>
+        <v>0.002801171034236033</v>
       </c>
       <c r="K7" t="n">
         <v>0.002157636147866446</v>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002424884793717278</v>
+        <v>0.002424884793717282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003154213487580691</v>
+        <v>0.003154213487580694</v>
       </c>
       <c r="D8" t="n">
         <v>0.003476153142426342</v>
@@ -1559,25 +1559,25 @@
         <v>0.002920331138726881</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002529624773026589</v>
+        <v>0.00252962477302659</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003295254198460866</v>
+        <v>0.00329525419846087</v>
       </c>
       <c r="H8" t="n">
         <v>0.003714604845198189</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003074496278627765</v>
+        <v>0.003074496278627766</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003743842978855327</v>
+        <v>0.003743842978855326</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002527344560197066</v>
+        <v>0.00252734456019707</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004118477956496288</v>
+        <v>0.004118477956496292</v>
       </c>
     </row>
     <row r="9">
@@ -1590,34 +1590,34 @@
         <v>0.002866086150852587</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003400283311104139</v>
+        <v>0.003400283311104138</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00360513562069084</v>
+        <v>0.003605135620690842</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003743455390492643</v>
+        <v>0.003743455390492645</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003320169497022937</v>
+        <v>0.003320169497022936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003540855060995373</v>
+        <v>0.003540855060995372</v>
       </c>
       <c r="H9" t="n">
         <v>0.00396020570773192</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003320097141162271</v>
+        <v>0.003320097141162272</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003989333313363133</v>
+        <v>0.003989333313363134</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003133269933703095</v>
+        <v>0.003133269933703093</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003776598700459917</v>
+        <v>0.00377659870045992</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00517851526772536</v>
+        <v>0.003933006390912772</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003842016476047975</v>
+        <v>0.002628990519324654</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005675296797283015</v>
+        <v>0.003959151016125801</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00447720097754379</v>
+        <v>0.003254971486268712</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00447720097754379</v>
+        <v>0.003254977920531529</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005549003184058151</v>
+        <v>0.003952504434101095</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005830698701002409</v>
+        <v>0.003966697589511551</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005298735605459843</v>
+        <v>0.003939355360289353</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007301463488907245</v>
+        <v>0.004965415587597253</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006100925016083929</v>
+        <v>0.004623032972083828</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005507829469702769</v>
+        <v>0.003950053203515568</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005559221470303776</v>
+        <v>0.004077730724936954</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004259072304539449</v>
+        <v>0.001996544737828882</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006130623137278908</v>
+        <v>0.004263827318428343</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004876027958809208</v>
+        <v>0.002993337874025939</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004876027958809208</v>
+        <v>0.002993344308288754</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005985359320427152</v>
+        <v>0.004216796702766927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006309807233416045</v>
+        <v>0.004323470657561182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00569754942914199</v>
+        <v>0.004122898598222111</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007823694037675842</v>
+        <v>0.006054203644954605</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006496610514382986</v>
+        <v>0.005245376467754671</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00593799353696063</v>
+        <v>0.004202272478435783</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001592634405304134</v>
+        <v>0.001592634405304136</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00170777711975056</v>
+        <v>0.001707777119750561</v>
       </c>
       <c r="D4" t="n">
         <v>0.001887949974207099</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001669084479288609</v>
+        <v>0.00166908447928861</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001669084479288609</v>
+        <v>0.00166908447928861</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001812227766537396</v>
+        <v>0.001812227766537398</v>
       </c>
       <c r="H4" t="n">
         <v>0.001980302372487147</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001660141687892772</v>
+        <v>0.001660141687892774</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002152729096298184</v>
+        <v>0.002152729096298187</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001651916247854998</v>
+        <v>0.001651916247854999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001788461814565618</v>
+        <v>0.001788461814565619</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003285928065415447</v>
+        <v>0.003285928065415449</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0058092542664124</v>
+        <v>0.005809254266412416</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008250528911283467</v>
+        <v>0.008250528911283478</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004475004965489735</v>
+        <v>0.004475004965489739</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004475004965489735</v>
+        <v>0.004475004965489739</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007132628183673125</v>
+        <v>0.007132628183673188</v>
       </c>
       <c r="H5" t="n">
         <v>0.01087885049721421</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004474948522094469</v>
+        <v>0.004474948522094476</v>
       </c>
       <c r="J5" t="n">
         <v>0.01331988012009884</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004249699200575247</v>
+        <v>0.004249699200575243</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007318461350258701</v>
+        <v>0.0073184613502587</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002078938023022593</v>
+        <v>0.002078938023022594</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001903085712435824</v>
+        <v>0.001903085712435816</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00237901257699529</v>
+        <v>0.002379012576995295</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001806927753857792</v>
+        <v>0.001806927753857791</v>
       </c>
       <c r="F6" t="n">
         <v>0.001834394048775593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001985186815161366</v>
+        <v>0.002298531384255854</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002494458424513167</v>
+        <v>0.002494458424513169</v>
       </c>
       <c r="I6" t="n">
         <v>0.00183310073651674</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002346921407732128</v>
+        <v>0.002346921407732132</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001821242089561807</v>
+        <v>0.001821242089561805</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001960849772818956</v>
+        <v>0.00196084977281896</v>
       </c>
     </row>
     <row r="7">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001891688861511376</v>
+        <v>0.001891688861511378</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002036353490127606</v>
+        <v>0.002036353490127607</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00218698196620802</v>
+        <v>0.002186981966208021</v>
       </c>
       <c r="E7" t="n">
         <v>0.001958809702250621</v>
@@ -1918,22 +1918,22 @@
         <v>0.001958809702250621</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002111282222744637</v>
+        <v>0.002111282222744639</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002279356828694388</v>
+        <v>0.002279356828694387</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001959196144100013</v>
+        <v>0.001959196144100015</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002451783552505425</v>
+        <v>0.002451783552505429</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001950970704062238</v>
+        <v>0.00195097070406224</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00208751627077286</v>
+        <v>0.002087516270772859</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00224032069955033</v>
+        <v>0.002240320699550331</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002894011988520268</v>
+        <v>0.00289401198851608</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003150570385465075</v>
+        <v>0.003150570385465079</v>
       </c>
       <c r="E8" t="n">
         <v>0.002677642208438427</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002323778368596612</v>
+        <v>0.002323778368596614</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002969236791676201</v>
+        <v>0.002969236791676203</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003137311397627264</v>
+        <v>0.00313731139762727</v>
       </c>
       <c r="I8" t="n">
         <v>0.002817150713031578</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003309838217127063</v>
+        <v>0.003309838217127064</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002290141610968942</v>
+        <v>0.002290141610968945</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003477501020217435</v>
+        <v>0.003477501020217436</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00253348819889909</v>
+        <v>0.002533488198899092</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002980914136632269</v>
+        <v>0.00298091413663227</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003131565258411745</v>
+        <v>0.003131565258411749</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003253193356066052</v>
+        <v>0.003253193356066054</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002903813095484965</v>
+        <v>0.002903813095484964</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003055842869249301</v>
+        <v>0.003055842869249305</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003223917475199051</v>
+        <v>0.003223917475199053</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002903756790604677</v>
+        <v>0.002903756790604681</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003396344199010088</v>
+        <v>0.003396344199010093</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002720110335364269</v>
+        <v>0.002720110335364271</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003032076917277521</v>
+        <v>0.003032076917277527</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005051642252046649</v>
+        <v>0.003878919696617401</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003705169264145184</v>
+        <v>0.002585542902107381</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005400572252123092</v>
+        <v>0.003897283189490624</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004277660685849304</v>
+        <v>0.003204953328392272</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004277660685849304</v>
+        <v>0.003204960496487391</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005302759357478924</v>
+        <v>0.003892135491117558</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005400086586428629</v>
+        <v>0.003896583660676399</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005089064617486829</v>
+        <v>0.00388091137930437</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006662766548165421</v>
+        <v>0.004793106730144221</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005947319268945903</v>
+        <v>0.004578610313977802</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005182718070867678</v>
+        <v>0.003885517177797761</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005441203339445535</v>
+        <v>0.004000104925611028</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004127479665823787</v>
+        <v>0.001929410121595668</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005842545120165205</v>
+        <v>0.004130837222292206</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004672906292899274</v>
+        <v>0.002898610078293422</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004672906292899274</v>
+        <v>0.002898617246388539</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005730040029444331</v>
+        <v>0.004094364224216015</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00584240263751646</v>
+        <v>0.004131058962773919</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005484306418843492</v>
+        <v>0.004014260227365027</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007134557419326718</v>
+        <v>0.005667339892711661</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006345711533225962</v>
+        <v>0.005171959901180745</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005591961139221301</v>
+        <v>0.004049549522358556</v>
       </c>
     </row>
     <row r="4">
@@ -2188,28 +2188,28 @@
         <v>0.001721259204499518</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001537172090157985</v>
+        <v>0.001537172090157986</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001537172090157985</v>
+        <v>0.001537172090157986</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001662577567557157</v>
+        <v>0.001662577567557158</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001720984371653227</v>
+        <v>0.001720984371653225</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001532857816037389</v>
+        <v>0.001532857816037388</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00183926649930555</v>
+        <v>0.001839266499305549</v>
       </c>
       <c r="K4" t="n">
         <v>0.001548785241859587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001591826947375824</v>
+        <v>0.001591826947375823</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002308071836919458</v>
+        <v>0.00230807183691946</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004584478524651835</v>
+        <v>0.004584478524651836</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005806282107505876</v>
+        <v>0.005806282107505877</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002671742429845711</v>
+        <v>0.002671742429845709</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002671742429845711</v>
+        <v>0.002671742429845709</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00491539047403131</v>
+        <v>0.004915390474031314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006356228165423942</v>
+        <v>0.006356228165423941</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002671692000648637</v>
+        <v>0.002671692000648638</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00813393571447844</v>
+        <v>0.008133935714478435</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002880482578419027</v>
+        <v>0.002880482578419021</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003932391042510306</v>
+        <v>0.003932391042510305</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001682211492154171</v>
+        <v>0.00168221149215417</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001807553890898702</v>
+        <v>0.001807553890898701</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001891288828855002</v>
+        <v>0.001891286279119473</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001674725403697779</v>
+        <v>0.001674725403697776</v>
       </c>
       <c r="F6" t="n">
         <v>0.001701946488497318</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002132449028497563</v>
+        <v>0.002132449028497562</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002215758453919353</v>
+        <v>0.002215758453919352</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002002729276977794</v>
+        <v>0.002002729276977793</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002313247600247204</v>
+        <v>0.002313247600247202</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001715676555735384</v>
+        <v>0.00171567655573538</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001758637369621574</v>
+        <v>0.001758637369621565</v>
       </c>
     </row>
     <row r="7">
@@ -2305,7 +2305,7 @@
         <v>0.001929304359834755</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002006313588721409</v>
+        <v>0.002006313588721408</v>
       </c>
       <c r="E7" t="n">
         <v>0.001817491421759518</v>
@@ -2317,19 +2317,19 @@
         <v>0.001947654420572927</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002006061224668995</v>
+        <v>0.002006061224668996</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001817934669053157</v>
+        <v>0.001817934669053156</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002124343352321319</v>
+        <v>0.00212434335232132</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001833862094875357</v>
+        <v>0.001833862094875356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001876903800391592</v>
+        <v>0.001876903800391591</v>
       </c>
     </row>
     <row r="8">
@@ -2342,34 +2342,34 @@
         <v>0.002138016318473502</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00275916748434054</v>
+        <v>0.002759167484344688</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002938381357943996</v>
+        <v>0.002938381357943995</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002513566555547235</v>
+        <v>0.002513566555547232</v>
       </c>
       <c r="F8" t="n">
         <v>0.002172375686873148</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002777865536150715</v>
+        <v>0.002777865536150714</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002836272340248062</v>
+        <v>0.002836272340248063</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002648145784630946</v>
+        <v>0.002648145784630948</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002954650983642977</v>
+        <v>0.002954650983642975</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002163843895431369</v>
+        <v>0.002163843895431367</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003220116986473946</v>
+        <v>0.003220116986473944</v>
       </c>
     </row>
     <row r="9">
@@ -2382,7 +2382,7 @@
         <v>0.002333530872163733</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002731749605496163</v>
+        <v>0.002731749605496162</v>
       </c>
       <c r="D9" t="n">
         <v>0.002808781476213776</v>
@@ -2394,19 +2394,19 @@
         <v>0.002620430244923306</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002750099666234334</v>
+        <v>0.002750099666234336</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002808506470330403</v>
+        <v>0.002808506470330405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002620379914714567</v>
+        <v>0.002620379914714565</v>
       </c>
       <c r="J9" t="n">
         <v>0.002926788597982729</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002299066137643465</v>
+        <v>0.00247483194746884</v>
       </c>
       <c r="L9" t="n">
         <v>0.002679349046053001</v>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005067808253407154</v>
+        <v>0.00388477223881617</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003487734856443119</v>
+        <v>0.002597797286865575</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005473895547739843</v>
+        <v>0.003906143806562571</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004410902721960379</v>
+        <v>0.003242167531893187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004410902721960379</v>
+        <v>0.003242173468963273</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00549345851304853</v>
+        <v>0.003907173366571586</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006154238381557877</v>
+        <v>0.003941538354650673</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005190003208923435</v>
+        <v>0.003891224877504581</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007634459964123251</v>
+        <v>0.004968884884590336</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006168213221245189</v>
+        <v>0.004616710020517378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006024080258895032</v>
+        <v>0.003935239570011658</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005434723062172356</v>
+        <v>0.003988630925540783</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003848622446546617</v>
+        <v>0.001854356659546943</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005901807571384547</v>
+        <v>0.004140771348610426</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004796234195019343</v>
+        <v>0.002963314582462527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004796234195019343</v>
+        <v>0.002963320519532611</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005924309033945588</v>
+        <v>0.004148406621546686</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006684800755820486</v>
+        <v>0.004398260441749575</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005575317131551393</v>
+        <v>0.004034563495252821</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008204084866213488</v>
+        <v>0.006168118312170828</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006570574362204876</v>
+        <v>0.005264737421660118</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006534596437063732</v>
+        <v>0.00435018413362147</v>
       </c>
     </row>
     <row r="4">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001555423204308675</v>
+        <v>0.001555423204308676</v>
       </c>
       <c r="C4" t="n">
         <v>0.001490980966779914</v>
@@ -2590,22 +2590,22 @@
         <v>0.001611414240647117</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001807733726191595</v>
+        <v>0.001807733726191596</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002201144642833982</v>
+        <v>0.002201144642833983</v>
       </c>
       <c r="I4" t="n">
         <v>0.001623606680318559</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002357665716912724</v>
+        <v>0.002357665716912723</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001695705092279123</v>
+        <v>0.001695705092279124</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002123818258815833</v>
+        <v>0.002123818258815834</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002699727465726751</v>
+        <v>0.00269972746572675</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002281132196377136</v>
+        <v>0.002281132196377135</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006980846261905361</v>
+        <v>0.006980846261905354</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003986234343608123</v>
+        <v>0.003986234343608109</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003986234343608123</v>
+        <v>0.003986234343608109</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007353795189700402</v>
+        <v>0.007353795189700415</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01583195037596337</v>
+        <v>0.01583195037596338</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003986170250522634</v>
+        <v>0.003986170250522622</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01779958681545</v>
+        <v>0.01779958681545001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005186792900641754</v>
+        <v>0.005186792900641763</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01452116692302935</v>
+        <v>0.01452116692302934</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001723478586130507</v>
+        <v>0.001723478586130508</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001685510151347403</v>
+        <v>0.0016855101513474</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001967122505908479</v>
+        <v>0.001967119978147084</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001760838957142157</v>
+        <v>0.001760838957142152</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001791205711363294</v>
+        <v>0.001791205711363293</v>
       </c>
       <c r="G6" t="n">
         <v>0.001975789108013428</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002728310354171882</v>
+        <v>0.002728310354171884</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001791662062140391</v>
+        <v>0.00211911921112839</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002859940549395155</v>
+        <v>0.002547758630525444</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001859132807148313</v>
+        <v>0.001859132807148314</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002294289245151661</v>
+        <v>0.002294289245151662</v>
       </c>
     </row>
     <row r="7">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001870628526232759</v>
+        <v>0.00187062852623276</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001847635289780645</v>
+        <v>0.001847635289780647</v>
       </c>
       <c r="D7" t="n">
         <v>0.002112006987324889</v>
@@ -2713,7 +2713,7 @@
         <v>0.002122939048115679</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002516349964758062</v>
+        <v>0.002516349964758065</v>
       </c>
       <c r="I7" t="n">
         <v>0.001938812002242643</v>
@@ -2722,10 +2722,10 @@
         <v>0.002672871038836807</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002010910414203205</v>
+        <v>0.002010910414203207</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002439023580739916</v>
+        <v>0.002439023580739918</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002238106495838757</v>
+        <v>0.002238106495838759</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002752014128166648</v>
+        <v>0.002752014128170879</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003128029554051737</v>
+        <v>0.003128029554051741</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002696371844459226</v>
+        <v>0.002696371844459229</v>
       </c>
       <c r="F8" t="n">
         <v>0.002323160856727216</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003027558583980036</v>
+        <v>0.003027558583980038</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003420969500623073</v>
+        <v>0.003420969500623075</v>
       </c>
       <c r="I8" t="n">
         <v>0.002843431538106999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003577596137541254</v>
+        <v>0.003577596137541257</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00236841070353267</v>
+        <v>0.002368410703532671</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003904732396782181</v>
+        <v>0.003904732396782184</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002622763279618702</v>
+        <v>0.002622763279618701</v>
       </c>
       <c r="C9" t="n">
         <v>0.002939941452565026</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003204336532453009</v>
+        <v>0.003204336532453008</v>
       </c>
       <c r="E9" t="n">
         <v>0.003423732750816482</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003031182065746939</v>
+        <v>0.003031182065746936</v>
       </c>
       <c r="G9" t="n">
         <v>0.00321524521090006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003608656127542445</v>
+        <v>0.003608656127542448</v>
       </c>
       <c r="I9" t="n">
         <v>0.003031118165027025</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003765177201621187</v>
+        <v>0.003765177201621186</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002674880012173256</v>
+        <v>0.002906119991337948</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003531329743524298</v>
+        <v>0.0035313297435243</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004943304675346901</v>
+        <v>0.003800371326374675</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003447380104733104</v>
+        <v>0.002554606698631629</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004981275135256888</v>
+        <v>0.00380236963626433</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004281044914659889</v>
+        <v>0.003191721466030063</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004281044914659889</v>
+        <v>0.003191727710609792</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005021373487761047</v>
+        <v>0.003804479932914878</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005023615075437527</v>
+        <v>0.003803922869449229</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005016188901730174</v>
+        <v>0.003804231268819281</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006679212059289709</v>
+        <v>0.004872271414066047</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005879657737884042</v>
+        <v>0.004550964895603637</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005084756541674727</v>
+        <v>0.003807687865154761</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005299879264447156</v>
+        <v>0.003873742144591403</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003803579681274234</v>
+        <v>0.001817976092658979</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005343553158900715</v>
+        <v>0.003887927424287714</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004648636278079666</v>
+        <v>0.002890293432214413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004648636278079666</v>
+        <v>0.002890299676794141</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005389674570629202</v>
+        <v>0.003903039008727766</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005392675530807064</v>
+        <v>0.003903504111845892</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005383914007095804</v>
+        <v>0.003901212580920218</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007107643419976724</v>
+        <v>0.005781345813130966</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006241779916835507</v>
+        <v>0.005123330268315313</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005462560132382503</v>
+        <v>0.003927200627035723</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001487530489179724</v>
+        <v>0.001487530489179725</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001457110225165136</v>
+        <v>0.001457110225165137</v>
       </c>
       <c r="D4" t="n">
         <v>0.001510102318651341</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001538574132327059</v>
+        <v>0.00153857413232706</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001538574132327059</v>
+        <v>0.00153857413232706</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001533385637218465</v>
+        <v>0.001533385637218464</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001535306770415968</v>
+        <v>0.001535306770415969</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001527545387790316</v>
+        <v>0.001527545387790315</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001771909801723108</v>
+        <v>0.001771909801723109</v>
       </c>
       <c r="K4" t="n">
         <v>0.001509485549966913</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001571639897977546</v>
+        <v>0.001571639897977547</v>
       </c>
     </row>
     <row r="5">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002093638659994068</v>
+        <v>0.002093638659994069</v>
       </c>
       <c r="C5" t="n">
         <v>0.002080911968230383</v>
@@ -3026,22 +3026,22 @@
         <v>0.002820704069168872</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002900182786757334</v>
+        <v>0.002900182786757305</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003069551265006355</v>
+        <v>0.003069551265006349</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002820681396637772</v>
+        <v>0.002820681396637777</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007179963906468926</v>
+        <v>0.007179963906468928</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002446782857159649</v>
+        <v>0.002446782857159646</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003811145032594979</v>
+        <v>0.003811145032594981</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001649149768284753</v>
+        <v>0.001649149768284754</v>
       </c>
       <c r="C6" t="n">
         <v>0.001640695072765642</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0016711926331697</v>
+        <v>0.001965275338267437</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001667066962925235</v>
+        <v>0.001667066962925234</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00169066531300579</v>
+        <v>0.001690665313005791</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001985523644251762</v>
+        <v>0.001695004916323492</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0020119406446484</v>
+        <v>0.002011940644648401</v>
       </c>
       <c r="I6" t="n">
         <v>0.001979683394823612</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001952166742411207</v>
+        <v>0.002227460487843026</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001670043535133098</v>
+        <v>0.001670043535133097</v>
       </c>
       <c r="L6" t="n">
         <v>0.001732048186328976</v>
@@ -3097,7 +3097,7 @@
         <v>0.001757286661055623</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001780484486312935</v>
+        <v>0.001780484486312934</v>
       </c>
       <c r="E7" t="n">
         <v>0.001797746395134268</v>
@@ -3106,7 +3106,7 @@
         <v>0.001797746395134268</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001803789784872021</v>
+        <v>0.001803789784872022</v>
       </c>
       <c r="H7" t="n">
         <v>0.001805710918069525</v>
@@ -3118,10 +3118,10 @@
         <v>0.002042313949376664</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001779889697620469</v>
+        <v>0.001779889697620468</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001842044045631102</v>
+        <v>0.001842044045631103</v>
       </c>
     </row>
     <row r="8">
@@ -3131,19 +3131,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002087133383054811</v>
+        <v>0.002087133383054812</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002559263419586444</v>
+        <v>0.002559263419582483</v>
       </c>
       <c r="D8" t="n">
         <v>0.00268063330574466</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002470627482603881</v>
+        <v>0.002470627482603878</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002142038749601626</v>
+        <v>0.002142038749601625</v>
       </c>
       <c r="G8" t="n">
         <v>0.002605863018846243</v>
@@ -3152,16 +3152,16 @@
         <v>0.002607784152044738</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002600022769418093</v>
+        <v>0.002600022769418095</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002844480115912829</v>
+        <v>0.002844480115912831</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002100304557538949</v>
+        <v>0.002100304557538948</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003138074222401901</v>
+        <v>0.0031380742224019</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002328943800516338</v>
+        <v>0.002328943800516337</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002600989859642726</v>
+        <v>0.002600989859642723</v>
       </c>
       <c r="D9" t="n">
         <v>0.002624209831392747</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002956358636367376</v>
+        <v>0.002956358636367375</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002641675362610412</v>
+        <v>0.002641675362610413</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002647492983459124</v>
+        <v>0.002647492983459125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002649414116656628</v>
+        <v>0.002649414116656626</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002641652734030975</v>
+        <v>0.002641652734030976</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002886017147963769</v>
+        <v>0.002886017147963768</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002280222387396912</v>
+        <v>0.002465592971461612</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002685747244218205</v>
+        <v>0.002685747244218206</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00484929747374272</v>
+        <v>0.003712218783962811</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003436117462972618</v>
+        <v>0.002531064251153036</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004879278794945534</v>
+        <v>0.003713796641350014</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00423123584321565</v>
+        <v>0.00316353265430479</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00423123584321565</v>
+        <v>0.003163539747748229</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004876461940096509</v>
+        <v>0.003713648395874033</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004884851221220349</v>
+        <v>0.003713439172400445</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00489245420218542</v>
+        <v>0.003714514353664385</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006153565144867227</v>
+        <v>0.004718123281592114</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005830099027621434</v>
+        <v>0.004527868069882952</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004867900415207412</v>
+        <v>0.003713027612535706</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005228229585253762</v>
+        <v>0.003753589979898695</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003815527102984975</v>
+        <v>0.001806020418842005</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005262714315248975</v>
+        <v>0.003764784473114131</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004616719807170059</v>
+        <v>0.002860562066232744</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004616719807170059</v>
+        <v>0.002860569159676184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005259474348662873</v>
+        <v>0.003763778451391189</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005269500203182576</v>
+        <v>0.003766475814030985</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005278126660733376</v>
+        <v>0.003769915647559995</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00654785584710986</v>
+        <v>0.005443577764933072</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006209173687870597</v>
+        <v>0.005100203396731878</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005249610738655872</v>
+        <v>0.003760597406616662</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001471385225896203</v>
+        <v>0.001471385225896208</v>
       </c>
       <c r="C4" t="n">
         <v>0.001448308103341556</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001489207850934929</v>
+        <v>0.001489207850934933</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001500854966145969</v>
+        <v>0.00150085496614597</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001500854966145969</v>
+        <v>0.00150085496614597</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001487082534356488</v>
+        <v>0.001487082534356548</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001492553403606237</v>
+        <v>0.001492553403606234</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001494414335824881</v>
+        <v>0.001494414335824872</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001532168160857466</v>
+        <v>0.00153216816085747</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001471949374705768</v>
+        <v>0.001471949374705769</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001482479934385007</v>
+        <v>0.001482479934385005</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002012117262614625</v>
+        <v>0.002012117262614641</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002057238311709025</v>
+        <v>0.002057238311709026</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002292746424768623</v>
+        <v>0.002292746424768624</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002437822397987861</v>
+        <v>0.00243782239798787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002437822397987861</v>
+        <v>0.00243782239798787</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002289634044775417</v>
+        <v>0.002289634044775416</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002471681859645026</v>
+        <v>0.002471681859645029</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002437803550207772</v>
+        <v>0.002437803550207782</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003105362938392858</v>
+        <v>0.003105362938392853</v>
       </c>
       <c r="K5" t="n">
         <v>0.002001850376091849</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002296765308719515</v>
+        <v>0.002296765308719519</v>
       </c>
     </row>
     <row r="6">
@@ -3453,31 +3453,31 @@
         <v>0.001631935302340416</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001651558431359638</v>
+        <v>0.001651558431359635</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001635728220177935</v>
+        <v>0.001635728220177938</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001659533639465274</v>
+        <v>0.001659533639465276</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001936475191931406</v>
+        <v>0.001936475191931404</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001964246259417906</v>
+        <v>0.001655186381966195</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001658459961255708</v>
+        <v>0.001943806993399814</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001984765931766417</v>
+        <v>0.001714003983671331</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001636242800994254</v>
+        <v>0.001636242800994231</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001644558735944673</v>
+        <v>0.001644558735944672</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001729778038168974</v>
+        <v>0.001729778038168975</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001732453077288336</v>
+        <v>0.001732453077288337</v>
       </c>
       <c r="D7" t="n">
         <v>0.001747578566956739</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001752560755422213</v>
+        <v>0.001752560755422214</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001752560755422213</v>
+        <v>0.001752560755422214</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001745475346629249</v>
+        <v>0.001745475346629251</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001750946215879008</v>
+        <v>0.001750946215879007</v>
       </c>
       <c r="I7" t="n">
         <v>0.001752807148097656</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001790560973130237</v>
+        <v>0.001790560973130238</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00173034218697854</v>
+        <v>0.001730342186978537</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001740872746657779</v>
+        <v>0.001740872746657777</v>
       </c>
     </row>
     <row r="8">
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002051239866855732</v>
+        <v>0.00205123986685573</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002511149257687024</v>
+        <v>0.002511149257690949</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002621272627666591</v>
+        <v>0.002621272627666588</v>
       </c>
       <c r="E8" t="n">
         <v>0.002406444768033868</v>
@@ -3542,22 +3542,22 @@
         <v>0.002088640739549644</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002524308406803257</v>
+        <v>0.002524308406803258</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002529779276053989</v>
+        <v>0.002529779276053991</v>
       </c>
       <c r="I8" t="n">
         <v>0.002531640208271665</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002569483919037317</v>
+        <v>0.002569483919037315</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002043308110306247</v>
+        <v>0.002043308110306246</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002997468302102277</v>
+        <v>0.002997468302102275</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002231047783769927</v>
+        <v>0.002231047783769928</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002482521918471875</v>
+        <v>0.002482521918471877</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002497669656479373</v>
+        <v>0.00249766965647937</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002790003803433977</v>
+        <v>0.002790003803433979</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00250289479544442</v>
+        <v>0.002502894795444421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002495544187812786</v>
+        <v>0.002495544187812788</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002501015057062545</v>
+        <v>0.00250101505706255</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002502875989281193</v>
+        <v>0.002502875989281195</v>
       </c>
       <c r="J9" t="n">
         <v>0.002540629814313777</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002330407357997087</v>
+        <v>0.002336255919039756</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002490941587841316</v>
+        <v>0.002490941587841318</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004953991786028377</v>
+        <v>0.003793649035960776</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003462714554770451</v>
+        <v>0.002571612364443152</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005032975828326631</v>
+        <v>0.003797805809232013</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004340707496837075</v>
+        <v>0.003211146924216358</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004340707496837076</v>
+        <v>0.00321115270958731</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005142469360124435</v>
+        <v>0.003803568236338868</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005861064857460775</v>
+        <v>0.003841087274652664</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005045641214855366</v>
+        <v>0.00379849572706202</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006589813774277904</v>
+        <v>0.004876533927434649</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005987269709662388</v>
+        <v>0.004572243914477503</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005721075825400464</v>
+        <v>0.003834245859634751</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005313708490555453</v>
+        <v>0.003857770862439827</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003818178014885213</v>
+        <v>0.001833891866545759</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005404556500693513</v>
+        <v>0.003887314731498449</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004714257283806416</v>
+        <v>0.002922876267857176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004714257283806407</v>
+        <v>0.002922882053228127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00553049674377777</v>
+        <v>0.003928513922327155</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006357468312132637</v>
+        <v>0.004199791447136756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005419284989142759</v>
+        <v>0.003892263763805825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007003222950783233</v>
+        <v>0.005748581279416384</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006362681354346144</v>
+        <v>0.00517302604749296</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006195970776046743</v>
+        <v>0.004147888151862121</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00152395866677483</v>
+        <v>0.001523958666774837</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001468483013353355</v>
+        <v>0.001468483013353356</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001570911333083362</v>
+        <v>0.001570911333083375</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001563757828946689</v>
+        <v>0.00156375782894669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001563757828946689</v>
+        <v>0.00156375782894669</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001635354680345674</v>
+        <v>0.001635354680345679</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002063045297203376</v>
+        <v>0.002063045297203385</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001574504595944638</v>
+        <v>0.001574504595944639</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001736451211774476</v>
+        <v>0.00173645121177448</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001586072733321432</v>
+        <v>0.001586072733321436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001979867172881926</v>
+        <v>0.001979867172881931</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002451194934929071</v>
+        <v>0.002451194934929075</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002159169908519366</v>
+        <v>0.002159169908519367</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003257902776659015</v>
+        <v>0.003257902776659021</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00341252991317384</v>
+        <v>0.003412529913173824</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00341252991317384</v>
+        <v>0.003412529913173824</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00450868550125945</v>
+        <v>0.004508685501259407</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0134098361652976</v>
+        <v>0.01340983616529762</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003412494096210178</v>
+        <v>0.00341249409621017</v>
       </c>
       <c r="J5" t="n">
         <v>0.006461926965705773</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003537615433906894</v>
+        <v>0.003537615433906903</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01193266723838754</v>
+        <v>0.01193266723838756</v>
       </c>
     </row>
     <row r="6">
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001683568973699547</v>
+        <v>0.001683568973699556</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001656489603923501</v>
+        <v>0.0016564896039235</v>
       </c>
       <c r="D6" t="n">
         <v>0.001729418916136539</v>
@@ -3858,22 +3858,22 @@
         <v>0.001733850647762159</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002111012162256156</v>
+        <v>0.001794964987270399</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002569377087372191</v>
+        <v>0.002569377087372194</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002050162077855116</v>
+        <v>0.001734114902869361</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002217946876918243</v>
+        <v>0.001913993149085396</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001741598236487612</v>
+        <v>0.001741598236487608</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002141233916944382</v>
+        <v>0.002141233916944386</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001822381480237317</v>
+        <v>0.001822381480237325</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001806463212650738</v>
+        <v>0.001806463212650739</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001869311016179761</v>
+        <v>0.00186931101617976</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001872647670443149</v>
+        <v>0.00187264767044315</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001872647670443149</v>
+        <v>0.00187264767044315</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00193377749380816</v>
+        <v>0.001933777493808168</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002361468110665858</v>
+        <v>0.002361468110665869</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001872927409407124</v>
+        <v>0.001872927409407125</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002034874025236966</v>
+        <v>0.002034874025236976</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001884495546783918</v>
+        <v>0.001884495546783919</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002278289986344414</v>
+        <v>0.002278289986344416</v>
       </c>
     </row>
     <row r="8">
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002178460349556604</v>
+        <v>0.002178460349556609</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002678226243076617</v>
+        <v>0.002678226243072463</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002848235605041953</v>
+        <v>0.002848235605041961</v>
       </c>
       <c r="E8" t="n">
         <v>0.002603657207289264</v>
@@ -3938,22 +3938,22 @@
         <v>0.00224521950162777</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002805712766612896</v>
+        <v>0.002805712766612897</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003233403383471242</v>
+        <v>0.003233403383471244</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002744862682211857</v>
+        <v>0.002744862682211858</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002906910677739594</v>
+        <v>0.002906910677739612</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002230992118652775</v>
+        <v>0.002230992118652772</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003689080406976439</v>
+        <v>0.003689080406976445</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002523432839521401</v>
+        <v>0.002523432839521408</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002827446707951712</v>
+        <v>0.002827446707951711</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002890317733827256</v>
+        <v>0.002890317733827264</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003263141488729088</v>
+        <v>0.003263141488729086</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002893946547753804</v>
+        <v>0.002893946547753803</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002954760989109134</v>
+        <v>0.00295476098910914</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003382451605966835</v>
+        <v>0.003382451605966843</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002893910904708098</v>
+        <v>0.002893910904708096</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003055857520537937</v>
+        <v>0.003055857520537943</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002720109144692865</v>
+        <v>0.002720109144692876</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003299273481645387</v>
+        <v>0.003299273481645391</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004726070270741785</v>
+        <v>0.003604292248405332</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003440964527070963</v>
+        <v>0.002535613015620631</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004750055622727635</v>
+        <v>0.003605554549841601</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004254526807034784</v>
+        <v>0.003166938144594592</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004254526807034784</v>
+        <v>0.003166944371619587</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004750978006948376</v>
+        <v>0.003605603093091138</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00475605653190702</v>
+        <v>0.003605219115434254</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004782856583677697</v>
+        <v>0.003607305174218155</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006277659741393635</v>
+        <v>0.004825009304954689</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005827844647039356</v>
+        <v>0.004510654921057978</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004740826527434698</v>
+        <v>0.003604895243444614</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005078877422461081</v>
+        <v>0.003573528991357908</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003793109574023499</v>
+        <v>0.001809448641476429</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005106465545795504</v>
+        <v>0.003582468669849597</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004615933238198686</v>
+        <v>0.00286819483768694</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004615933238198686</v>
+        <v>0.002868201064711934</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005107526478720674</v>
+        <v>0.003582868522875139</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005113764263532342</v>
+        <v>0.003584331465390342</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005144424664773487</v>
+        <v>0.003594960732264554</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006644101488878691</v>
+        <v>0.00561479043774327</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00618271700034735</v>
+        <v>0.005073561522335902</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005095834965164574</v>
+        <v>0.00357910181041546</v>
       </c>
     </row>
     <row r="4">
@@ -4159,34 +4159,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00148083443048259</v>
+        <v>0.001480834430482589</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001450028350057123</v>
+        <v>0.001450028350057122</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001495092705892599</v>
+        <v>0.001495092705892598</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001522980630952575</v>
+        <v>0.001522980630952574</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001522980630952575</v>
+        <v>0.001522980630952574</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001495107470439884</v>
+        <v>0.001495107470439881</v>
       </c>
       <c r="H4" t="n">
         <v>0.001498694039245787</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001511414328366272</v>
+        <v>0.001511414328366271</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001534794508079338</v>
+        <v>0.001534794508079337</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001489007642207636</v>
+        <v>0.001489007642207634</v>
       </c>
       <c r="L4" t="n">
         <v>0.001489643218977895</v>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002119386768174829</v>
+        <v>0.002119386768174828</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002085925494316407</v>
+        <v>0.002085925494316406</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002335587667729753</v>
+        <v>0.00233558766772975</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002680734616665261</v>
+        <v>0.00268073461666526</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002680734616665261</v>
+        <v>0.00268073461666526</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002372423896332128</v>
+        <v>0.002372423896332077</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002524462096338811</v>
+        <v>0.00252446209633881</v>
       </c>
       <c r="I5" t="n">
         <v>0.002680716732977681</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003092045341344573</v>
+        <v>0.003092045341344574</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002235527118720585</v>
+        <v>0.002235527118720583</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002370451345964513</v>
+        <v>0.002370451345964512</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001641300525885986</v>
+        <v>0.001928046807266453</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001632484009014569</v>
+        <v>0.001632484009014568</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001655465933991987</v>
+        <v>0.00165546849472487</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001650553593483509</v>
+        <v>0.001650553593483508</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001673396009723703</v>
+        <v>0.001673396009723702</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00165557356584328</v>
+        <v>0.001655573565843278</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001969720062639058</v>
+        <v>0.001969720062639056</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001958626705150136</v>
+        <v>0.001958626705150135</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001985010187531651</v>
+        <v>0.001712383475916142</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001648663644512052</v>
+        <v>0.00164866364451205</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00164849270197578</v>
+        <v>0.001648492701975779</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0017401312154932</v>
+        <v>0.001740131215493199</v>
       </c>
       <c r="C7" t="n">
         <v>0.001738329399393715</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001754367492137428</v>
+        <v>0.001754367492137427</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001770592847719367</v>
+        <v>0.001770592847719366</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001770592847719368</v>
+        <v>0.001770592847719366</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001754404255450496</v>
+        <v>0.001754404255450493</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001757990824256399</v>
+        <v>0.001757990824256398</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001770711113376884</v>
+        <v>0.001770711113376882</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00179409129308995</v>
+        <v>0.001794091293089948</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001748304427218246</v>
+        <v>0.001748304427218244</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001748940003988506</v>
+        <v>0.001748940003988504</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002060941811806798</v>
+        <v>0.002060941811806796</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002517219792058078</v>
+        <v>0.002517219792058075</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002628282125334457</v>
+        <v>0.00262828212533445</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00242433157884209</v>
+        <v>0.002424331578842086</v>
       </c>
       <c r="F8" t="n">
         <v>0.002105992350620966</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002533308241400225</v>
+        <v>0.00253330824140022</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002536894810207127</v>
+        <v>0.002536894810207121</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002549615099326612</v>
+        <v>0.00254961509932661</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002573085306696275</v>
+        <v>0.00257308530669627</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002060605703714614</v>
+        <v>0.002060605703714613</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003006360839780036</v>
+        <v>0.00300636083978003</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002304731704858298</v>
+        <v>0.002304731704858295</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00256973784375835</v>
+        <v>0.002569737843758347</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002585798090161474</v>
+        <v>0.002585798090161471</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002910028259623853</v>
+        <v>0.002910028259623849</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002602137405706872</v>
+        <v>0.002602137405706867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002585812699815129</v>
+        <v>0.002585812699815125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002589399268621036</v>
+        <v>0.002589399268621032</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002602119557741521</v>
+        <v>0.002602119557741516</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002625499737454586</v>
+        <v>0.002625499737454583</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002425123359768103</v>
+        <v>0.002243753991041859</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002580348448353145</v>
+        <v>0.002580348448353139</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004717537734407278</v>
+        <v>0.003572599294722326</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003430084195289831</v>
+        <v>0.002498633121802023</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004737709769026977</v>
+        <v>0.003573660908839474</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004214554884374767</v>
+        <v>0.003127854356962893</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004214554884374767</v>
+        <v>0.003127861460263579</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004734487290613027</v>
+        <v>0.003573491316200918</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004744117339110702</v>
+        <v>0.003573359799814643</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004750238105053214</v>
+        <v>0.003574344565317019</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006115403710903917</v>
+        <v>0.004679340221253355</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005821978044494504</v>
+        <v>0.004484019860717253</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004731752104254246</v>
+        <v>0.003573181166430936</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005089431292745687</v>
+        <v>0.003570566392289526</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003801984832671861</v>
+        <v>0.001798977781294761</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005112633311182722</v>
+        <v>0.003578081774777173</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004591429670424241</v>
+        <v>0.002846097776068274</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004591429670424241</v>
+        <v>0.00284610487936895</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005108926793472289</v>
+        <v>0.003576919548484523</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005120358699719267</v>
+        <v>0.003580082641936719</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005127299983745973</v>
+        <v>0.003582968922224342</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006498239065118843</v>
+        <v>0.005418507564103106</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006195389936254146</v>
+        <v>0.005077903714093961</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005105764331151097</v>
+        <v>0.003575924334233258</v>
       </c>
     </row>
     <row r="4">
@@ -4555,34 +4555,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001467063585606025</v>
+        <v>0.001467063585606024</v>
       </c>
       <c r="C4" t="n">
         <v>0.00144255332762119</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001479055005425822</v>
+        <v>0.001479055005425821</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001490644792659001</v>
+        <v>0.001490644792658999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001490644792659001</v>
+        <v>0.001490644792658999</v>
       </c>
       <c r="G4" t="n">
         <v>0.001476716942090027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001482896486003025</v>
+        <v>0.001482896486003024</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001484065096770635</v>
+        <v>0.001484065096770634</v>
       </c>
       <c r="J4" t="n">
         <v>0.001510366677585263</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001473072519837377</v>
+        <v>0.001473072519837376</v>
       </c>
       <c r="L4" t="n">
         <v>0.001475547537605581</v>
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002036372123898864</v>
+        <v>0.002036372123898862</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002048598125517003</v>
+        <v>0.002048598125517002</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002216635791255768</v>
+        <v>0.002216635791255764</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00235459466678166</v>
+        <v>0.002354594666781667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00235459466678166</v>
+        <v>0.002354594666781667</v>
       </c>
       <c r="G5" t="n">
         <v>0.002207292532637347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002395905181687791</v>
+        <v>0.002395905181687788</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002354575510853845</v>
+        <v>0.002354575510853836</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002817665193951039</v>
+        <v>0.002817665193951038</v>
       </c>
       <c r="K5" t="n">
         <v>0.002117878073948941</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002272745006849545</v>
+        <v>0.002272745006849543</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001631900459038723</v>
+        <v>0.001914826833936857</v>
       </c>
       <c r="C6" t="n">
         <v>0.001626658694317197</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001642128020941373</v>
+        <v>0.001642125392319381</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001626238300210939</v>
+        <v>0.001626238300210938</v>
       </c>
       <c r="F6" t="n">
         <v>0.001649950207665617</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001924480190420859</v>
+        <v>0.001641553815522726</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001952584673047352</v>
+        <v>0.001952584673047351</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001931828345101468</v>
+        <v>0.001648901970203333</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001692724312407936</v>
+        <v>0.001961049933562089</v>
       </c>
       <c r="K6" t="n">
         <v>0.00163848168876775</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001638409552971107</v>
+        <v>0.001638409552971138</v>
       </c>
     </row>
     <row r="7">
@@ -4681,31 +4681,31 @@
         <v>0.001717144854702243</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001728333987535729</v>
+        <v>0.00172833398753573</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001733157356713544</v>
+        <v>0.001733157356713543</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001733157356713544</v>
+        <v>0.001733157356713543</v>
       </c>
       <c r="G7" t="n">
         <v>0.00172601804549181</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001732197589404809</v>
+        <v>0.001732197589404808</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00173336620017242</v>
+        <v>0.001733366200172418</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001759667780987045</v>
+        <v>0.001759667780987046</v>
       </c>
       <c r="K7" t="n">
         <v>0.00172237362323916</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001724848641007365</v>
+        <v>0.001724848641007364</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00203026868354323</v>
+        <v>0.002030268683543229</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002475790127261651</v>
+        <v>0.00247579012725775</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002579346502547826</v>
+        <v>0.002579346502547823</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002370375458860596</v>
+        <v>0.002370375458860592</v>
       </c>
       <c r="F8" t="n">
         <v>0.002061267431592705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002484766949415482</v>
+        <v>0.00248476694941548</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00249094649332949</v>
+        <v>0.002490946493329489</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002492115104096089</v>
+        <v>0.002492115104096087</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002518504108867368</v>
+        <v>0.002518504108867369</v>
       </c>
       <c r="K8" t="n">
         <v>0.002028014395279137</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00294827524933964</v>
+        <v>0.002948275249339639</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002217635145940945</v>
+        <v>0.002217635145940944</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002463852639311108</v>
+        <v>0.002463852639311107</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002475064041304875</v>
+        <v>0.002475064041304871</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002763322699847863</v>
+        <v>0.002763322699847862</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002480093103463551</v>
+        <v>0.002480093103463547</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002472725830100678</v>
+        <v>0.002472725830100676</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002478905374013675</v>
+        <v>0.00247890537401367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002480073984781285</v>
+        <v>0.002480073984781282</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002506375565595912</v>
+        <v>0.00250637556559591</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002321104583115196</v>
+        <v>0.002321104583115194</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002471556425616231</v>
+        <v>0.002471556425616227</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005280403820565809</v>
+        <v>0.003378590427317734</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005886323706809309</v>
+        <v>0.004339089051209265</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005648940344967725</v>
+        <v>0.003397985772624509</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006336794036752892</v>
+        <v>0.00471563919123499</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004428860775266491</v>
+        <v>0.00312754062875453</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005660358970538639</v>
+        <v>0.003398586712209088</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007077795166288723</v>
+        <v>0.003472937644901404</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004692794885719106</v>
+        <v>0.003347681026980684</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01039165889324857</v>
+        <v>0.00663802908079383</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007232873959828854</v>
+        <v>0.005284683991978902</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008899240051106753</v>
+        <v>0.003570999027248709</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005821417777390423</v>
+        <v>0.003275344423859653</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006338674246175457</v>
+        <v>0.00469363673020373</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00624531112256367</v>
+        <v>0.003413858440260388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006789588572497683</v>
+        <v>0.005313808808606326</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004881655311011283</v>
+        <v>0.002692356947739259</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006258444907331376</v>
+        <v>0.003418797367873537</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007889206631395635</v>
+        <v>0.003955529066595835</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00514509539733458</v>
+        <v>0.003055603724456498</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01112434948851016</v>
+        <v>0.009026036977157075</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007719772869755655</v>
+        <v>0.006318605353994885</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009983666795755942</v>
+        <v>0.0046479343165574</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002226957179440171</v>
+        <v>0.002226957179440176</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001836484689416322</v>
+        <v>0.001836484689416321</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002446036526979884</v>
+        <v>0.002446036526979885</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001846369407033545</v>
+        <v>0.001846369407033543</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001846369407033545</v>
+        <v>0.001846369407033543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002452107069646315</v>
+        <v>0.002452107069646318</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003295143405553753</v>
+        <v>0.003295143405553755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001873115534279627</v>
+        <v>0.001873115534279626</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002985533851696036</v>
+        <v>0.002985533851696039</v>
       </c>
       <c r="K4" t="n">
         <v>0.002012792258094211</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004377549462465199</v>
+        <v>0.004377549462465202</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01301235697359019</v>
+        <v>0.01301235697359028</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006885353327218602</v>
+        <v>0.006885353327218589</v>
       </c>
       <c r="D5" t="n">
         <v>0.01720389117399583</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006885354277224543</v>
+        <v>0.006885354277224526</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006885354277224543</v>
+        <v>0.006885354277224526</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01769301301109497</v>
+        <v>0.01769301301109499</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03625191561184248</v>
+        <v>0.03625191561184245</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006885198997511891</v>
+        <v>0.006885198997511882</v>
       </c>
       <c r="J5" t="n">
         <v>0.02843482762974092</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009478791704809799</v>
+        <v>0.009478791704809857</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01954028705039561</v>
+        <v>0.01954028705039559</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002823015173172723</v>
+        <v>0.002429617927952524</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002055317943759499</v>
+        <v>0.002055317943759497</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002656512082540882</v>
+        <v>0.002656513945516607</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002031539318938779</v>
+        <v>0.002031539318938778</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002073594764573167</v>
+        <v>0.002073594764573165</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003048165063378862</v>
+        <v>0.002654767818158663</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003918333095224285</v>
+        <v>0.003918333095224286</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002469173528012177</v>
+        <v>0.002469173528012176</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00358930303405964</v>
+        <v>0.003215044859399255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002204903822278598</v>
+        <v>0.00220490382227859</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00459579078394651</v>
+        <v>0.004595790783946513</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002585642186256868</v>
+        <v>0.002585642186256869</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002231954870803036</v>
+        <v>0.002231954870803034</v>
       </c>
       <c r="D7" t="n">
         <v>0.002804695905738689</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002231478375471586</v>
+        <v>0.002231478375471585</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002231478375471586</v>
+        <v>0.002231478375471585</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002810792076463011</v>
+        <v>0.002810792076463012</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003653828412370451</v>
+        <v>0.003653828412370449</v>
       </c>
       <c r="I7" t="n">
         <v>0.002231800541096322</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003344218858512732</v>
+        <v>0.003344218858512735</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002371477264910906</v>
+        <v>0.002371477264910908</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004736234469281888</v>
+        <v>0.004736234469281886</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002985397449122145</v>
+        <v>0.002985397449122148</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003225149988592503</v>
+        <v>0.003225149988596577</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003921343219003014</v>
+        <v>0.003921343219003012</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003062793145608147</v>
+        <v>0.003062793145608144</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002650262471879753</v>
+        <v>0.00265026247187975</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003804296090308251</v>
+        <v>0.003804296090308253</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004647332426215707</v>
+        <v>0.004647332426215708</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003225304554941565</v>
+        <v>0.003225304554941564</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004337839560099437</v>
+        <v>0.004337839560099438</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00276020333998499</v>
+        <v>0.002760203339984993</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006349958701128514</v>
+        <v>0.006349958701128505</v>
       </c>
     </row>
     <row r="9">
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003581223311308503</v>
+        <v>0.003581223311308508</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003650745776171444</v>
+        <v>0.00365074577617144</v>
       </c>
       <c r="D9" t="n">
         <v>0.004223512581773559</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00413912135440484</v>
+        <v>0.004139121354404842</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00365074623523628</v>
+        <v>0.003650746235236278</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004229582981831417</v>
+        <v>0.004229582981831416</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005072619317738861</v>
+        <v>0.005072619317738863</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003650591446464734</v>
+        <v>0.003650591446464731</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004763009763881141</v>
+        <v>0.004763009763881144</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003545058821471333</v>
+        <v>0.003545058821471337</v>
       </c>
       <c r="L9" t="n">
         <v>0.006155025374650297</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005027056323488171</v>
+        <v>0.003355175184940943</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005948109293494631</v>
+        <v>0.004330041807098571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005593578136858716</v>
+        <v>0.003384990102775683</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006398924261967098</v>
+        <v>0.004706805166599095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004491539262972774</v>
+        <v>0.003119163228310447</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005578555080832073</v>
+        <v>0.003384199469175192</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00661971901404288</v>
+        <v>0.003438559271429214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004757493958766106</v>
+        <v>0.003341005096785315</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009987074550363266</v>
+        <v>0.006601658073497688</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007220547161965529</v>
+        <v>0.005271291371615212</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008544988099380625</v>
+        <v>0.003542084360971259</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005530299176462781</v>
+        <v>0.003175393504960146</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006410520755129601</v>
+        <v>0.004708234285044575</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006181916616478996</v>
+        <v>0.00338728278576758</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006861723853017892</v>
+        <v>0.00532885275078581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004954338854023565</v>
+        <v>0.002708154457859072</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006164636990031696</v>
+        <v>0.003382359790620077</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007362547158186773</v>
+        <v>0.003777408975207642</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005219928449735531</v>
+        <v>0.0030742089361375</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01066023969189983</v>
+        <v>0.008862218385278996</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007706390765298226</v>
+        <v>0.00630438936918007</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009576500489734574</v>
+        <v>0.004508906794192843</v>
       </c>
     </row>
     <row r="4">
@@ -5347,31 +5347,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002062161248528063</v>
+        <v>0.002062161248528066</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001871421105955653</v>
+        <v>0.001871421105955654</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002398934461011287</v>
+        <v>0.002398934461011291</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001880132904978562</v>
+        <v>0.001880132904978563</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001880132904978562</v>
+        <v>0.001880132904978563</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002389385852468339</v>
+        <v>0.002389385852468345</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003008731419494695</v>
+        <v>0.003008731419494694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001898060152088229</v>
+        <v>0.00189806015208823</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002734643222599249</v>
+        <v>0.002734643222599248</v>
       </c>
       <c r="K4" t="n">
         <v>0.001993302231588193</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009996717850249602</v>
+        <v>0.009996717850249614</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00713500657911212</v>
+        <v>0.007135006579112114</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01548604534686402</v>
+        <v>0.0154860453468641</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007135007320231832</v>
+        <v>0.007135007320231822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007135007320231832</v>
+        <v>0.007135007320231825</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01570049162963862</v>
+        <v>0.01570049162963868</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02898790138224992</v>
+        <v>0.02898790138224987</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007134872239170738</v>
+        <v>0.007134872239170729</v>
       </c>
       <c r="J5" t="n">
         <v>0.02255213764279939</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008541032622985672</v>
+        <v>0.008541032622985693</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02032421571234697</v>
+        <v>0.02032421571234698</v>
       </c>
     </row>
     <row r="6">
@@ -5427,22 +5427,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002624083118800366</v>
+        <v>0.002261788217658221</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002081640358537879</v>
+        <v>0.002081640358537878</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00260553436029513</v>
+        <v>0.002605534360295174</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002058534653028528</v>
+        <v>0.002058534653028529</v>
       </c>
       <c r="F6" t="n">
         <v>0.002096278719861993</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002951307722740639</v>
+        <v>0.002589012821598501</v>
       </c>
       <c r="H6" t="n">
         <v>0.003591917500015639</v>
@@ -5451,13 +5451,13 @@
         <v>0.00245998202236053</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003302016382864361</v>
+        <v>0.002959045367258232</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002186474259982822</v>
+        <v>0.002186474259982824</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004366088494722324</v>
+        <v>0.004366088494722328</v>
       </c>
     </row>
     <row r="7">
@@ -5470,10 +5470,10 @@
         <v>0.00238445634413739</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002220489587638939</v>
+        <v>0.00222048958763894</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002721205657830789</v>
+        <v>0.002721205657830794</v>
       </c>
       <c r="E7" t="n">
         <v>0.002219961466014588</v>
@@ -5482,22 +5482,22 @@
         <v>0.002219961466014588</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002711680948077666</v>
+        <v>0.002711680948077668</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003331026515104015</v>
+        <v>0.003331026515104014</v>
       </c>
       <c r="I7" t="n">
         <v>0.002220355247697554</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003056938318208572</v>
+        <v>0.003056938318208575</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002315597327197516</v>
+        <v>0.002315597327197518</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004475124623699322</v>
+        <v>0.004475124623699324</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002746427712531558</v>
+        <v>0.002746427712531559</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003118328823215631</v>
+        <v>0.003118328823215636</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003730633202344175</v>
+        <v>0.003730633202344182</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002971707239429011</v>
+        <v>0.002971707239429013</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002599158426918578</v>
+        <v>0.00259915842691858</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003609891836177857</v>
+        <v>0.003609891836177863</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004229237403204277</v>
+        <v>0.004229237403204278</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003118566135797745</v>
+        <v>0.003118566135797746</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003955254591900785</v>
+        <v>0.003955254591900787</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002667607771290842</v>
+        <v>0.002667607771290845</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005933482528950893</v>
+        <v>0.005933482528950894</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00320503884204466</v>
+        <v>0.003205038842044665</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003401303314726781</v>
+        <v>0.003401303314726787</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003902043449049764</v>
+        <v>0.003902043449049763</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003817002924206215</v>
+        <v>0.003817002924206219</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003401303670691414</v>
+        <v>0.003401303670691415</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003892494675165511</v>
+        <v>0.003892494675165512</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00451184024219186</v>
+        <v>0.004511840242191861</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003401168974785396</v>
+        <v>0.003401168974785397</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004237752045296415</v>
+        <v>0.004237752045296417</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003042815592847137</v>
+        <v>0.003287691734902851</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005655938350787165</v>
+        <v>0.005655938350787162</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004905288415594327</v>
+        <v>0.003335209908663354</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006058861675269684</v>
+        <v>0.004272957016763623</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005360346369003523</v>
+        <v>0.003359158704933386</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006478968521201701</v>
+        <v>0.004624067043716461</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004667220307162465</v>
+        <v>0.003116030372881144</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005418935960736336</v>
+        <v>0.00336224215877798</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006004101161263639</v>
+        <v>0.003392387708235429</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004931604988802024</v>
+        <v>0.003336614380038764</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009516912242328389</v>
+        <v>0.006445925274768106</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007095600557859399</v>
+        <v>0.005248422291683211</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008107417710892476</v>
+        <v>0.00350532685571887</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005400919135584971</v>
+        <v>0.003123091350426304</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006558148058799148</v>
+        <v>0.004679640531962364</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005924330046976614</v>
+        <v>0.003292996013658938</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006978607783911096</v>
+        <v>0.005258072694988404</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00516685956987186</v>
+        <v>0.002768777386539662</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005991720214266711</v>
+        <v>0.003315679045547013</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006665102295281529</v>
+        <v>0.003537314051985126</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005431105983287957</v>
+        <v>0.003132754942104943</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01015275572535624</v>
+        <v>0.008528961482176816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007573881719717381</v>
+        <v>0.006247364891063905</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009083894237247786</v>
+        <v>0.004335878936084034</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001993301993741551</v>
+        <v>0.001993301993741554</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001984242763879736</v>
+        <v>0.001984242763879739</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002263814664602151</v>
+        <v>0.002263814664602154</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001992674189227638</v>
+        <v>0.001992674189227643</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001992674189227637</v>
+        <v>0.001992674189227643</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00229813423798305</v>
+        <v>0.002298134237983046</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002646404045410585</v>
+        <v>0.002646404045410588</v>
       </c>
       <c r="I4" t="n">
         <v>0.002005858675665301</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002548205982354361</v>
+        <v>0.002548205982354365</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001924639635194839</v>
+        <v>0.001924639635194843</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003896295316815156</v>
+        <v>0.003896295316815165</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008665197877603349</v>
+        <v>0.008665197877603361</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008755903116976077</v>
+        <v>0.008755903116976093</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01292154344207315</v>
+        <v>0.01292154344207317</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008755903750985864</v>
+        <v>0.00875590375098589</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008755903750985864</v>
+        <v>0.00875590375098589</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0138875016568229</v>
+        <v>0.01388750165682291</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02135723919066311</v>
+        <v>0.02135723919066312</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008755814459430317</v>
+        <v>0.008755814459430368</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01927772032631051</v>
+        <v>0.0192777203263105</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007200250920389687</v>
+        <v>0.007200250920389675</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04685009977014758</v>
+        <v>0.01460427201776809</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002196053370845705</v>
+        <v>0.002196053370845709</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002198853961251503</v>
+        <v>0.002198853961251509</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002826142571896488</v>
+        <v>0.002469213825909084</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002175388258757464</v>
+        <v>0.002175388258757461</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002208893015068433</v>
+        <v>0.002208893015068432</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002500885615087201</v>
+        <v>0.002855408185770881</v>
       </c>
       <c r="H6" t="n">
         <v>0.003223907178313947</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002563132623453144</v>
+        <v>0.002208610052769459</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002775638839420336</v>
+        <v>0.003111122381315834</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002121786220654722</v>
+        <v>0.002121786220654723</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004111028945772192</v>
+        <v>0.004111028945772199</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002307693426224544</v>
+        <v>0.002307693426224547</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002320338765694015</v>
+        <v>0.002320338765694014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002578182092037757</v>
+        <v>0.002578182092037754</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002319787180630417</v>
+        <v>0.002319787180630419</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002319787180630417</v>
+        <v>0.002319787180630419</v>
       </c>
       <c r="G7" t="n">
         <v>0.002612525670466034</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002960795477893574</v>
+        <v>0.002960795477893578</v>
       </c>
       <c r="I7" t="n">
         <v>0.002320250108148296</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002862597414837353</v>
+        <v>0.002862597414837355</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002239031067677833</v>
+        <v>0.002239031067677834</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004210686749298156</v>
+        <v>0.004210686749298155</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002660887507674841</v>
+        <v>0.002660887507674848</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003196969592094533</v>
+        <v>0.003196969592094537</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003563853189480833</v>
+        <v>0.00356385318948084</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003053743414318696</v>
+        <v>0.003053743414318697</v>
       </c>
       <c r="F8" t="n">
         <v>0.002689823069035815</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003489552607803059</v>
+        <v>0.003489552607803066</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003837822415230703</v>
+        <v>0.003837822415230706</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003197277045485317</v>
+        <v>0.003197277045485318</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003739727299504537</v>
+        <v>0.003739727299504541</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002582494684977081</v>
+        <v>0.002582494684977083</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005634900906001883</v>
+        <v>0.005634900906001892</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00302793829325921</v>
+        <v>0.003027938293259208</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003370093316831065</v>
+        <v>0.003370093316831068</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003627960836140879</v>
+        <v>0.003627960836140883</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003750340948575993</v>
+        <v>0.003750340948575992</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003370093662153134</v>
+        <v>0.003370093662153135</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003662280221603093</v>
+        <v>0.003662280221603092</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004010550029030633</v>
+        <v>0.00401055002903064</v>
       </c>
       <c r="I9" t="n">
         <v>0.00337000465928535</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003912351965974409</v>
+        <v>0.003912351965974415</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003097866492799447</v>
+        <v>0.003097866492799448</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005260441300435213</v>
+        <v>0.005260441300435221</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004380173271440389</v>
+        <v>0.003239510652143649</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005566585002042167</v>
+        <v>0.004224620458043379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004597529070083085</v>
+        <v>0.003250949656122824</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006011353518484908</v>
+        <v>0.004595830359943886</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004120541498675828</v>
+        <v>0.003021982461620716</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004712074635147448</v>
+        <v>0.003256977961706349</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00512724243365825</v>
+        <v>0.003278274033958728</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004381323376938895</v>
+        <v>0.003239592245076572</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009746197550522254</v>
+        <v>0.006486795913023101</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006893758349445705</v>
+        <v>0.005166685757737893</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005724799571937498</v>
+        <v>0.003310759199438467</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004782544405118338</v>
+        <v>0.002887054436222145</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005968815051281455</v>
+        <v>0.004514576963169404</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005032548598675482</v>
+        <v>0.002967946585494174</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006413957528932646</v>
+        <v>0.005126504910101521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004523145509123562</v>
+        <v>0.002528576727242319</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005164299726541819</v>
+        <v>0.003011181399581864</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005642160048318158</v>
+        <v>0.003166880586019018</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004783839199567448</v>
+        <v>0.002887645038054022</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01038343755143208</v>
+        <v>0.008699333189921572</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007327925468741678</v>
+        <v>0.006128758618375875</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006329079372884518</v>
+        <v>0.003394945461222259</v>
       </c>
     </row>
     <row r="4">
@@ -6139,28 +6139,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001663975869578228</v>
+        <v>0.00166397586957823</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001629211095296829</v>
+        <v>0.001629211095296828</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001793184681724847</v>
+        <v>0.001793184681724846</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001638546553484322</v>
+        <v>0.001638546553484321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001638546553484322</v>
+        <v>0.001638546553484321</v>
       </c>
       <c r="G4" t="n">
         <v>0.001860795912965135</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002108017519021022</v>
+        <v>0.002108017519021023</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001661782111294549</v>
+        <v>0.001661782111294548</v>
       </c>
       <c r="J4" t="n">
         <v>0.002593489477361184</v>
@@ -6169,7 +6169,7 @@
         <v>0.001789811199109796</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002463121170428687</v>
+        <v>0.002463121170428688</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004295837622093263</v>
+        <v>0.004295837622093297</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004314813940995255</v>
+        <v>0.004314813940995253</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006322574163507336</v>
+        <v>0.006322574163507347</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004314814867593454</v>
+        <v>0.004314814867593453</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004314814867593454</v>
+        <v>0.004314814867593455</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007726647275385781</v>
+        <v>0.007726647275385779</v>
       </c>
       <c r="H5" t="n">
         <v>0.01258386280368029</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004314747147749737</v>
+        <v>0.004314747147749734</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02218347858057396</v>
+        <v>0.02218347858057397</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006357467985615113</v>
+        <v>0.006357467985615129</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02076902782551178</v>
+        <v>0.02076902782551179</v>
       </c>
     </row>
     <row r="6">
@@ -6219,13 +6219,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001845474185094171</v>
+        <v>0.002174868372788846</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001831526076009144</v>
+        <v>0.001831526076009143</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002313578296087444</v>
+        <v>0.002313578296087442</v>
       </c>
       <c r="E6" t="n">
         <v>0.001808893655449036</v>
@@ -6234,16 +6234,16 @@
         <v>0.001841325418100405</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002042294228481078</v>
+        <v>0.002371688416175753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002643861948055683</v>
+        <v>0.002290917808037431</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001843280426810492</v>
+        <v>0.002172674614505163</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003113464270949987</v>
+        <v>0.003113464270949985</v>
       </c>
       <c r="K6" t="n">
         <v>0.001968076364180771</v>
@@ -6259,16 +6259,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001969393134092573</v>
+        <v>0.001969393134092574</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001967266169054414</v>
+        <v>0.001967266169054413</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002098577029523979</v>
+        <v>0.002098577029523978</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001966744827191961</v>
+        <v>0.00196674482719196</v>
       </c>
       <c r="F7" t="n">
         <v>0.001966744827191961</v>
@@ -6277,16 +6277,16 @@
         <v>0.002166213177479482</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002413434783535372</v>
+        <v>0.002413434783535371</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001967199375808895</v>
+        <v>0.001967199375808894</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00289890674187553</v>
+        <v>0.002898906741875529</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002095228463624143</v>
+        <v>0.002095228463624141</v>
       </c>
       <c r="L7" t="n">
         <v>0.002768538434943037</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002323279489382619</v>
+        <v>0.002323279489382621</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002840957150394556</v>
+        <v>0.002840957150394553</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003080520968270992</v>
+        <v>0.003080520968270991</v>
       </c>
       <c r="E8" t="n">
         <v>0.002698729243295497</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002337345396086915</v>
+        <v>0.002337345396086913</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00304027121306529</v>
+        <v>0.003040271213065289</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003287492819121197</v>
+        <v>0.003287492819121195</v>
       </c>
       <c r="I8" t="n">
         <v>0.002841257411394701</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003773067005219782</v>
+        <v>0.003773067005219778</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002439452362983449</v>
+        <v>0.002439452362983451</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004185959285804643</v>
+        <v>0.004185959285804642</v>
       </c>
     </row>
     <row r="9">
@@ -6342,13 +6342,13 @@
         <v>0.002778733062490001</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003128970508011828</v>
+        <v>0.003128970508011826</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003260306446639163</v>
+        <v>0.003260306446639165</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003535592399388985</v>
+        <v>0.003535592399388986</v>
       </c>
       <c r="F9" t="n">
         <v>0.003128971242917596</v>
@@ -6357,16 +6357,16 @@
         <v>0.003327917516436896</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003575139122492783</v>
+        <v>0.003575139122492785</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003128903714766311</v>
+        <v>0.00312890371476631</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004060611080832946</v>
+        <v>0.004060611080832948</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003052771547163383</v>
+        <v>0.003052771547163382</v>
       </c>
       <c r="L9" t="n">
         <v>0.003930242773900448</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004305967035824685</v>
+        <v>0.003215643166054652</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005626711243270317</v>
+        <v>0.004204832243140856</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004395659889581694</v>
+        <v>0.003220363522803527</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006070509885878598</v>
+        <v>0.004575096058140739</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004184019262661554</v>
+        <v>0.003004845352592803</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004521351155463754</v>
+        <v>0.003226978404483939</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004284117233039637</v>
+        <v>0.003213621122412073</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004445420388494737</v>
+        <v>0.003223005504339001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009096724227135589</v>
+        <v>0.006421756938305441</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006857725989516545</v>
+        <v>0.005141716654790789</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004187412669728938</v>
+        <v>0.003208924434615767</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004697322866359499</v>
+        <v>0.002847710809293304</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006038767944092673</v>
+        <v>0.004521312051545852</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004800488227998738</v>
+        <v>0.002880954703516275</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006482878780858435</v>
+        <v>0.00513184672751392</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004596388157641382</v>
+        <v>0.00253985624352216</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004945059220630404</v>
+        <v>0.002928081511774461</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004672512030061242</v>
+        <v>0.002838979604706328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004857867494028763</v>
+        <v>0.00289983213148247</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009638638732070834</v>
+        <v>0.008428400071860676</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007287211017931075</v>
+        <v>0.006099572380608515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004560963996834945</v>
+        <v>0.002803221122173233</v>
       </c>
     </row>
     <row r="4">
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001605298698362245</v>
+        <v>0.001605298698362247</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001664816016674017</v>
+        <v>0.001664816016674016</v>
       </c>
       <c r="D4" t="n">
         <v>0.001658617299312176</v>
@@ -6547,10 +6547,10 @@
         <v>0.001672829017706385</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001672829017706385</v>
+        <v>0.001672829017706386</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001732991227983434</v>
+        <v>0.001732991227983438</v>
       </c>
       <c r="H4" t="n">
         <v>0.001592400462959637</v>
@@ -6559,13 +6559,13 @@
         <v>0.001686260535163116</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002201147515084296</v>
+        <v>0.002201147515084295</v>
       </c>
       <c r="K4" t="n">
         <v>0.001756198256489102</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001534947548318658</v>
+        <v>0.001534947548318659</v>
       </c>
     </row>
     <row r="5">
@@ -6575,34 +6575,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003529739805434501</v>
+        <v>0.0035297398054345</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004778657304738773</v>
+        <v>0.004778657304738778</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004241884049549723</v>
+        <v>0.004241884049549726</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004778657996629291</v>
+        <v>0.004778657996629293</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004778657996629291</v>
+        <v>0.004778657996629293</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005519557633638384</v>
+        <v>0.005519557633638426</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003456411551883648</v>
+        <v>0.003456411551883649</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00477862529952974</v>
+        <v>0.004778625299529739</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01354968574458361</v>
+        <v>0.0135496857445836</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005799922470691447</v>
+        <v>0.005799922470691443</v>
       </c>
       <c r="L5" t="n">
         <v>0.003796846683325568</v>
@@ -6615,13 +6615,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002076904827208112</v>
+        <v>0.002076904827208111</v>
       </c>
       <c r="C6" t="n">
         <v>0.001856838002243022</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001834098171554906</v>
+        <v>0.001834100208864326</v>
       </c>
       <c r="E6" t="n">
         <v>0.001834997017836608</v>
@@ -6630,22 +6630,22 @@
         <v>0.001862159721775488</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001909776772310433</v>
+        <v>0.002204597356829297</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001767136775430016</v>
+        <v>0.002080688688280497</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001863046079490116</v>
+        <v>0.002157866664008982</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002678433647229687</v>
+        <v>0.002398516261499357</v>
       </c>
       <c r="K6" t="n">
         <v>0.001934283883871002</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001711638510037378</v>
+        <v>0.00171163851003738</v>
       </c>
     </row>
     <row r="7">
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001873311706721707</v>
+        <v>0.001873311706721708</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001954305548731614</v>
+        <v>0.001954305548731613</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001926606910307659</v>
+        <v>0.001926606910307658</v>
       </c>
       <c r="E7" t="n">
         <v>0.001953904437868826</v>
@@ -6670,7 +6670,7 @@
         <v>0.001953904437868826</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002001004236342895</v>
+        <v>0.002001004236342898</v>
       </c>
       <c r="H7" t="n">
         <v>0.001860413471319096</v>
@@ -6679,10 +6679,10 @@
         <v>0.001954273543522575</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002469160523443755</v>
+        <v>0.002469160523443756</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002024211264848563</v>
+        <v>0.002024211264848562</v>
       </c>
       <c r="L7" t="n">
         <v>0.001802960556678118</v>
@@ -6695,34 +6695,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002186791833944236</v>
+        <v>0.002186791833944237</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002727415538843545</v>
+        <v>0.002727415538843544</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002795368374271505</v>
+        <v>0.002795368374271506</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002601662108426561</v>
+        <v>0.002601662108426562</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002282138611308845</v>
+        <v>0.002282138611308844</v>
       </c>
       <c r="G8" t="n">
         <v>0.002774379955976618</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002633789190952759</v>
+        <v>0.002633789190952758</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002727649263156299</v>
+        <v>0.002727649263156298</v>
       </c>
       <c r="J8" t="n">
         <v>0.003242626624927091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002329148595412142</v>
+        <v>0.002329148595412141</v>
       </c>
       <c r="L8" t="n">
         <v>0.00305673567765328</v>
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002525066865324684</v>
+        <v>0.002525066865324685</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00289978336646559</v>
+        <v>0.002899783366465592</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002872108336016505</v>
+        <v>0.002872108336016506</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00323873391396583</v>
+        <v>0.003238733913965832</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002899784013965037</v>
+        <v>0.002899784013965038</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00294648205407687</v>
+        <v>0.002946482054076872</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002805891289053073</v>
+        <v>0.002805891289053075</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002899751361256551</v>
+        <v>0.002899751361256552</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003414638341177733</v>
+        <v>0.003414638341177736</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00279260052159573</v>
+        <v>0.002799505108926259</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002748438374412093</v>
+        <v>0.002748438374412096</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00440645715099571</v>
+        <v>0.003214710680266873</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005610968070847916</v>
+        <v>0.004145411597873765</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004313290766972739</v>
+        <v>0.003209807518519086</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006024896801616726</v>
+        <v>0.004490760380663935</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004231765401276727</v>
+        <v>0.002998219266907862</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004462748560761938</v>
+        <v>0.003217673185359122</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004281432861896109</v>
+        <v>0.003207312905098313</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00449689107982996</v>
+        <v>0.003219494091119707</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008719762602058411</v>
+        <v>0.006279170278597155</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006775740207335863</v>
+        <v>0.005128546506273251</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004263718273717256</v>
+        <v>0.003206831528932706</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004824524641493137</v>
+        <v>0.002882193064797535</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006042394016706653</v>
+        <v>0.004445215636119886</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004717364000508408</v>
+        <v>0.002847311018586508</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006456616764553687</v>
+        <v>0.005014691866308063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00466348536421369</v>
+        <v>0.002550975143642922</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004889271423454704</v>
+        <v>0.002903284323694667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004681029564756785</v>
+        <v>0.002835074653206049</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004928777061508231</v>
+        <v>0.002916091881825302</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009239119496469253</v>
+        <v>0.008135145414388376</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007205035178907028</v>
+        <v>0.006062415319233375</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004660340655784526</v>
+        <v>0.002829023796733392</v>
       </c>
     </row>
     <row r="4">
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001665978221700066</v>
+        <v>0.001665978221700064</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001700367405665681</v>
+        <v>0.00170036740566568</v>
       </c>
       <c r="D4" t="n">
         <v>0.00161059475419298</v>
@@ -6946,22 +6946,22 @@
         <v>0.001708142905622427</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00169911867379291</v>
+        <v>0.001699118673792907</v>
       </c>
       <c r="H4" t="n">
         <v>0.001591733950020264</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001717959384895871</v>
+        <v>0.00171795938489587</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002066839691214418</v>
+        <v>0.002066839691214417</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001710411937254471</v>
+        <v>0.00171041193725447</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001581215682469506</v>
+        <v>0.001581215682469504</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004516166389581054</v>
+        <v>0.004516166389581052</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005345060379768516</v>
+        <v>0.005345060379768549</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003594692507619691</v>
+        <v>0.003594692507619692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005345060966302604</v>
+        <v>0.005345060966302622</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005345060966302604</v>
+        <v>0.005345060966302622</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005080593101024808</v>
+        <v>0.00508059310102479</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003523174810743978</v>
+        <v>0.003523174810743975</v>
       </c>
       <c r="I5" t="n">
         <v>0.005345043392344141</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01150066245081314</v>
+        <v>0.01150066245081313</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005044888929111161</v>
+        <v>0.005044888929111152</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003412442682697936</v>
+        <v>0.004336205006692496</v>
       </c>
     </row>
     <row r="6">
@@ -7014,34 +7014,34 @@
         <v>0.001846088879961301</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001893786209833017</v>
+        <v>0.00189378620983301</v>
       </c>
       <c r="D6" t="n">
         <v>0.001786224950562277</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001871650602062756</v>
+        <v>0.001871650602062757</v>
       </c>
       <c r="F6" t="n">
         <v>0.001897469943451652</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002174703970336009</v>
+        <v>0.001879229332054146</v>
       </c>
       <c r="H6" t="n">
         <v>0.002081403758817222</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001898070043157109</v>
+        <v>0.001898070043157107</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002545940267194476</v>
+        <v>0.002267055108216658</v>
       </c>
       <c r="K6" t="n">
         <v>0.00189171595064552</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001760539617977192</v>
+        <v>0.001760539617977193</v>
       </c>
     </row>
     <row r="7">
@@ -7051,13 +7051,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001929670827897964</v>
+        <v>0.001929670827897963</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001981668978518183</v>
+        <v>0.001981668978518182</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001874263862239575</v>
+        <v>0.001874263862239574</v>
       </c>
       <c r="E7" t="n">
         <v>0.00198129412063662</v>
@@ -7066,19 +7066,19 @@
         <v>0.00198129412063662</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00196281127999081</v>
+        <v>0.001962811279990809</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001855426556218165</v>
+        <v>0.001855426556218163</v>
       </c>
       <c r="I7" t="n">
         <v>0.00198165199109377</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002330532297412318</v>
+        <v>0.002330532297412316</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00197410454345237</v>
+        <v>0.001974104543452368</v>
       </c>
       <c r="L7" t="n">
         <v>0.001844908288667403</v>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002238706934723843</v>
+        <v>0.002238706934723842</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002743835148368798</v>
+        <v>0.002743835148368797</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002730704573151581</v>
+        <v>0.002730704573151584</v>
       </c>
       <c r="E8" t="n">
         <v>0.002619863112837659</v>
@@ -7106,22 +7106,22 @@
         <v>0.002304866897727432</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002725218946476206</v>
+        <v>0.002725218946476201</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002617834222703473</v>
+        <v>0.002617834222703471</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002744059657579167</v>
+        <v>0.002744059657579166</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003093029063592712</v>
+        <v>0.003093029063592709</v>
       </c>
       <c r="K8" t="n">
         <v>0.002274719040876708</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003080900458758795</v>
+        <v>0.003080900458758792</v>
       </c>
     </row>
     <row r="9">
@@ -7131,22 +7131,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002509563677681526</v>
+        <v>0.002509563677681524</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002833800034965055</v>
+        <v>0.002833800034965051</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002726418601526683</v>
+        <v>0.00272641860152668</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003147957854784482</v>
+        <v>0.003147957854784479</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002833800580077869</v>
+        <v>0.002833800580077867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002814942336437678</v>
+        <v>0.002814942336437677</v>
       </c>
       <c r="H9" t="n">
         <v>0.002707557612665033</v>
@@ -7155,13 +7155,13 @@
         <v>0.00283378304754064</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003182663353859188</v>
+        <v>0.003182663353859185</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002662100242985071</v>
+        <v>0.002662100242985069</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002697039345114276</v>
+        <v>0.002697039345114274</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004882385474856351</v>
+        <v>0.003333764615640639</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005809688305578521</v>
+        <v>0.004305636536421015</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00556977917030665</v>
+        <v>0.00336994078055834</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006256870666980632</v>
+        <v>0.004679293738153963</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004358428203776073</v>
+        <v>0.003099094920471436</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005459096615263734</v>
+        <v>0.003364115777519693</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006995609128798992</v>
+        <v>0.003444868960484029</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004623446243038076</v>
+        <v>0.003320153419634593</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009843469134049272</v>
+        <v>0.006567523343194638</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007173523426027994</v>
+        <v>0.005253593245341213</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008250973460343531</v>
+        <v>0.0035127079105199</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005361710034443897</v>
+        <v>0.003113167376202742</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006249744723667087</v>
+        <v>0.004644534031788726</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00615235517738678</v>
+        <v>0.003369896767311412</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006697347115030474</v>
+        <v>0.005260071314640132</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004798904651825921</v>
+        <v>0.002651659497713975</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006025047311265228</v>
+        <v>0.003329432401450826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007792707358569324</v>
+        <v>0.003906776234635582</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005063542816711828</v>
+        <v>0.003016421429894609</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01049533796495712</v>
+        <v>0.008784087089888761</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007650390833158112</v>
+        <v>0.006277610019182539</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009236139292198338</v>
+        <v>0.00438928354848065</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001982135937500987</v>
+        <v>0.001982135937500986</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001788109534555412</v>
+        <v>0.00178810953455541</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002390762362104513</v>
+        <v>0.002390762362104511</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001797874329016418</v>
+        <v>0.001797874329016416</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001797874329016417</v>
+        <v>0.001797874329016416</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002324295453462982</v>
+        <v>0.002324295453462977</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00323804253938241</v>
+        <v>0.003238042539382402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00182399872304432</v>
+        <v>0.001823998723044318</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002664994632343962</v>
+        <v>0.002664994632343961</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001972411546727127</v>
+        <v>0.001972411546727126</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003984061078879817</v>
+        <v>0.003984061078879816</v>
       </c>
     </row>
     <row r="5">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00900878118115263</v>
+        <v>0.009008781181152614</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006318792913879023</v>
+        <v>0.006318792913879012</v>
       </c>
       <c r="D5" t="n">
         <v>0.0159221220928038</v>
@@ -7382,22 +7382,22 @@
         <v>0.006318793862146942</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01529414194409586</v>
+        <v>0.01529414194409578</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0328361420136485</v>
+        <v>0.03283614201364849</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006318656773044837</v>
+        <v>0.00631865677304483</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02266249183747318</v>
+        <v>0.02266249183747317</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008901274452282669</v>
+        <v>0.008901274452282653</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05213710620492738</v>
+        <v>0.01491678953838664</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002179532889210558</v>
+        <v>0.002179532889210556</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002002949085431503</v>
+        <v>0.002002949085431504</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00259752710031277</v>
+        <v>0.002597527100312774</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001979641509422269</v>
+        <v>0.001979641509422266</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002019427668433775</v>
+        <v>0.002019427668433774</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002899515085608045</v>
+        <v>0.002899515085608041</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00384313534464669</v>
+        <v>0.003843135344646683</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002399218355189383</v>
+        <v>0.002399218355189378</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003250382325925787</v>
+        <v>0.003250382325925786</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002161375431811013</v>
+        <v>0.002161375431811003</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004195036754236524</v>
+        <v>0.004195036754236521</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002321772345122815</v>
+        <v>0.002321772345122811</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002163771271500341</v>
+        <v>0.002163771271500339</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002730373416501157</v>
+        <v>0.002730373416501154</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002163259189186975</v>
+        <v>0.002163259189186971</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002163259189186975</v>
+        <v>0.002163259189186971</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002663931861084811</v>
+        <v>0.002663931861084808</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003577678947004233</v>
+        <v>0.003577678947004226</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00216363513066615</v>
+        <v>0.002163635130666148</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003004631039965793</v>
+        <v>0.003004631039965789</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002312047954348958</v>
+        <v>0.002312047954348954</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004323697486501631</v>
+        <v>0.004323697486501624</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002705697830994268</v>
+        <v>0.002705697830994263</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003115292613976693</v>
+        <v>0.00311529261397275</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003800035365466376</v>
+        <v>0.00380003536546637</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002959997325273081</v>
+        <v>0.002959997325273075</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002565409736627643</v>
+        <v>0.002565409736627639</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0036158015306015</v>
+        <v>0.003615801530601492</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004529548616520965</v>
+        <v>0.004529548616520951</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003115504800182838</v>
+        <v>0.003115504800182833</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003956612325889734</v>
+        <v>0.003956612325889724</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002685423585515247</v>
+        <v>0.00268542358551524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00586883234569833</v>
+        <v>0.00586883234569832</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003280530795224141</v>
+        <v>0.003280530795224134</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003528702325679459</v>
+        <v>0.003528702325679451</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004095329920521966</v>
+        <v>0.004095329920521958</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003997417344071909</v>
+        <v>0.0039974173440719</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003528702801891248</v>
+        <v>0.003528702801891243</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004028862915263933</v>
+        <v>0.004028862915263926</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004942610001183358</v>
+        <v>0.004942610001183351</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003528566184845267</v>
+        <v>0.003528566184845262</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004369562094144912</v>
+        <v>0.004369562094144902</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003441641047199026</v>
+        <v>0.00344164104719902</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005688628540680759</v>
+        <v>0.005688628540680755</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00426374766718955</v>
+        <v>0.003254608689755522</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005673119877198286</v>
+        <v>0.004249300094794617</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005388220668795613</v>
+        <v>0.003313787470446778</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006120045376031826</v>
+        <v>0.004622436617758555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004224293443021157</v>
+        <v>0.003044477335541314</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004966596733715823</v>
+        <v>0.003291598240156113</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004536039948473444</v>
+        <v>0.003267825792714177</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004490480454483007</v>
+        <v>0.003266560593487213</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009412013534916873</v>
+        <v>0.006491748482747523</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006780698084805773</v>
+        <v>0.005175453599208445</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009470012108102305</v>
+        <v>0.003531616834838164</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004650072175038397</v>
+        <v>0.002856992721139215</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006093213671883885</v>
+        <v>0.004565067450681304</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005943449060765915</v>
+        <v>0.003276285621341519</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006540482160939244</v>
+        <v>0.005180053711979069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004644730227928572</v>
+        <v>0.0025753386451422</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005458494196289123</v>
+        <v>0.003119767113576118</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004963606677210693</v>
+        <v>0.002958342234828694</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004910802804667382</v>
+        <v>0.002941790837901491</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01000024477497568</v>
+        <v>0.0085888941684876</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007200577625279939</v>
+        <v>0.006091614994039317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01063811888384227</v>
+        <v>0.004823223345308512</v>
       </c>
     </row>
     <row r="4">
@@ -7732,22 +7732,22 @@
         <v>0.002258120350261934</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00170567247493869</v>
+        <v>0.001705672474938691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00170567247493869</v>
+        <v>0.001705672474938691</v>
       </c>
       <c r="G4" t="n">
         <v>0.002006993624745017</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001751672372334783</v>
+        <v>0.001751672372334782</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001721494015698827</v>
+        <v>0.001721494015698828</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002388731941127123</v>
+        <v>0.002388731941127122</v>
       </c>
       <c r="K4" t="n">
         <v>0.001722465707114861</v>
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002862746223428652</v>
+        <v>0.002862746223428651</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004986614649047352</v>
+        <v>0.004986614649047353</v>
       </c>
       <c r="D5" t="n">
         <v>0.01309497938122142</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004986615361698401</v>
+        <v>0.004986615361698404</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004986615361698401</v>
+        <v>0.004986615361698404</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009618782259095579</v>
+        <v>0.009618782259095592</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005786410141118948</v>
+        <v>0.005786410141118958</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004986527821359554</v>
+        <v>0.004986527821359553</v>
       </c>
       <c r="J5" t="n">
         <v>0.01714742855563598</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00490818228081528</v>
+        <v>0.004908182280815284</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007856971317048508</v>
+        <v>0.06184767397722278</v>
       </c>
     </row>
     <row r="6">
@@ -7806,10 +7806,10 @@
         <v>0.002107830261148198</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001894273498523834</v>
+        <v>0.001894273498523833</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002454407030666677</v>
+        <v>0.002454409052363983</v>
       </c>
       <c r="E6" t="n">
         <v>0.001872029314962922</v>
@@ -7818,22 +7818,22 @@
         <v>0.001904350846885517</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002190926619644378</v>
+        <v>0.002525155087123148</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00228783963910457</v>
+        <v>0.002287839639104569</v>
       </c>
       <c r="I6" t="n">
         <v>0.002239655478076956</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002595127359961904</v>
+        <v>0.002595127359961902</v>
       </c>
       <c r="K6" t="n">
         <v>0.00190122858922489</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00488496725307581</v>
+        <v>0.004884967253075812</v>
       </c>
     </row>
     <row r="7">
@@ -7846,10 +7846,10 @@
         <v>0.00187892780585298</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00201083985046953</v>
+        <v>0.002010839850469531</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002547355806748643</v>
+        <v>0.002547355806748642</v>
       </c>
       <c r="E7" t="n">
         <v>0.002010389995268589</v>
@@ -7861,19 +7861,19 @@
         <v>0.002296252631827927</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002040931379417694</v>
+        <v>0.002040931379417693</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002010753022781737</v>
+        <v>0.002010753022781736</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002677990948210033</v>
+        <v>0.002677990948210032</v>
       </c>
       <c r="K7" t="n">
         <v>0.002011724714197771</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004972859447564981</v>
+        <v>0.004972859447564983</v>
       </c>
     </row>
     <row r="8">
@@ -7886,34 +7886,34 @@
         <v>0.00221442102026912</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002837939110830003</v>
+        <v>0.002837939110830002</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003476785649108144</v>
+        <v>0.003476785649108142</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002703433758207017</v>
+        <v>0.002703433758207015</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002361671890245762</v>
+        <v>0.002361671890245763</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003123657779735662</v>
+        <v>0.003123657779735663</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002868336527325406</v>
+        <v>0.002868336527325403</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002838158170689471</v>
+        <v>0.002838158170689472</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003505492770084179</v>
+        <v>0.003505492770084178</v>
       </c>
       <c r="K8" t="n">
         <v>0.002338080411983372</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006314107742225445</v>
+        <v>0.006314107742225449</v>
       </c>
     </row>
     <row r="9">
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002601688879224657</v>
+        <v>0.002601688879224656</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003054807978317222</v>
+        <v>0.003054807978317224</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003591347741992149</v>
+        <v>0.003591347741992147</v>
       </c>
       <c r="E9" t="n">
         <v>0.003425474887665324</v>
@@ -7938,22 +7938,22 @@
         <v>0.003054808558472293</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003340220759675621</v>
+        <v>0.003340220759675623</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003084899507265387</v>
+        <v>0.003084899507265386</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00305472115062943</v>
+        <v>0.003054721150629429</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003721959076057726</v>
+        <v>0.003721959076057724</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002651235758646802</v>
+        <v>0.002869584321213532</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006016827575412681</v>
+        <v>0.00601682757541268</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia photochemical ozone formation results.xlsx
+++ b/Results/Ammonia/ammonia photochemical ozone formation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003454784462611146</v>
+        <v>0.003454784462611149</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004442957941848742</v>
+        <v>0.004442957941848745</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003524854955369161</v>
+        <v>0.003524854955369163</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004826446001751193</v>
+        <v>0.004826446001751192</v>
       </c>
       <c r="F2" t="n">
         <v>0.003215933800998124</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003481331008497992</v>
+        <v>0.003481331008497994</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003560892633163869</v>
+        <v>0.003560892633163871</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003424858857142003</v>
+        <v>0.003424858857142005</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006737648106863639</v>
+        <v>0.006737648106863641</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005367309868422965</v>
+        <v>0.005367309868422969</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003652034288606678</v>
+        <v>0.003652034288606681</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003432275056466838</v>
+        <v>0.003432275056466839</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004902022727170187</v>
+        <v>0.004902022727170188</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00393182699747898</v>
+        <v>0.003931826997478981</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005533426336325822</v>
+        <v>0.00553342633632582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002874977100164779</v>
+        <v>0.00287497710016478</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003622803021137021</v>
+        <v>0.003622803021137023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004198156840184526</v>
+        <v>0.004198156840184528</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003219713832165267</v>
+        <v>0.003219713832165269</v>
       </c>
       <c r="J3" t="n">
         <v>0.009118543230497505</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006458566931047499</v>
+        <v>0.0064585669310475</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004841086695297498</v>
+        <v>0.004841086695297502</v>
       </c>
     </row>
     <row r="4">
@@ -610,22 +610,22 @@
         <v>0.002116320910763257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002769621059908556</v>
+        <v>0.002769621059908554</v>
       </c>
       <c r="H4" t="n">
         <v>0.003672182663929001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002128437326728274</v>
+        <v>0.002128437326728273</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00301612490174822</v>
+        <v>0.003016124901748219</v>
       </c>
       <c r="K4" t="n">
         <v>0.002198972560341933</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004676879465914689</v>
+        <v>0.004676879465914687</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01704382710414378</v>
+        <v>0.01704382710414379</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01083885449854038</v>
+        <v>0.01083885449854042</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03265878276109899</v>
+        <v>0.03265878276109897</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01083885500602863</v>
+        <v>0.01083885500602864</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01083885500602863</v>
+        <v>0.01083885500602864</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0237140262780563</v>
+        <v>0.02371402627805622</v>
       </c>
       <c r="H5" t="n">
         <v>0.04528847524704142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01083868638351352</v>
+        <v>0.01083868638351355</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02935201001923448</v>
+        <v>0.02935201001923449</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01225467850348603</v>
+        <v>0.01225467850348605</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06903725162731326</v>
+        <v>0.06903725162731343</v>
       </c>
     </row>
     <row r="6">
@@ -678,34 +678,34 @@
         <v>0.002709086076057361</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002347223322096671</v>
+        <v>0.002347223322096675</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003527963038502984</v>
+        <v>0.003527963038502986</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002320049719362263</v>
+        <v>0.002320049719362261</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002366792646574072</v>
+        <v>0.002366792646574074</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003470429133171223</v>
+        <v>0.003470429133171225</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004404557039447002</v>
+        <v>0.004404557039447005</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002829245399990946</v>
+        <v>0.002829245399990945</v>
       </c>
       <c r="J6" t="n">
         <v>0.003721684481750814</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002426279117242811</v>
+        <v>0.002426279117242818</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004933126793717438</v>
+        <v>0.004933126793717437</v>
       </c>
     </row>
     <row r="7">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002888851209625836</v>
+        <v>0.002888851209625838</v>
       </c>
       <c r="C7" t="n">
         <v>0.002547092089498024</v>
@@ -733,13 +733,13 @@
         <v>0.00318810770765144</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004090669311671891</v>
+        <v>0.00409066931167189</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002546923974471162</v>
+        <v>0.002546923974471161</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003434611549491108</v>
+        <v>0.003434611549491109</v>
       </c>
       <c r="K7" t="n">
         <v>0.002617459208084819</v>
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003347871351448542</v>
+        <v>0.003347871351448544</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003690795301403952</v>
+        <v>0.003690795301403955</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004966312173897924</v>
+        <v>0.004966312173897927</v>
       </c>
       <c r="E8" t="n">
         <v>0.003503492290442941</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003027577546331812</v>
+        <v>0.003027577546331813</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004332064206666409</v>
+        <v>0.004332064206666415</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005234625810686863</v>
+        <v>0.005234625810686866</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003690880473486128</v>
+        <v>0.00369088047348613</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004578702657157344</v>
+        <v>0.004578702657157343</v>
       </c>
       <c r="K8" t="n">
         <v>0.003063756305521799</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006954795910281395</v>
+        <v>0.006954795910281399</v>
       </c>
     </row>
     <row r="9">
@@ -795,31 +795,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004327453318774331</v>
+        <v>0.004327453318774332</v>
       </c>
       <c r="C9" t="n">
         <v>0.004554723352556308</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005687961120495838</v>
+        <v>0.005687961120495842</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005211370875233132</v>
+        <v>0.005211370875233134</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004554723266343613</v>
+        <v>0.004554723266343615</v>
       </c>
       <c r="G9" t="n">
         <v>0.005195738970709726</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006098300574730174</v>
+        <v>0.006098300574730177</v>
       </c>
       <c r="I9" t="n">
         <v>0.004554555237529445</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005442242812549391</v>
+        <v>0.005442242812549389</v>
       </c>
       <c r="K9" t="n">
         <v>0.003908581143685095</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003213115413401282</v>
+        <v>0.003213115413401284</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004156847184905985</v>
+        <v>0.004156847184905988</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003221938808213309</v>
+        <v>0.003221938808213311</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004503842104876532</v>
+        <v>0.004503842104876534</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003006604358193791</v>
+        <v>0.003006604358193794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003229954913218172</v>
+        <v>0.003229954913218171</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003219161195152717</v>
+        <v>0.003219161195152716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003227708714562873</v>
+        <v>0.003227708714562874</v>
       </c>
       <c r="J2" t="n">
         <v>0.006304679570605987</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005137314336406864</v>
+        <v>0.005137314336406866</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003216640811789893</v>
+        <v>0.003216640811789886</v>
       </c>
     </row>
     <row r="3">
@@ -954,34 +954,34 @@
         <v>0.002815467118824121</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004453556648075728</v>
+        <v>0.004453556648075729</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002878065564582597</v>
+        <v>0.002878065564582596</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005025678859507841</v>
+        <v>0.005025678859507842</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00255420946352497</v>
+        <v>0.002554209463524968</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002935202566838309</v>
+        <v>0.002935202566838308</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002864200377523772</v>
+        <v>0.002864200377523773</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002919044937229363</v>
+        <v>0.002919044937229365</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008204611123757978</v>
+        <v>0.008204611123757975</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006060558153917169</v>
+        <v>0.006060558153917177</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002843697941458439</v>
+        <v>0.002843697941458436</v>
       </c>
     </row>
     <row r="4">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001553806010804658</v>
+        <v>0.001553806010804656</v>
       </c>
       <c r="C4" t="n">
         <v>0.001698241546236004</v>
@@ -1006,22 +1006,22 @@
         <v>0.001706103431653887</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001743670202355449</v>
+        <v>0.001743670202355447</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001631778057609161</v>
+        <v>0.00163177805760916</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001716436777974344</v>
+        <v>0.001716436777974343</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002142366861039952</v>
+        <v>0.00214236686103995</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001697084918538974</v>
+        <v>0.001697084918538973</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001598380980831516</v>
+        <v>0.001598380980831515</v>
       </c>
     </row>
     <row r="5">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002611001404922791</v>
+        <v>0.002611001404922792</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005226120171069217</v>
+        <v>0.005226120171069221</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00417962134199271</v>
+        <v>0.004179621341992712</v>
       </c>
       <c r="E5" t="n">
         <v>0.005226120764034163</v>
@@ -1046,22 +1046,22 @@
         <v>0.005226120764034163</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005742199680177093</v>
+        <v>0.005742199680177103</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004157815532748936</v>
+        <v>0.004157815532748934</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005226092647871597</v>
+        <v>0.00522609264787161</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01306158639696915</v>
+        <v>0.01306158639696909</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0047594786163139</v>
+        <v>0.004759478616313901</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003651732556633113</v>
+        <v>0.003651732556633106</v>
       </c>
     </row>
     <row r="6">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001733620900344671</v>
+        <v>0.001733620900344669</v>
       </c>
       <c r="C6" t="n">
         <v>0.001891965396655454</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002135922444934871</v>
+        <v>0.00213592244493487</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00186969636067965</v>
+        <v>0.001869696360679654</v>
       </c>
       <c r="F6" t="n">
         <v>0.001896436158381987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002219355880499052</v>
+        <v>0.00221935588049905</v>
       </c>
       <c r="H6" t="n">
         <v>0.002126915333651664</v>
@@ -1095,13 +1095,13 @@
         <v>0.001896251667514359</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002343749730077664</v>
+        <v>0.002343749730077661</v>
       </c>
       <c r="K6" t="n">
         <v>0.001877898257674317</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001778389246075067</v>
+        <v>0.001778389246075065</v>
       </c>
     </row>
     <row r="7">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001826075275165595</v>
+        <v>0.001826075275165594</v>
       </c>
       <c r="C7" t="n">
         <v>0.0019887335655329</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001925715997788082</v>
+        <v>0.001925715997788081</v>
       </c>
       <c r="E7" t="n">
         <v>0.001988336476221331</v>
@@ -1126,22 +1126,22 @@
         <v>0.001988336476221331</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002015939466716386</v>
+        <v>0.002015939466716385</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001904047321970099</v>
+        <v>0.001904047321970097</v>
       </c>
       <c r="I7" t="n">
         <v>0.001988706042335282</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002414636125400891</v>
+        <v>0.002414636125400888</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001969354182899912</v>
+        <v>0.001969354182899911</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001870650245192454</v>
+        <v>0.001870650245192453</v>
       </c>
     </row>
     <row r="8">
@@ -1154,34 +1154,34 @@
         <v>0.002143181284728461</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002771263373650223</v>
+        <v>0.002771263373650224</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002805092241416796</v>
+        <v>0.002805092241416798</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002643925961468507</v>
+        <v>0.002643925961468508</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00232037846367727</v>
+        <v>0.002320378463677269</v>
       </c>
       <c r="G8" t="n">
         <v>0.00279872951134492</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002686837366598644</v>
+        <v>0.002686837366598645</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002771496086963817</v>
+        <v>0.002771496086963819</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003197517689473788</v>
+        <v>0.003197517689473786</v>
       </c>
       <c r="K8" t="n">
         <v>0.00227780987250988</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003139886203536439</v>
+        <v>0.003139886203536442</v>
       </c>
     </row>
     <row r="9">
@@ -1191,22 +1191,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00241397344595895</v>
+        <v>0.002413973445958948</v>
       </c>
       <c r="C9" t="n">
         <v>0.00285421111336029</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002791217328989483</v>
+        <v>0.002791217328989484</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003174532539662522</v>
+        <v>0.003174532539662523</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002854211654083649</v>
+        <v>0.00285421165408365</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002881417014543773</v>
+        <v>0.002881417014543774</v>
       </c>
       <c r="H9" t="n">
         <v>0.002769524869797487</v>
@@ -1215,10 +1215,10 @@
         <v>0.002854183590162673</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00328011367322828</v>
+        <v>0.003280113673228282</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002674001234761892</v>
+        <v>0.002674001234761891</v>
       </c>
       <c r="L9" t="n">
         <v>0.002736127793019842</v>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003973851965676488</v>
+        <v>0.003973851965676489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002674120978828744</v>
+        <v>0.002674120978828745</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004006807132757205</v>
+        <v>0.004006807132757206</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003298977804831883</v>
+        <v>0.003298977804831884</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003298983887389605</v>
+        <v>0.003298983887389606</v>
       </c>
       <c r="G2" t="n">
         <v>0.004001182430931012</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004037780532377909</v>
+        <v>0.00403778053237791</v>
       </c>
       <c r="I2" t="n">
         <v>0.003982004057809714</v>
       </c>
       <c r="J2" t="n">
-        <v>0.005019996344401992</v>
+        <v>0.005019996344401996</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004671943737501419</v>
+        <v>0.004671943737501421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004021971559673266</v>
+        <v>0.004021971559673268</v>
       </c>
     </row>
     <row r="3">
@@ -1347,31 +1347,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004157128227565</v>
+        <v>0.004157128227565003</v>
       </c>
       <c r="C3" t="n">
         <v>0.002094228638832662</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004391652729218086</v>
+        <v>0.004391652729218087</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003087772344788892</v>
+        <v>0.003087772344788894</v>
       </c>
       <c r="F3" t="n">
         <v>0.003087778427346615</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004352058599196328</v>
+        <v>0.004352058599196329</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004618853562103975</v>
+        <v>0.004618853562103978</v>
       </c>
       <c r="I3" t="n">
         <v>0.004215093294720152</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006251761185833296</v>
+        <v>0.006251761185833302</v>
       </c>
       <c r="K3" t="n">
         <v>0.005364002720458622</v>
@@ -1390,7 +1390,7 @@
         <v>0.001709287210665049</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001837209279773378</v>
+        <v>0.001837209279773379</v>
       </c>
       <c r="D4" t="n">
         <v>0.002081530982967575</v>
@@ -1405,16 +1405,16 @@
         <v>0.002017250591690979</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002436601238427529</v>
+        <v>0.00243660123842753</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001796492671857877</v>
+        <v>0.001796492671857876</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002465728844058743</v>
+        <v>0.002465728844058744</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001822193957689156</v>
+        <v>0.001822193957689157</v>
       </c>
       <c r="L4" t="n">
         <v>0.002252994231155524</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004906632286592478</v>
+        <v>0.004906632286592479</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007977562930208112</v>
+        <v>0.007977562930208133</v>
       </c>
       <c r="D5" t="n">
         <v>0.01146574467186887</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006497507367440033</v>
+        <v>0.006497507367440042</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006497507367440033</v>
+        <v>0.006497507367440043</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01058290312290459</v>
+        <v>0.01058290312290457</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01988751620674263</v>
+        <v>0.01988751620674268</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006497434764200553</v>
+        <v>0.006497434764200579</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01918952729192341</v>
+        <v>0.01918952729192339</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006847680657461584</v>
+        <v>0.006847680657461591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01647114477080374</v>
+        <v>0.01647114477080375</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002236828630786662</v>
+        <v>0.002236828630786666</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002047376055194377</v>
+        <v>0.002047376055194379</v>
       </c>
       <c r="D6" t="n">
         <v>0.002267514612810638</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001944582008213865</v>
+        <v>0.001944582008213856</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001976563699616016</v>
+        <v>0.001976563699616017</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002197806055150451</v>
+        <v>0.002197806055150454</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00299753257720972</v>
+        <v>0.002997532577209722</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001977048135317351</v>
+        <v>0.001977048135317352</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003000909574499834</v>
+        <v>0.003000909574499836</v>
       </c>
       <c r="K6" t="n">
         <v>0.001995963644589413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002435836330741901</v>
+        <v>0.002435836330741902</v>
       </c>
     </row>
     <row r="7">
@@ -1513,31 +1513,31 @@
         <v>0.002212121031977033</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002416949534357237</v>
+        <v>0.002416949534357235</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002131371155152778</v>
+        <v>0.002131371155152779</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002131371155152778</v>
+        <v>0.00213137115515278</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002352692781868269</v>
+        <v>0.002352692781868272</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002772043428604818</v>
+        <v>0.00277204342860482</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002131934862035168</v>
+        <v>0.002131934862035169</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002801171034236033</v>
+        <v>0.002801171034236035</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002157636147866446</v>
+        <v>0.002157636147866447</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002588436421332813</v>
+        <v>0.002588436421332814</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002424884793717282</v>
+        <v>0.002424884793717278</v>
       </c>
       <c r="C8" t="n">
         <v>0.003154213487580694</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003476153142426342</v>
+        <v>0.003476153142426346</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002920331138726881</v>
+        <v>0.00292033113872688</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00252962477302659</v>
+        <v>0.002529624773026592</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00329525419846087</v>
+        <v>0.003295254198460868</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003714604845198189</v>
+        <v>0.003714604845198192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003074496278627766</v>
+        <v>0.003074496278627765</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003743842978855326</v>
+        <v>0.00374384297885533</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00252734456019707</v>
+        <v>0.002527344560197069</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004118477956496292</v>
+        <v>0.004118477956496288</v>
       </c>
     </row>
     <row r="9">
@@ -1590,34 +1590,34 @@
         <v>0.002866086150852587</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003400283311104138</v>
+        <v>0.003400283311104142</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003605135620690842</v>
+        <v>0.003605135620690843</v>
       </c>
       <c r="E9" t="n">
         <v>0.003743455390492645</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003320169497022936</v>
+        <v>0.003320169497022938</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003540855060995372</v>
+        <v>0.003540855060995377</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00396020570773192</v>
+        <v>0.003960205707731921</v>
       </c>
       <c r="I9" t="n">
         <v>0.003320097141162272</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003989333313363134</v>
+        <v>0.003989333313363135</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003133269933703093</v>
+        <v>0.003133269933703095</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00377659870045992</v>
+        <v>0.003776598700459918</v>
       </c>
     </row>
   </sheetData>
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003933006390912772</v>
+        <v>0.003933006390912774</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002628990519324654</v>
+        <v>0.002628990519324655</v>
       </c>
       <c r="D2" t="n">
         <v>0.003959151016125801</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003254971486268712</v>
+        <v>0.003254971486268714</v>
       </c>
       <c r="F2" t="n">
         <v>0.003254977920531529</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003952504434101095</v>
+        <v>0.003952504434101097</v>
       </c>
       <c r="H2" t="n">
         <v>0.003966697589511551</v>
@@ -1730,7 +1730,7 @@
         <v>0.004965415587597253</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004623032972083828</v>
+        <v>0.004623032972083823</v>
       </c>
       <c r="L2" t="n">
         <v>0.003950053203515568</v>
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004077730724936954</v>
+        <v>0.004077730724936955</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001996544737828882</v>
+        <v>0.001996544737828881</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004263827318428343</v>
+        <v>0.004263827318428345</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002993337874025939</v>
+        <v>0.002993337874025938</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002993344308288754</v>
+        <v>0.002993344308288757</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004216796702766927</v>
+        <v>0.004216796702766926</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004323470657561182</v>
+        <v>0.004323470657561181</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004122898598222111</v>
+        <v>0.00412289859822211</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006054203644954605</v>
+        <v>0.006054203644954608</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005245376467754671</v>
+        <v>0.005245376467754664</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004202272478435783</v>
+        <v>0.004202272478435781</v>
       </c>
     </row>
     <row r="4">
@@ -1786,10 +1786,10 @@
         <v>0.001592634405304136</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001707777119750561</v>
+        <v>0.00170777711975056</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001887949974207099</v>
+        <v>0.001887949974207098</v>
       </c>
       <c r="E4" t="n">
         <v>0.00166908447928861</v>
@@ -1804,16 +1804,16 @@
         <v>0.001980302372487147</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001660141687892774</v>
+        <v>0.001660141687892775</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002152729096298187</v>
+        <v>0.002152729096298188</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001651916247854999</v>
+        <v>0.001651916247855001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001788461814565619</v>
+        <v>0.001788461814565616</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003285928065415449</v>
+        <v>0.003285928065415448</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005809254266412416</v>
+        <v>0.005809254266412417</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008250528911283478</v>
+        <v>0.008250528911283488</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004475004965489739</v>
+        <v>0.004475004965489743</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004475004965489739</v>
+        <v>0.004475004965489743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007132628183673188</v>
+        <v>0.00713262818367318</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01087885049721421</v>
+        <v>0.0108788504972142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004474948522094476</v>
+        <v>0.004474948522094472</v>
       </c>
       <c r="J5" t="n">
         <v>0.01331988012009884</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004249699200575243</v>
+        <v>0.004249699200575246</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0073184613502587</v>
+        <v>0.00731846135025871</v>
       </c>
     </row>
     <row r="6">
@@ -1863,31 +1863,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002078938023022594</v>
+        <v>0.002078938023022593</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001903085712435816</v>
+        <v>0.001903085712435821</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002379012576995295</v>
+        <v>0.002379012576995294</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001806927753857791</v>
+        <v>0.001806927753857793</v>
       </c>
       <c r="F6" t="n">
         <v>0.001834394048775593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002298531384255854</v>
+        <v>0.002298531384255855</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002494458424513169</v>
+        <v>0.002494458424513167</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00183310073651674</v>
+        <v>0.001833100736516739</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002346921407732132</v>
+        <v>0.002346921407732131</v>
       </c>
       <c r="K6" t="n">
         <v>0.001821242089561805</v>
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001891688861511378</v>
+        <v>0.001891688861511376</v>
       </c>
       <c r="C7" t="n">
         <v>0.002036353490127607</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002186981966208021</v>
+        <v>0.00218698196620802</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001958809702250621</v>
+        <v>0.001958809702250623</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001958809702250621</v>
+        <v>0.001958809702250623</v>
       </c>
       <c r="G7" t="n">
         <v>0.002111282222744639</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002279356828694387</v>
+        <v>0.002279356828694385</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001959196144100015</v>
+        <v>0.001959196144100016</v>
       </c>
       <c r="J7" t="n">
         <v>0.002451783552505429</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00195097070406224</v>
+        <v>0.001950970704062239</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002087516270772859</v>
+        <v>0.00208751627077286</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002240320699550331</v>
+        <v>0.002240320699550337</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00289401198851608</v>
+        <v>0.002894011988516076</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003150570385465079</v>
+        <v>0.003150570385465078</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002677642208438427</v>
+        <v>0.002677642208438428</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002323778368596614</v>
+        <v>0.002323778368596613</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002969236791676203</v>
+        <v>0.002969236791676209</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00313731139762727</v>
+        <v>0.003137311397627266</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002817150713031578</v>
+        <v>0.002817150713031574</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003309838217127064</v>
+        <v>0.003309838217127056</v>
       </c>
       <c r="K8" t="n">
         <v>0.002290141610968945</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003477501020217436</v>
+        <v>0.003477501020217438</v>
       </c>
     </row>
     <row r="9">
@@ -1983,34 +1983,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002533488198899092</v>
+        <v>0.002533488198899089</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00298091413663227</v>
+        <v>0.002980914136632274</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003131565258411749</v>
+        <v>0.003131565258411748</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003253193356066054</v>
+        <v>0.00325319335606605</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002903813095484964</v>
+        <v>0.002903813095484962</v>
       </c>
       <c r="G9" t="n">
         <v>0.003055842869249305</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003223917475199053</v>
+        <v>0.003223917475199049</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002903756790604681</v>
+        <v>0.002903756790604677</v>
       </c>
       <c r="J9" t="n">
         <v>0.003396344199010093</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002720110335364271</v>
+        <v>0.00272011033536427</v>
       </c>
       <c r="L9" t="n">
         <v>0.003032076917277527</v>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003878919696617401</v>
+        <v>0.003878919696617403</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002585542902107381</v>
+        <v>0.002585542902107379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003897283189490624</v>
+        <v>0.003897283189490628</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003204953328392272</v>
+        <v>0.003204953328392275</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003204960496487391</v>
+        <v>0.003204960496487393</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003892135491117558</v>
+        <v>0.003892135491117561</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003896583660676399</v>
+        <v>0.0038965836606764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00388091137930437</v>
+        <v>0.003880911379304372</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004793106730144221</v>
+        <v>0.004793106730144217</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004578610313977802</v>
+        <v>0.004578610313977804</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003885517177797761</v>
+        <v>0.003885517177797762</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004000104925611028</v>
+        <v>0.004000104925611029</v>
       </c>
       <c r="C3" t="n">
         <v>0.001929410121595668</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004130837222292206</v>
+        <v>0.004130837222292207</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002898610078293422</v>
+        <v>0.002898610078293419</v>
       </c>
       <c r="F3" t="n">
         <v>0.002898617246388539</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004094364224216015</v>
+        <v>0.004094364224216017</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004131058962773919</v>
+        <v>0.004131058962773921</v>
       </c>
       <c r="I3" t="n">
         <v>0.004014260227365027</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005667339892711661</v>
+        <v>0.005667339892711668</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005171959901180745</v>
+        <v>0.005171959901180753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004049549522358556</v>
+        <v>0.004049549522358558</v>
       </c>
     </row>
     <row r="4">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001513835104872388</v>
+        <v>0.001513835104872389</v>
       </c>
       <c r="C4" t="n">
         <v>0.001619188237468775</v>
@@ -2194,22 +2194,22 @@
         <v>0.001537172090157986</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001662577567557158</v>
+        <v>0.001662577567557157</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001720984371653225</v>
+        <v>0.001720984371653226</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001532857816037388</v>
+        <v>0.001532857816037389</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001839266499305549</v>
+        <v>0.00183926649930555</v>
       </c>
       <c r="K4" t="n">
         <v>0.001548785241859587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001591826947375823</v>
+        <v>0.001591826947375824</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00230807183691946</v>
+        <v>0.002308071836919461</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004584478524651836</v>
+        <v>0.004584478524651837</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005806282107505877</v>
+        <v>0.005806282107505865</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002671742429845709</v>
+        <v>0.002671742429845712</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002671742429845709</v>
+        <v>0.002671742429845712</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004915390474031314</v>
+        <v>0.004915390474031313</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006356228165423941</v>
+        <v>0.006356228165423953</v>
       </c>
       <c r="I5" t="n">
         <v>0.002671692000648638</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008133935714478435</v>
+        <v>0.008133935714478433</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002880482578419021</v>
+        <v>0.002880482578419025</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003932391042510305</v>
+        <v>0.003932391042510304</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00168221149215417</v>
+        <v>0.001682211492154171</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001807553890898701</v>
+        <v>0.0018075538908987</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001891286279119473</v>
+        <v>0.001891286279119453</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001674725403697776</v>
+        <v>0.001674725403697778</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001701946488497318</v>
+        <v>0.001701946488497319</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002132449028497562</v>
+        <v>0.002132449028497563</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002215758453919352</v>
+        <v>0.002215758453919353</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002002729276977793</v>
+        <v>0.002002729276977794</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002313247600247202</v>
+        <v>0.002313247600247203</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00171567655573538</v>
+        <v>0.001715676555735357</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001758637369621565</v>
+        <v>0.001758637369621567</v>
       </c>
     </row>
     <row r="7">
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001798911957888156</v>
+        <v>0.001798911957888157</v>
       </c>
       <c r="C7" t="n">
         <v>0.001929304359834755</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002006313588721408</v>
+        <v>0.002006313588721409</v>
       </c>
       <c r="E7" t="n">
         <v>0.001817491421759518</v>
@@ -2320,16 +2320,16 @@
         <v>0.002006061224668996</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001817934669053156</v>
+        <v>0.001817934669053158</v>
       </c>
       <c r="J7" t="n">
         <v>0.00212434335232132</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001833862094875356</v>
+        <v>0.001833862094875357</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001876903800391591</v>
+        <v>0.001876903800391592</v>
       </c>
     </row>
     <row r="8">
@@ -2342,25 +2342,25 @@
         <v>0.002138016318473502</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002759167484344688</v>
+        <v>0.00275916748434469</v>
       </c>
       <c r="D8" t="n">
         <v>0.002938381357943995</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002513566555547232</v>
+        <v>0.002513566555547235</v>
       </c>
       <c r="F8" t="n">
         <v>0.002172375686873148</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002777865536150714</v>
+        <v>0.002777865536150716</v>
       </c>
       <c r="H8" t="n">
         <v>0.002836272340248063</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002648145784630948</v>
+        <v>0.002648145784630947</v>
       </c>
       <c r="J8" t="n">
         <v>0.002954650983642975</v>
@@ -2369,7 +2369,7 @@
         <v>0.002163843895431367</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003220116986473944</v>
+        <v>0.003220116986473946</v>
       </c>
     </row>
     <row r="9">
@@ -2379,19 +2379,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002333530872163733</v>
+        <v>0.002333530872163735</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002731749605496162</v>
+        <v>0.002731749605496165</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002808781476213776</v>
+        <v>0.002808781476213777</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002929496284181785</v>
+        <v>0.002929496284181787</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002620430244923306</v>
+        <v>0.002620430244923307</v>
       </c>
       <c r="G9" t="n">
         <v>0.002750099666234336</v>
@@ -2400,16 +2400,16 @@
         <v>0.002808506470330405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002620379914714565</v>
+        <v>0.002620379914714568</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002926788597982729</v>
+        <v>0.00292678859798273</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00247483194746884</v>
+        <v>0.002474831947468839</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002679349046053001</v>
+        <v>0.002679349046053004</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00388477223881617</v>
+        <v>0.003884772238816169</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002597797286865575</v>
+        <v>0.002597797286865577</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003906143806562571</v>
+        <v>0.003906143806562568</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003242167531893187</v>
+        <v>0.00324216753189319</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003242173468963273</v>
+        <v>0.003242173468963275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003907173366571586</v>
+        <v>0.003907173366571585</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003941538354650673</v>
+        <v>0.003941538354650675</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003891224877504581</v>
+        <v>0.003891224877504584</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004968884884590336</v>
+        <v>0.004968884884590337</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004616710020517378</v>
+        <v>0.004616710020517381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003935239570011658</v>
+        <v>0.003935239570011661</v>
       </c>
     </row>
     <row r="3">
@@ -2541,31 +2541,31 @@
         <v>0.001854356659546943</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004140771348610426</v>
+        <v>0.004140771348610427</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002963314582462527</v>
+        <v>0.002963314582462526</v>
       </c>
       <c r="F3" t="n">
         <v>0.002963320519532611</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004148406621546686</v>
+        <v>0.004148406621546685</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004398260441749575</v>
+        <v>0.004398260441749578</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004034563495252821</v>
+        <v>0.004034563495252822</v>
       </c>
       <c r="J3" t="n">
         <v>0.006168118312170828</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005264737421660118</v>
+        <v>0.005264737421660122</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00435018413362147</v>
+        <v>0.004350184133621472</v>
       </c>
     </row>
     <row r="4">
@@ -2581,25 +2581,25 @@
         <v>0.001490980966779914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001796824893411138</v>
+        <v>0.001796824893411137</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001611414240647117</v>
+        <v>0.001611414240647118</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001611414240647117</v>
+        <v>0.001611414240647118</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001807733726191596</v>
+        <v>0.001807733726191597</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002201144642833983</v>
+        <v>0.002201144642833984</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001623606680318559</v>
+        <v>0.00162360668031856</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002357665716912723</v>
+        <v>0.002357665716912724</v>
       </c>
       <c r="K4" t="n">
         <v>0.001695705092279124</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00269972746572675</v>
+        <v>0.002699727465726754</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002281132196377135</v>
+        <v>0.002281132196377139</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006980846261905354</v>
+        <v>0.006980846261905352</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003986234343608109</v>
+        <v>0.003986234343608139</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003986234343608109</v>
+        <v>0.003986234343608139</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007353795189700415</v>
+        <v>0.007353795189700431</v>
       </c>
       <c r="H5" t="n">
         <v>0.01583195037596338</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003986170250522622</v>
+        <v>0.003986170250522655</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01779958681545001</v>
+        <v>0.01779958681545002</v>
       </c>
       <c r="K5" t="n">
         <v>0.005186792900641763</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01452116692302934</v>
+        <v>0.01452116692302935</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001723478586130508</v>
+        <v>0.00172347858613051</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0016855101513474</v>
+        <v>0.001685510151347366</v>
       </c>
       <c r="D6" t="n">
         <v>0.001967119978147084</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001760838957142152</v>
+        <v>0.001760838957142157</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001791205711363293</v>
+        <v>0.001791205711363295</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001975789108013428</v>
+        <v>0.00197578910801343</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002728310354171884</v>
+        <v>0.002728310354171887</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00211911921112839</v>
+        <v>0.002119119211128393</v>
       </c>
       <c r="J6" t="n">
         <v>0.002547758630525444</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001859132807148314</v>
+        <v>0.001859132807148315</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002294289245151662</v>
+        <v>0.002294289245151663</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00187062852623276</v>
+        <v>0.001870628526232762</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001847635289780647</v>
+        <v>0.001847635289780648</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002112006987324889</v>
+        <v>0.00211200698732489</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00193848446983379</v>
+        <v>0.001938484469833793</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00193848446983379</v>
+        <v>0.001938484469833793</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002122939048115679</v>
+        <v>0.002122939048115681</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002516349964758065</v>
+        <v>0.002516349964758069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001938812002242643</v>
+        <v>0.001938812002242646</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002672871038836807</v>
+        <v>0.002672871038836809</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002010910414203207</v>
+        <v>0.002010910414203208</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002439023580739918</v>
+        <v>0.00243902358073992</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002238106495838759</v>
+        <v>0.00223810649583876</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002752014128170879</v>
+        <v>0.002752014128170881</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003128029554051741</v>
+        <v>0.003128029554051743</v>
       </c>
       <c r="E8" t="n">
         <v>0.002696371844459229</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002323160856727216</v>
+        <v>0.00232316085672722</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003027558583980038</v>
+        <v>0.003027558583980041</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003420969500623075</v>
+        <v>0.003420969500623078</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002843431538106999</v>
+        <v>0.002843431538107002</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003577596137541257</v>
+        <v>0.00357759613754126</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002368410703532671</v>
+        <v>0.002368410703532673</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003904732396782184</v>
+        <v>0.003904732396782186</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002622763279618701</v>
+        <v>0.002622763279618706</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002939941452565026</v>
+        <v>0.002939941452565031</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003204336532453008</v>
+        <v>0.003204336532453015</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003423732750816482</v>
+        <v>0.003423732750816488</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003031182065746936</v>
+        <v>0.003031182065746942</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00321524521090006</v>
+        <v>0.003215245210900065</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003608656127542448</v>
+        <v>0.003608656127542452</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003031118165027025</v>
+        <v>0.00303111816502703</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003765177201621186</v>
+        <v>0.003765177201621191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002906119991337948</v>
+        <v>0.002906119991337951</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0035313297435243</v>
+        <v>0.003531329743524305</v>
       </c>
     </row>
   </sheetData>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003800371326374675</v>
+        <v>0.003800371326374676</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002554606698631629</v>
+        <v>0.002554606698631628</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00380236963626433</v>
+        <v>0.003802369636264328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003191721466030063</v>
+        <v>0.003191721466030065</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003191727710609792</v>
+        <v>0.003191727710609793</v>
       </c>
       <c r="G2" t="n">
         <v>0.003804479932914878</v>
@@ -2912,16 +2912,16 @@
         <v>0.003803922869449229</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003804231268819281</v>
+        <v>0.003804231268819284</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004872271414066047</v>
+        <v>0.004872271414066044</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004550964895603637</v>
+        <v>0.004550964895603642</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003807687865154761</v>
+        <v>0.003807687865154763</v>
       </c>
     </row>
     <row r="3">
@@ -2931,34 +2931,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003873742144591403</v>
+        <v>0.003873742144591401</v>
       </c>
       <c r="C3" t="n">
         <v>0.001817976092658979</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003887927424287714</v>
+        <v>0.003887927424287713</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002890293432214413</v>
+        <v>0.00289029343221441</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002890299676794141</v>
+        <v>0.002890299676794138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003903039008727766</v>
+        <v>0.003903039008727765</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003903504111845892</v>
+        <v>0.003903504111845893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003901212580920218</v>
+        <v>0.003901212580920216</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005781345813130966</v>
+        <v>0.005781345813130963</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005123330268315313</v>
+        <v>0.005123330268315316</v>
       </c>
       <c r="L3" t="n">
         <v>0.003927200627035723</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001487530489179725</v>
+        <v>0.001487530489179726</v>
       </c>
       <c r="C4" t="n">
         <v>0.001457110225165137</v>
@@ -2980,13 +2980,13 @@
         <v>0.001510102318651341</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00153857413232706</v>
+        <v>0.001538574132327059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00153857413232706</v>
+        <v>0.001538574132327059</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001533385637218464</v>
+        <v>0.001533385637218463</v>
       </c>
       <c r="H4" t="n">
         <v>0.001535306770415969</v>
@@ -2995,7 +2995,7 @@
         <v>0.001527545387790315</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001771909801723109</v>
+        <v>0.001771909801723108</v>
       </c>
       <c r="K4" t="n">
         <v>0.001509485549966913</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002093638659994069</v>
+        <v>0.002093638659994066</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002080911968230383</v>
+        <v>0.002080911968230382</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00245308102511708</v>
+        <v>0.002453081025117077</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002820704069168872</v>
+        <v>0.002820704069168873</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002820704069168872</v>
+        <v>0.002820704069168873</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002900182786757305</v>
+        <v>0.002900182786757337</v>
       </c>
       <c r="H5" t="n">
         <v>0.003069551265006349</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002820681396637777</v>
+        <v>0.002820681396637776</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007179963906468928</v>
+        <v>0.007179963906468924</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002446782857159646</v>
+        <v>0.002446782857159645</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003811145032594981</v>
+        <v>0.003811145032594983</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001649149768284754</v>
+        <v>0.001649149768284748</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001640695072765642</v>
+        <v>0.001640695072765639</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001965275338267437</v>
+        <v>0.001965275338267439</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001667066962925234</v>
+        <v>0.001667066962925244</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001690665313005791</v>
+        <v>0.00169066531300579</v>
       </c>
       <c r="G6" t="n">
         <v>0.001695004916323492</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002011940644648401</v>
+        <v>0.002011940644648399</v>
       </c>
       <c r="I6" t="n">
         <v>0.001979683394823612</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002227460487843026</v>
+        <v>0.00222746048784302</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001670043535133097</v>
+        <v>0.001670043535133076</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001732048186328976</v>
+        <v>0.001732048186328977</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001757934636833281</v>
+        <v>0.001757934636833274</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001757286661055623</v>
+        <v>0.001757286661055621</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001780484486312934</v>
+        <v>0.001780484486312933</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001797746395134268</v>
+        <v>0.001797746395134267</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001797746395134268</v>
+        <v>0.001797746395134267</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001803789784872022</v>
+        <v>0.001803789784872019</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001805710918069525</v>
+        <v>0.001805710918069519</v>
       </c>
       <c r="I7" t="n">
         <v>0.001797949535443872</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002042313949376664</v>
+        <v>0.002042313949376657</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001779889697620468</v>
+        <v>0.001779889697620462</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001842044045631103</v>
+        <v>0.001842044045631108</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002087133383054812</v>
+        <v>0.002087133383054808</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002559263419582483</v>
+        <v>0.002559263419582481</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00268063330574466</v>
+        <v>0.002680633305744656</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002470627482603878</v>
+        <v>0.00247062748260388</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002142038749601625</v>
+        <v>0.002142038749601626</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002605863018846243</v>
+        <v>0.002605863018846241</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002607784152044738</v>
+        <v>0.002607784152044735</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002600022769418095</v>
+        <v>0.002600022769418093</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002844480115912831</v>
+        <v>0.002844480115912823</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002100304557538948</v>
+        <v>0.002100304557538947</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0031380742224019</v>
+        <v>0.003138074222401897</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002328943800516337</v>
+        <v>0.002328943800516339</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002600989859642723</v>
+        <v>0.002600989859642724</v>
       </c>
       <c r="D9" t="n">
         <v>0.002624209831392747</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002956358636367375</v>
+        <v>0.002956358636367376</v>
       </c>
       <c r="F9" t="n">
         <v>0.002641675362610413</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002647492983459125</v>
+        <v>0.002647492983459123</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002649414116656626</v>
+        <v>0.002649414116656633</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002641652734030976</v>
+        <v>0.002641652734030975</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002886017147963768</v>
+        <v>0.002886017147963772</v>
       </c>
       <c r="K9" t="n">
         <v>0.002465592971461612</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002685747244218206</v>
+        <v>0.002685747244218205</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003712218783962811</v>
+        <v>0.00371221878396281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002531064251153036</v>
+        <v>0.002531064251153034</v>
       </c>
       <c r="D2" t="n">
         <v>0.003713796641350014</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00316353265430479</v>
+        <v>0.003163532654304791</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003163539747748229</v>
+        <v>0.00316353974774823</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003713648395874033</v>
+        <v>0.003713648395874032</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003713439172400445</v>
+        <v>0.003713439172400446</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003714514353664385</v>
+        <v>0.003714514353664383</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004718123281592114</v>
+        <v>0.004718123281592115</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004527868069882952</v>
+        <v>0.004527868069882951</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003713027612535706</v>
+        <v>0.003713027612535707</v>
       </c>
     </row>
     <row r="3">
@@ -3327,25 +3327,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003753589979898695</v>
+        <v>0.003753589979898694</v>
       </c>
       <c r="C3" t="n">
         <v>0.001806020418842005</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003764784473114131</v>
+        <v>0.003764784473114128</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002860562066232744</v>
+        <v>0.002860562066232741</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002860569159676184</v>
+        <v>0.002860569159676185</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003763778451391189</v>
+        <v>0.003763778451391191</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003766475814030985</v>
+        <v>0.003766475814030987</v>
       </c>
       <c r="I3" t="n">
         <v>0.003769915647559995</v>
@@ -3354,7 +3354,7 @@
         <v>0.005443577764933072</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005100203396731878</v>
+        <v>0.005100203396731883</v>
       </c>
       <c r="L3" t="n">
         <v>0.003760597406616662</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001471385225896208</v>
+        <v>0.001471385225896203</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001448308103341556</v>
+        <v>0.001448308103341552</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001489207850934933</v>
+        <v>0.001489207850934929</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00150085496614597</v>
+        <v>0.001500854966145969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00150085496614597</v>
+        <v>0.001500854966145969</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001487082534356548</v>
+        <v>0.00148708253435648</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001492553403606234</v>
+        <v>0.001492553403606236</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001494414335824872</v>
+        <v>0.001494414335824884</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00153216816085747</v>
+        <v>0.001532168160857467</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001471949374705769</v>
+        <v>0.001471949374705768</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001482479934385005</v>
+        <v>0.001482479934385007</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002012117262614641</v>
+        <v>0.002012117262614625</v>
       </c>
       <c r="C5" t="n">
         <v>0.002057238311709026</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002292746424768624</v>
+        <v>0.002292746424768623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00243782239798787</v>
+        <v>0.002437822397987864</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00243782239798787</v>
+        <v>0.002437822397987863</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002289634044775416</v>
+        <v>0.00228963404477537</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002471681859645029</v>
+        <v>0.002471681859645027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002437803550207782</v>
+        <v>0.002437803550207776</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003105362938392853</v>
+        <v>0.003105362938392856</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002001850376091849</v>
+        <v>0.00200185037609185</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002296765308719519</v>
+        <v>0.002296765308719517</v>
       </c>
     </row>
     <row r="6">
@@ -3450,34 +3450,34 @@
         <v>0.001920777883471133</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001631935302340416</v>
+        <v>0.001631935302340415</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001651558431359635</v>
+        <v>0.001651558431359638</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001635728220177938</v>
+        <v>0.00163572822017794</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001659533639465276</v>
+        <v>0.001659533639465274</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001936475191931404</v>
+        <v>0.00193647519193141</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001655186381966195</v>
+        <v>0.001655186381966193</v>
       </c>
       <c r="I6" t="n">
         <v>0.001943806993399814</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001714003983671331</v>
+        <v>0.00171400398367133</v>
       </c>
       <c r="K6" t="n">
         <v>0.001636242800994231</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001644558735944672</v>
+        <v>0.001644558735944673</v>
       </c>
     </row>
     <row r="7">
@@ -3490,22 +3490,22 @@
         <v>0.001729778038168975</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001732453077288337</v>
+        <v>0.001732453077288334</v>
       </c>
       <c r="D7" t="n">
         <v>0.001747578566956739</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001752560755422214</v>
+        <v>0.001752560755422213</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001752560755422214</v>
+        <v>0.001752560755422213</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001745475346629251</v>
+        <v>0.001745475346629249</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001750946215879007</v>
+        <v>0.001750946215879008</v>
       </c>
       <c r="I7" t="n">
         <v>0.001752807148097656</v>
@@ -3514,10 +3514,10 @@
         <v>0.001790560973130238</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001730342186978537</v>
+        <v>0.00173034218697854</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001740872746657777</v>
+        <v>0.00174087274665778</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00205123986685573</v>
+        <v>0.002051239866855732</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002511149257690949</v>
+        <v>0.002511149257690947</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002621272627666588</v>
+        <v>0.002621272627666591</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002406444768033868</v>
+        <v>0.002406444768033867</v>
       </c>
       <c r="F8" t="n">
         <v>0.002088640739549644</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002524308406803258</v>
+        <v>0.002524308406803262</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002529779276053991</v>
+        <v>0.00252977927605399</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002531640208271665</v>
+        <v>0.002531640208271664</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002569483919037315</v>
+        <v>0.002569483919037316</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002043308110306246</v>
+        <v>0.002043308110306249</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002997468302102275</v>
+        <v>0.002997468302102277</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002231047783769928</v>
+        <v>0.00223104778376993</v>
       </c>
       <c r="C9" t="n">
         <v>0.002482521918471877</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00249766965647937</v>
+        <v>0.002497669656479375</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002790003803433979</v>
+        <v>0.002790003803433982</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002502894795444421</v>
+        <v>0.002502894795444424</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002495544187812788</v>
+        <v>0.002495544187812792</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00250101505706255</v>
+        <v>0.002501015057062548</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002502875989281195</v>
+        <v>0.002502875989281196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002540629814313777</v>
+        <v>0.002540629814313779</v>
       </c>
       <c r="K9" t="n">
         <v>0.002336255919039756</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002490941587841318</v>
+        <v>0.002490941587841319</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003793649035960776</v>
+        <v>0.003793649035960788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002571612364443152</v>
+        <v>0.002571612364443167</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003797805809232013</v>
+        <v>0.003797805809232001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003211146924216358</v>
+        <v>0.003211146924216386</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00321115270958731</v>
+        <v>0.003211152709587332</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003803568236338868</v>
+        <v>0.003803568236338853</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003841087274652664</v>
+        <v>0.003841087274652676</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00379849572706202</v>
+        <v>0.003798495727062012</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004876533927434649</v>
+        <v>0.004876533927434657</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004572243914477503</v>
+        <v>0.004572243914477513</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003834245859634751</v>
+        <v>0.003834245859634741</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003857770862439827</v>
+        <v>0.003857770862439829</v>
       </c>
       <c r="C3" t="n">
         <v>0.001833891866545759</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003887314731498449</v>
+        <v>0.003887314731498443</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002922876267857176</v>
+        <v>0.00292287626785717</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002922882053228127</v>
+        <v>0.002922882053228121</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003928513922327155</v>
+        <v>0.003928513922327153</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004199791447136756</v>
+        <v>0.004199791447136757</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003892263763805825</v>
+        <v>0.003892263763805828</v>
       </c>
       <c r="J3" t="n">
         <v>0.005748581279416384</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00517302604749296</v>
+        <v>0.005173026047492962</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004147888151862121</v>
+        <v>0.00414788815186212</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001523958666774837</v>
+        <v>0.001523958666774836</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001468483013353356</v>
+        <v>0.001468483013353355</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001570911333083375</v>
+        <v>0.001570911333083368</v>
       </c>
       <c r="E4" t="n">
         <v>0.00156375782894669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00156375782894669</v>
+        <v>0.001563757828946689</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001635354680345679</v>
+        <v>0.001635354680345678</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002063045297203385</v>
+        <v>0.002063045297203378</v>
       </c>
       <c r="I4" t="n">
         <v>0.001574504595944639</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00173645121177448</v>
+        <v>0.001736451211774483</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001586072733321436</v>
+        <v>0.001586072733321438</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001979867172881931</v>
+        <v>0.001979867172881933</v>
       </c>
     </row>
     <row r="5">
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002451194934929075</v>
+        <v>0.002451194934929074</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002159169908519367</v>
+        <v>0.002159169908519368</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003257902776659021</v>
+        <v>0.003257902776659015</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003412529913173824</v>
+        <v>0.003412529913173819</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003412529913173824</v>
+        <v>0.003412529913173819</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004508685501259407</v>
+        <v>0.004508685501259473</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01340983616529762</v>
+        <v>0.01340983616529761</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00341249409621017</v>
+        <v>0.003412494096210166</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006461926965705773</v>
+        <v>0.006461926965705792</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003537615433906903</v>
+        <v>0.003537615433906902</v>
       </c>
       <c r="L5" t="n">
         <v>0.01193266723838756</v>
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001683568973699556</v>
+        <v>0.001683568973699558</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0016564896039235</v>
+        <v>0.001656489603923498</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001729418916136539</v>
+        <v>0.001729418916136542</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001706900273571283</v>
+        <v>0.001706900273571281</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001733850647762159</v>
+        <v>0.00173385064776216</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001794964987270399</v>
+        <v>0.0017949649872704</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002569377087372194</v>
+        <v>0.002569377087372188</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001734114902869361</v>
+        <v>0.00173411490286936</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001913993149085396</v>
+        <v>0.00191399314908539</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001741598236487608</v>
+        <v>0.00174159823648763</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002141233916944386</v>
+        <v>0.002141233916944385</v>
       </c>
     </row>
     <row r="7">
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001822381480237325</v>
+        <v>0.001822381480237321</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001806463212650739</v>
+        <v>0.00180646321265074</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00186931101617976</v>
+        <v>0.001869311016179757</v>
       </c>
       <c r="E7" t="n">
         <v>0.00187264767044315</v>
@@ -3898,22 +3898,22 @@
         <v>0.00187264767044315</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001933777493808168</v>
+        <v>0.001933777493808163</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002361468110665869</v>
+        <v>0.002361468110665862</v>
       </c>
       <c r="I7" t="n">
         <v>0.001872927409407125</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002034874025236976</v>
+        <v>0.002034874025236968</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001884495546783919</v>
+        <v>0.001884495546783924</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002278289986344416</v>
+        <v>0.002278289986344419</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002178460349556609</v>
+        <v>0.002178460349556604</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002678226243072463</v>
+        <v>0.002678226243072462</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002848235605041961</v>
+        <v>0.002848235605041962</v>
       </c>
       <c r="E8" t="n">
         <v>0.002603657207289264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00224521950162777</v>
+        <v>0.002245219501627772</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002805712766612897</v>
+        <v>0.002805712766612898</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003233403383471244</v>
+        <v>0.003233403383471242</v>
       </c>
       <c r="I8" t="n">
         <v>0.002744862682211858</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002906910677739612</v>
+        <v>0.002906910677739604</v>
       </c>
       <c r="K8" t="n">
         <v>0.002230992118652772</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003689080406976445</v>
+        <v>0.003689080406976442</v>
       </c>
     </row>
     <row r="9">
@@ -3972,28 +3972,28 @@
         <v>0.002890317733827264</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003263141488729086</v>
+        <v>0.003263141488729089</v>
       </c>
       <c r="F9" t="n">
         <v>0.002893946547753803</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00295476098910914</v>
+        <v>0.002954760989109137</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003382451605966843</v>
+        <v>0.003382451605966834</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002893910904708096</v>
+        <v>0.002893910904708097</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003055857520537943</v>
+        <v>0.003055857520537942</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002720109144692876</v>
+        <v>0.002720109144692871</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003299273481645391</v>
+        <v>0.003299273481645393</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003604292248405332</v>
+        <v>0.003604292248405321</v>
       </c>
       <c r="C2" t="n">
         <v>0.002535613015620631</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003605554549841601</v>
+        <v>0.00360555454984159</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003166938144594592</v>
+        <v>0.003166938144594588</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003166944371619587</v>
+        <v>0.003166944371619584</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003605603093091138</v>
+        <v>0.003605603093091127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003605219115434254</v>
+        <v>0.003605219115434256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003607305174218155</v>
+        <v>0.003607305174218144</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004825009304954689</v>
+        <v>0.004825009304954686</v>
       </c>
       <c r="K2" t="n">
         <v>0.004510654921057978</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003604895243444614</v>
+        <v>0.003604895243444615</v>
       </c>
     </row>
     <row r="3">
@@ -4119,34 +4119,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003573528991357908</v>
+        <v>0.003573528991357904</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001809448641476429</v>
+        <v>0.00180944864147643</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003582468669849597</v>
+        <v>0.003582468669849594</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00286819483768694</v>
+        <v>0.002868194837686943</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002868201064711934</v>
+        <v>0.00286820106471194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003582868522875139</v>
+        <v>0.003582868522875138</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003584331465390342</v>
+        <v>0.003584331465390343</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003594960732264554</v>
+        <v>0.003594960732264551</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00561479043774327</v>
+        <v>0.005614790437743268</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005073561522335902</v>
+        <v>0.005073561522335903</v>
       </c>
       <c r="L3" t="n">
         <v>0.00357910181041546</v>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001480834430482589</v>
+        <v>0.001480834430482591</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001450028350057122</v>
+        <v>0.00145002835005712</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001495092705892598</v>
+        <v>0.001495092705892601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001522980630952574</v>
+        <v>0.001522980630952575</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001522980630952574</v>
+        <v>0.001522980630952575</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001495107470439881</v>
+        <v>0.001495107470439885</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001498694039245787</v>
+        <v>0.001498694039245789</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001511414328366271</v>
+        <v>0.001511414328366273</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001534794508079337</v>
+        <v>0.001534794508079338</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001489007642207634</v>
+        <v>0.001489007642207631</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001489643218977895</v>
+        <v>0.001489643218977894</v>
       </c>
     </row>
     <row r="5">
@@ -4199,13 +4199,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002119386768174828</v>
+        <v>0.00211938676817483</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002085925494316406</v>
+        <v>0.002085925494316401</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00233558766772975</v>
+        <v>0.002335587667729751</v>
       </c>
       <c r="E5" t="n">
         <v>0.00268073461666526</v>
@@ -4214,22 +4214,22 @@
         <v>0.00268073461666526</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002372423896332077</v>
+        <v>0.002372423896332107</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00252446209633881</v>
+        <v>0.002524462096338811</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002680716732977681</v>
+        <v>0.002680716732977682</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003092045341344574</v>
+        <v>0.003092045341344568</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002235527118720583</v>
+        <v>0.002235527118720586</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002370451345964512</v>
+        <v>0.002370451345964509</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001928046807266453</v>
+        <v>0.001928046807266456</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001632484009014568</v>
+        <v>0.001632484009014559</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00165546849472487</v>
+        <v>0.001655468494724868</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001650553593483508</v>
+        <v>0.001650553593483509</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001673396009723702</v>
+        <v>0.001673396009723703</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001655573565843278</v>
+        <v>0.00165557356584328</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001969720062639056</v>
+        <v>0.001969720062639062</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001958626705150135</v>
+        <v>0.001958626705150136</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001712383475916142</v>
+        <v>0.001712383475916141</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00164866364451205</v>
+        <v>0.001648663644512047</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001648492701975779</v>
+        <v>0.001648492701975778</v>
       </c>
     </row>
     <row r="7">
@@ -4279,13 +4279,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001740131215493199</v>
+        <v>0.001740131215493195</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001738329399393715</v>
+        <v>0.001738329399393713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001754367492137427</v>
+        <v>0.001754367492137428</v>
       </c>
       <c r="E7" t="n">
         <v>0.001770592847719366</v>
@@ -4297,19 +4297,19 @@
         <v>0.001754404255450493</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001757990824256398</v>
+        <v>0.001757990824256394</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001770711113376882</v>
+        <v>0.001770711113376884</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001794091293089948</v>
+        <v>0.00179409129308995</v>
       </c>
       <c r="K7" t="n">
         <v>0.001748304427218244</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001748940003988504</v>
+        <v>0.001748940003988506</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002060941811806796</v>
+        <v>0.0020609418118068</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002517219792058075</v>
+        <v>0.002517219792058073</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00262828212533445</v>
+        <v>0.002628282125334454</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002424331578842086</v>
+        <v>0.002424331578842088</v>
       </c>
       <c r="F8" t="n">
         <v>0.002105992350620966</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00253330824140022</v>
+        <v>0.002533308241400218</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002536894810207121</v>
+        <v>0.002536894810207119</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00254961509932661</v>
+        <v>0.002549615099326612</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00257308530669627</v>
+        <v>0.002573085306696269</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002060605703714613</v>
+        <v>0.002060605703714611</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00300636083978003</v>
+        <v>0.003006360839780035</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002304731704858295</v>
+        <v>0.002304731704858297</v>
       </c>
       <c r="C9" t="n">
         <v>0.002569737843758347</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002585798090161471</v>
+        <v>0.002585798090161469</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002910028259623849</v>
+        <v>0.002910028259623852</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002602137405706867</v>
+        <v>0.00260213740570687</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002585812699815125</v>
+        <v>0.002585812699815128</v>
       </c>
       <c r="H9" t="n">
         <v>0.002589399268621032</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002602119557741516</v>
+        <v>0.002602119557741519</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002625499737454583</v>
+        <v>0.002625499737454585</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002243753991041859</v>
+        <v>0.002243753991041855</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002580348448353139</v>
+        <v>0.002580348448353143</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003572599294722326</v>
+        <v>0.003572599294722325</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002498633121802023</v>
+        <v>0.002498633121802025</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003573660908839474</v>
+        <v>0.00357366090883947</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003127854356962893</v>
+        <v>0.003127854356962899</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003127861460263579</v>
+        <v>0.00312786146026358</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003573491316200918</v>
+        <v>0.003573491316200904</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003573359799814643</v>
+        <v>0.003573359799814645</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003574344565317019</v>
+        <v>0.003574344565317013</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004679340221253355</v>
+        <v>0.004679340221253356</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004484019860717253</v>
+        <v>0.004484019860717265</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003573181166430936</v>
+        <v>0.003573181166430937</v>
       </c>
     </row>
     <row r="3">
@@ -4515,34 +4515,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003570566392289526</v>
+        <v>0.003570566392289528</v>
       </c>
       <c r="C3" t="n">
         <v>0.001798977781294761</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003578081774777173</v>
+        <v>0.003578081774777174</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002846097776068274</v>
+        <v>0.002846097776068265</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00284610487936895</v>
+        <v>0.002846104879368949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003576919548484523</v>
+        <v>0.003576919548484529</v>
       </c>
       <c r="H3" t="n">
         <v>0.003580082641936719</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003582968922224342</v>
+        <v>0.003582968922224334</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005418507564103106</v>
+        <v>0.005418507564103113</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005077903714093961</v>
+        <v>0.005077903714093957</v>
       </c>
       <c r="L3" t="n">
         <v>0.003575924334233258</v>
@@ -4564,28 +4564,28 @@
         <v>0.001479055005425821</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001490644792658999</v>
+        <v>0.001490644792659</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001490644792658999</v>
+        <v>0.001490644792659</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001476716942090027</v>
+        <v>0.001476716942090026</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001482896486003024</v>
+        <v>0.001482896486003025</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001484065096770634</v>
+        <v>0.001484065096770635</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001510366677585263</v>
+        <v>0.001510366677585262</v>
       </c>
       <c r="K4" t="n">
         <v>0.001473072519837376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001475547537605581</v>
+        <v>0.00147554753760558</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002036372123898862</v>
+        <v>0.002036372123898864</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002048598125517002</v>
+        <v>0.002048598125517001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002216635791255764</v>
+        <v>0.002216635791255767</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002354594666781667</v>
+        <v>0.002354594666781668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002354594666781667</v>
+        <v>0.002354594666781668</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002207292532637347</v>
+        <v>0.002207292532637393</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002395905181687788</v>
+        <v>0.002395905181687789</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002354575510853836</v>
+        <v>0.002354575510853837</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002817665193951038</v>
+        <v>0.002817665193951041</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002117878073948941</v>
+        <v>0.002117878073948942</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002272745006849543</v>
+        <v>0.002272745006849541</v>
       </c>
     </row>
     <row r="6">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001914826833936857</v>
+        <v>0.001914826833936858</v>
       </c>
       <c r="C6" t="n">
         <v>0.001626658694317197</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001642125392319381</v>
+        <v>0.001642125392319382</v>
       </c>
       <c r="E6" t="n">
         <v>0.001626238300210938</v>
@@ -4653,19 +4653,19 @@
         <v>0.001641553815522726</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001952584673047351</v>
+        <v>0.001952584673047352</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001648901970203333</v>
+        <v>0.001648901970203334</v>
       </c>
       <c r="J6" t="n">
         <v>0.001961049933562089</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00163848168876775</v>
+        <v>0.001638481688767749</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001638409552971138</v>
+        <v>0.001638409552971139</v>
       </c>
     </row>
     <row r="7">
@@ -4678,16 +4678,16 @@
         <v>0.001716364689007808</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001717144854702243</v>
+        <v>0.001717144854702245</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00172833398753573</v>
+        <v>0.001728333987535729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001733157356713543</v>
+        <v>0.001733157356713544</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001733157356713543</v>
+        <v>0.001733157356713544</v>
       </c>
       <c r="G7" t="n">
         <v>0.00172601804549181</v>
@@ -4696,13 +4696,13 @@
         <v>0.001732197589404808</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001733366200172418</v>
+        <v>0.001733366200172419</v>
       </c>
       <c r="J7" t="n">
         <v>0.001759667780987046</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00172237362323916</v>
+        <v>0.001722373623239159</v>
       </c>
       <c r="L7" t="n">
         <v>0.001724848641007364</v>
@@ -4721,31 +4721,31 @@
         <v>0.00247579012725775</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002579346502547823</v>
+        <v>0.002579346502547826</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002370375458860592</v>
+        <v>0.002370375458860593</v>
       </c>
       <c r="F8" t="n">
         <v>0.002061267431592705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00248476694941548</v>
+        <v>0.002484766949415482</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002490946493329489</v>
+        <v>0.002490946493329488</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002492115104096087</v>
+        <v>0.002492115104096089</v>
       </c>
       <c r="J8" t="n">
         <v>0.002518504108867369</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002028014395279137</v>
+        <v>0.002028014395279136</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002948275249339639</v>
+        <v>0.002948275249339641</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002217635145940944</v>
+        <v>0.002217635145940947</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002463852639311107</v>
+        <v>0.002463852639311111</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002475064041304871</v>
+        <v>0.002475064041304877</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002763322699847862</v>
+        <v>0.002763322699847868</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002480093103463547</v>
+        <v>0.002480093103463552</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002472725830100676</v>
+        <v>0.002472725830100679</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00247890537401367</v>
+        <v>0.002478905374013676</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002480073984781282</v>
+        <v>0.002480073984781288</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00250637556559591</v>
+        <v>0.002506375565595916</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002321104583115194</v>
+        <v>0.0023211045831152</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002471556425616227</v>
+        <v>0.002471556425616233</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003378590427317734</v>
+        <v>0.003378590427317733</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004339089051209265</v>
+        <v>0.004339089051209267</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003397985772624509</v>
+        <v>0.003397985772624511</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00471563919123499</v>
+        <v>0.004715639191234992</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00312754062875453</v>
+        <v>0.003127540628754531</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003398586712209088</v>
+        <v>0.003398586712209089</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003472937644901404</v>
+        <v>0.003472937644901405</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003347681026980684</v>
+        <v>0.003347681026980685</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00663802908079383</v>
+        <v>0.006638029080793828</v>
       </c>
       <c r="K2" t="n">
         <v>0.005284683991978902</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003570999027248709</v>
+        <v>0.003570999027248708</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003275344423859653</v>
+        <v>0.003275344423859649</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00469363673020373</v>
+        <v>0.004693636730203725</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003413858440260388</v>
+        <v>0.003413858440260389</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005313808808606326</v>
+        <v>0.005313808808606325</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002692356947739259</v>
+        <v>0.002692356947739261</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003418797367873537</v>
+        <v>0.003418797367873536</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003955529066595835</v>
+        <v>0.003955529066595832</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003055603724456498</v>
+        <v>0.003055603724456499</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009026036977157075</v>
+        <v>0.009026036977157068</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006318605353994885</v>
+        <v>0.006318605353994884</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0046479343165574</v>
+        <v>0.004647934316557398</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002226957179440176</v>
+        <v>0.002226957179440168</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001836484689416321</v>
+        <v>0.001836484689416323</v>
       </c>
       <c r="D4" t="n">
         <v>0.002446036526979885</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001846369407033543</v>
+        <v>0.001846369407033545</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001846369407033543</v>
+        <v>0.001846369407033544</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002452107069646318</v>
+        <v>0.002452107069646315</v>
       </c>
       <c r="H4" t="n">
         <v>0.003295143405553755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001873115534279626</v>
+        <v>0.001873115534279627</v>
       </c>
       <c r="J4" t="n">
         <v>0.002985533851696039</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002012792258094211</v>
+        <v>0.002012792258094212</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004377549462465202</v>
+        <v>0.0043775494624652</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01301235697359028</v>
+        <v>0.01301235697359026</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006885353327218589</v>
+        <v>0.006885353327218601</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01720389117399583</v>
+        <v>0.01720389117399584</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006885354277224526</v>
+        <v>0.006885354277224537</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006885354277224526</v>
+        <v>0.006885354277224538</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01769301301109499</v>
+        <v>0.017693013011095</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03625191561184245</v>
+        <v>0.03625191561184243</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006885198997511882</v>
+        <v>0.00688519899751189</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02843482762974092</v>
+        <v>0.02843482762974091</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009478791704809857</v>
+        <v>0.009478791704809858</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01954028705039559</v>
+        <v>0.0195402870503956</v>
       </c>
     </row>
     <row r="6">
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002429617927952524</v>
+        <v>0.002429617927952516</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002055317943759497</v>
+        <v>0.002055317943759501</v>
       </c>
       <c r="D6" t="n">
         <v>0.002656513945516607</v>
@@ -5043,10 +5043,10 @@
         <v>0.002031539318938778</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002073594764573165</v>
+        <v>0.002073594764573166</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002654767818158663</v>
+        <v>0.002654767818158665</v>
       </c>
       <c r="H6" t="n">
         <v>0.003918333095224286</v>
@@ -5055,13 +5055,13 @@
         <v>0.002469173528012176</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003215044859399255</v>
+        <v>0.003215044859399254</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00220490382227859</v>
+        <v>0.0022049038222786</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004595790783946513</v>
+        <v>0.004595790783946512</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002585642186256869</v>
+        <v>0.002585642186256861</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002231954870803034</v>
+        <v>0.002231954870803035</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002804695905738689</v>
+        <v>0.002804695905738686</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002231478375471585</v>
+        <v>0.002231478375471586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002231478375471585</v>
+        <v>0.002231478375471586</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002810792076463012</v>
+        <v>0.002810792076463009</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003653828412370449</v>
+        <v>0.003653828412370452</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002231800541096322</v>
+        <v>0.002231800541096323</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003344218858512735</v>
+        <v>0.003344218858512733</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002371477264910908</v>
+        <v>0.002371477264910907</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004736234469281886</v>
+        <v>0.004736234469281887</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002985397449122148</v>
+        <v>0.002985397449122145</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003225149988596577</v>
+        <v>0.003225149988596579</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003921343219003012</v>
+        <v>0.003921343219003008</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003062793145608144</v>
+        <v>0.003062793145608146</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00265026247187975</v>
+        <v>0.002650262471879748</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003804296090308253</v>
+        <v>0.003804296090308247</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004647332426215708</v>
+        <v>0.004647332426215706</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003225304554941564</v>
+        <v>0.003225304554941563</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004337839560099438</v>
+        <v>0.004337839560099434</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002760203339984993</v>
+        <v>0.00276020333998499</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006349958701128505</v>
+        <v>0.006349958701128513</v>
       </c>
     </row>
     <row r="9">
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003581223311308508</v>
+        <v>0.003581223311308507</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00365074577617144</v>
+        <v>0.003650745776171443</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004223512581773559</v>
+        <v>0.004223512581773557</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004139121354404842</v>
+        <v>0.004139121354404841</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003650746235236278</v>
+        <v>0.00365074623523628</v>
       </c>
       <c r="G9" t="n">
         <v>0.004229582981831416</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005072619317738863</v>
+        <v>0.005072619317738858</v>
       </c>
       <c r="I9" t="n">
         <v>0.003650591446464731</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004763009763881144</v>
+        <v>0.004763009763881142</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003545058821471337</v>
+        <v>0.003545058821471333</v>
       </c>
       <c r="L9" t="n">
         <v>0.006155025374650297</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003355175184940943</v>
+        <v>0.003355175184940945</v>
       </c>
       <c r="C2" t="n">
         <v>0.004330041807098571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003384990102775683</v>
+        <v>0.003384990102775686</v>
       </c>
       <c r="E2" t="n">
         <v>0.004706805166599095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003119163228310447</v>
+        <v>0.003119163228310449</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003384199469175192</v>
+        <v>0.003384199469175194</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003438559271429214</v>
+        <v>0.003438559271429217</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003341005096785315</v>
+        <v>0.003341005096785317</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006601658073497688</v>
+        <v>0.006601658073497687</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005271291371615212</v>
+        <v>0.005271291371615213</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003542084360971259</v>
+        <v>0.003542084360971264</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003175393504960146</v>
+        <v>0.003175393504960148</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004708234285044575</v>
+        <v>0.004708234285044578</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00338728278576758</v>
+        <v>0.003387282785767582</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00532885275078581</v>
+        <v>0.005328852750785817</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002708154457859072</v>
+        <v>0.002708154457859071</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003382359790620077</v>
+        <v>0.003382359790620079</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003777408975207642</v>
+        <v>0.003777408975207646</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0030742089361375</v>
+        <v>0.003074208936137501</v>
       </c>
       <c r="J3" t="n">
         <v>0.008862218385278996</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00630438936918007</v>
+        <v>0.006304389369180069</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004508906794192843</v>
+        <v>0.00450890679419285</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002062161248528066</v>
+        <v>0.002062161248528065</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001871421105955654</v>
+        <v>0.001871421105955653</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002398934461011291</v>
+        <v>0.002398934461011293</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001880132904978563</v>
+        <v>0.001880132904978562</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001880132904978563</v>
+        <v>0.001880132904978562</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002389385852468345</v>
+        <v>0.002389385852468343</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003008731419494694</v>
+        <v>0.003008731419494693</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00189806015208823</v>
+        <v>0.001898060152088228</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002734643222599248</v>
+        <v>0.00273464322259925</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001993302231588193</v>
+        <v>0.001993302231588194</v>
       </c>
       <c r="L4" t="n">
         <v>0.004152829528089988</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009996717850249614</v>
+        <v>0.009996717850249616</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007135006579112114</v>
+        <v>0.007135006579112135</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0154860453468641</v>
+        <v>0.01548604534686413</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007135007320231822</v>
+        <v>0.007135007320231832</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007135007320231825</v>
+        <v>0.007135007320231832</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01570049162963868</v>
+        <v>0.0157004916296387</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02898790138224987</v>
+        <v>0.02898790138224994</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007134872239170729</v>
+        <v>0.007134872239170748</v>
       </c>
       <c r="J5" t="n">
         <v>0.02255213764279939</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008541032622985693</v>
+        <v>0.008541032622985665</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02032421571234698</v>
+        <v>0.02032421571234693</v>
       </c>
     </row>
     <row r="6">
@@ -5433,31 +5433,31 @@
         <v>0.002081640358537878</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002605534360295174</v>
+        <v>0.002605534360295173</v>
       </c>
       <c r="E6" t="n">
         <v>0.002058534653028529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002096278719861993</v>
+        <v>0.002096278719861992</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002589012821598501</v>
+        <v>0.0025890128215985</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003591917500015639</v>
+        <v>0.003591917500015641</v>
       </c>
       <c r="I6" t="n">
         <v>0.00245998202236053</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002959045367258232</v>
+        <v>0.002959045367258234</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002186474259982824</v>
+        <v>0.002186474259982823</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004366088494722328</v>
+        <v>0.004366088494722324</v>
       </c>
     </row>
     <row r="7">
@@ -5470,34 +5470,34 @@
         <v>0.00238445634413739</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00222048958763894</v>
+        <v>0.002220489587638938</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002721205657830794</v>
+        <v>0.002721205657830795</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002219961466014588</v>
+        <v>0.002219961466014589</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002219961466014588</v>
+        <v>0.002219961466014589</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002711680948077668</v>
+        <v>0.00271168094807767</v>
       </c>
       <c r="H7" t="n">
         <v>0.003331026515104014</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002220355247697554</v>
+        <v>0.002220355247697555</v>
       </c>
       <c r="J7" t="n">
         <v>0.003056938318208575</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002315597327197518</v>
+        <v>0.002315597327197517</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004475124623699324</v>
+        <v>0.004475124623699323</v>
       </c>
     </row>
     <row r="8">
@@ -5507,28 +5507,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002746427712531559</v>
+        <v>0.00274642771253156</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003118328823215636</v>
+        <v>0.003118328823215633</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003730633202344182</v>
+        <v>0.003730633202344181</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002971707239429013</v>
+        <v>0.002971707239429012</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00259915842691858</v>
+        <v>0.002599158426918579</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003609891836177863</v>
+        <v>0.003609891836177862</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004229237403204278</v>
+        <v>0.004229237403204277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003118566135797746</v>
+        <v>0.003118566135797745</v>
       </c>
       <c r="J8" t="n">
         <v>0.003955254591900787</v>
@@ -5537,7 +5537,7 @@
         <v>0.002667607771290845</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005933482528950894</v>
+        <v>0.005933482528950892</v>
       </c>
     </row>
     <row r="9">
@@ -5550,34 +5550,34 @@
         <v>0.003205038842044665</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003401303314726787</v>
+        <v>0.003401303314726784</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003902043449049763</v>
+        <v>0.00390204344904977</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003817002924206219</v>
+        <v>0.00381700292420622</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003401303670691415</v>
+        <v>0.003401303670691417</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003892494675165512</v>
+        <v>0.003892494675165514</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004511840242191861</v>
+        <v>0.004511840242191863</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003401168974785397</v>
+        <v>0.0034011689747854</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004237752045296417</v>
+        <v>0.00423775204529642</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003287691734902851</v>
+        <v>0.003287691734902854</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005655938350787162</v>
+        <v>0.005655938350787168</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003335209908663354</v>
+        <v>0.003335209908663355</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004272957016763623</v>
+        <v>0.004272957016763622</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003359158704933386</v>
+        <v>0.00335915870493339</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004624067043716461</v>
+        <v>0.004624067043716462</v>
       </c>
       <c r="F2" t="n">
         <v>0.003116030372881144</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00336224215877798</v>
+        <v>0.003362242158777984</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003392387708235429</v>
+        <v>0.00339238770823543</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003336614380038764</v>
+        <v>0.003336614380038767</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006445925274768106</v>
+        <v>0.006445925274768105</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005248422291683211</v>
+        <v>0.005248422291683215</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00350532685571887</v>
+        <v>0.003505326855718871</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003123091350426304</v>
+        <v>0.003123091350426305</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004679640531962364</v>
+        <v>0.004679640531962365</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003292996013658938</v>
+        <v>0.00329299601365894</v>
       </c>
       <c r="E3" t="n">
         <v>0.005258072694988404</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002768777386539662</v>
+        <v>0.002768777386539661</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003315679045547013</v>
+        <v>0.003315679045547014</v>
       </c>
       <c r="H3" t="n">
         <v>0.003537314051985126</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003132754942104943</v>
+        <v>0.003132754942104939</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008528961482176816</v>
+        <v>0.008528961482176812</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006247364891063905</v>
+        <v>0.006247364891063912</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004335878936084034</v>
+        <v>0.004335878936084035</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001993301993741554</v>
+        <v>0.00199330199374156</v>
       </c>
       <c r="C4" t="n">
         <v>0.001984242763879739</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002263814664602154</v>
+        <v>0.00226381466460216</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001992674189227643</v>
+        <v>0.001992674189227642</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001992674189227643</v>
+        <v>0.001992674189227642</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002298134237983046</v>
+        <v>0.002298134237983047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002646404045410588</v>
+        <v>0.002646404045410593</v>
       </c>
       <c r="I4" t="n">
         <v>0.002005858675665301</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002548205982354365</v>
+        <v>0.002548205982354369</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001924639635194843</v>
+        <v>0.001924639635194849</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003896295316815165</v>
+        <v>0.003896295316815169</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008665197877603361</v>
+        <v>0.008665197877603371</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008755903116976093</v>
+        <v>0.008755903116976094</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01292154344207317</v>
+        <v>0.01292154344207316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00875590375098589</v>
+        <v>0.008755903750985896</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00875590375098589</v>
+        <v>0.008755903750985896</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01388750165682291</v>
+        <v>0.01388750165682296</v>
       </c>
       <c r="H5" t="n">
         <v>0.02135723919066312</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008755814459430368</v>
+        <v>0.008755814459430366</v>
       </c>
       <c r="J5" t="n">
         <v>0.0192777203263105</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007200250920389675</v>
+        <v>0.0072002509203897</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01460427201776809</v>
+        <v>0.01460427201776816</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002196053370845709</v>
+        <v>0.0021960533708457</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002198853961251509</v>
+        <v>0.002198853961251508</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002469213825909084</v>
+        <v>0.002469213825909087</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002175388258757461</v>
+        <v>0.002175388258757462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002208893015068432</v>
+        <v>0.002208893015068433</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002855408185770881</v>
+        <v>0.002855408185770897</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003223907178313947</v>
+        <v>0.003223907178313952</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002208610052769459</v>
+        <v>0.002208610052769452</v>
       </c>
       <c r="J6" t="n">
         <v>0.003111122381315834</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002121786220654723</v>
+        <v>0.002121786220654725</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004111028945772199</v>
+        <v>0.004111028945772202</v>
       </c>
     </row>
     <row r="7">
@@ -5869,31 +5869,31 @@
         <v>0.002320338765694014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002578182092037754</v>
+        <v>0.002578182092037764</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002319787180630419</v>
+        <v>0.00231978718063042</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002319787180630419</v>
+        <v>0.00231978718063042</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002612525670466034</v>
+        <v>0.002612525670466046</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002960795477893578</v>
+        <v>0.00296079547789358</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002320250108148296</v>
+        <v>0.002320250108148297</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002862597414837355</v>
+        <v>0.002862597414837357</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002239031067677834</v>
+        <v>0.002239031067677837</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004210686749298155</v>
+        <v>0.004210686749298156</v>
       </c>
     </row>
     <row r="8">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002660887507674848</v>
+        <v>0.002660887507674846</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003196969592094537</v>
+        <v>0.00319696959209454</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00356385318948084</v>
+        <v>0.003563853189480843</v>
       </c>
       <c r="E8" t="n">
         <v>0.003053743414318697</v>
@@ -5921,19 +5921,19 @@
         <v>0.003489552607803066</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003837822415230706</v>
+        <v>0.003837822415230713</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003197277045485318</v>
+        <v>0.003197277045485319</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003739727299504541</v>
+        <v>0.003739727299504544</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002582494684977083</v>
+        <v>0.002582494684977088</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005634900906001892</v>
+        <v>0.005634900906001896</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003027938293259208</v>
+        <v>0.003027938293259218</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003370093316831068</v>
+        <v>0.003370093316831071</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003627960836140883</v>
+        <v>0.003627960836140885</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003750340948575992</v>
+        <v>0.003750340948575996</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003370093662153135</v>
+        <v>0.003370093662153136</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003662280221603092</v>
+        <v>0.003662280221603103</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00401055002903064</v>
+        <v>0.004010550029030647</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00337000465928535</v>
+        <v>0.003370004659285353</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003912351965974415</v>
+        <v>0.00391235196597442</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003097866492799448</v>
+        <v>0.00309786649279946</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005260441300435221</v>
+        <v>0.005260441300435226</v>
       </c>
     </row>
   </sheetData>
@@ -6059,34 +6059,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003239510652143649</v>
+        <v>0.00323951065214365</v>
       </c>
       <c r="C2" t="n">
         <v>0.004224620458043379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003250949656122824</v>
+        <v>0.003250949656122826</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004595830359943886</v>
+        <v>0.004595830359943885</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003021982461620716</v>
+        <v>0.003021982461620715</v>
       </c>
       <c r="G2" t="n">
         <v>0.003256977961706349</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003278274033958728</v>
+        <v>0.003278274033958729</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003239592245076572</v>
+        <v>0.003239592245076571</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006486795913023101</v>
+        <v>0.006486795913023106</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005166685757737893</v>
+        <v>0.005166685757737896</v>
       </c>
       <c r="L2" t="n">
         <v>0.003310759199438467</v>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002887054436222145</v>
+        <v>0.002887054436222143</v>
       </c>
       <c r="C3" t="n">
         <v>0.004514576963169404</v>
@@ -6108,28 +6108,28 @@
         <v>0.002967946585494174</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005126504910101521</v>
+        <v>0.00512650491010152</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002528576727242319</v>
+        <v>0.002528576727242317</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003011181399581864</v>
+        <v>0.003011181399581862</v>
       </c>
       <c r="H3" t="n">
         <v>0.003166880586019018</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002887645038054022</v>
+        <v>0.002887645038054021</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008699333189921572</v>
+        <v>0.008699333189921579</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006128758618375875</v>
+        <v>0.006128758618375878</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003394945461222259</v>
+        <v>0.00339494546122226</v>
       </c>
     </row>
     <row r="4">
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00166397586957823</v>
+        <v>0.001663975869578229</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001629211095296828</v>
+        <v>0.001629211095296829</v>
       </c>
       <c r="D4" t="n">
         <v>0.001793184681724846</v>
@@ -6163,7 +6163,7 @@
         <v>0.001661782111294548</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002593489477361184</v>
+        <v>0.002593489477361186</v>
       </c>
       <c r="K4" t="n">
         <v>0.001789811199109796</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004295837622093297</v>
+        <v>0.004295837622093263</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004314813940995253</v>
+        <v>0.004314813940995254</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006322574163507347</v>
+        <v>0.006322574163507337</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004314814867593453</v>
+        <v>0.004314814867593452</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004314814867593455</v>
+        <v>0.004314814867593452</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007726647275385779</v>
+        <v>0.007726647275385802</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01258386280368029</v>
+        <v>0.01258386280368028</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004314747147749734</v>
+        <v>0.004314747147749738</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02218347858057397</v>
+        <v>0.02218347858057399</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006357467985615129</v>
+        <v>0.006357467985615116</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02076902782551179</v>
+        <v>0.02076902782551177</v>
       </c>
     </row>
     <row r="6">
@@ -6219,31 +6219,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002174868372788846</v>
+        <v>0.002174868372788844</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001831526076009143</v>
+        <v>0.001831526076009146</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002313578296087442</v>
+        <v>0.002313578296087443</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001808893655449036</v>
+        <v>0.001808893655449037</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001841325418100405</v>
+        <v>0.001841325418100406</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002371688416175753</v>
+        <v>0.002371688416175752</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002290917808037431</v>
+        <v>0.002290917808037432</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002172674614505163</v>
+        <v>0.002172674614505162</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003113464270949985</v>
+        <v>0.003113464270949988</v>
       </c>
       <c r="K6" t="n">
         <v>0.001968076364180771</v>
@@ -6259,16 +6259,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001969393134092574</v>
+        <v>0.001969393134092575</v>
       </c>
       <c r="C7" t="n">
         <v>0.001967266169054413</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002098577029523978</v>
+        <v>0.002098577029523979</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00196674482719196</v>
+        <v>0.001966744827191961</v>
       </c>
       <c r="F7" t="n">
         <v>0.001966744827191961</v>
@@ -6277,16 +6277,16 @@
         <v>0.002166213177479482</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002413434783535371</v>
+        <v>0.002413434783535372</v>
       </c>
       <c r="I7" t="n">
         <v>0.001967199375808894</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002898906741875529</v>
+        <v>0.002898906741875532</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002095228463624141</v>
+        <v>0.002095228463624143</v>
       </c>
       <c r="L7" t="n">
         <v>0.002768538434943037</v>
@@ -6302,34 +6302,34 @@
         <v>0.002323279489382621</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002840957150394553</v>
+        <v>0.002840957150394555</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003080520968270991</v>
+        <v>0.003080520968270993</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002698729243295497</v>
+        <v>0.002698729243295495</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002337345396086913</v>
+        <v>0.002337345396086914</v>
       </c>
       <c r="G8" t="n">
         <v>0.003040271213065289</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003287492819121195</v>
+        <v>0.003287492819121197</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002841257411394701</v>
+        <v>0.0028412574113947</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003773067005219778</v>
+        <v>0.003773067005219783</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002439452362983451</v>
+        <v>0.00243945236298345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004185959285804642</v>
+        <v>0.004185959285804647</v>
       </c>
     </row>
     <row r="9">
@@ -6345,10 +6345,10 @@
         <v>0.003128970508011826</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003260306446639165</v>
+        <v>0.003260306446639164</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003535592399388986</v>
+        <v>0.003535592399388983</v>
       </c>
       <c r="F9" t="n">
         <v>0.003128971242917596</v>
@@ -6357,19 +6357,19 @@
         <v>0.003327917516436896</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003575139122492785</v>
+        <v>0.003575139122492783</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00312890371476631</v>
+        <v>0.003128903714766309</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004060611080832948</v>
+        <v>0.004060611080832946</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003052771547163382</v>
+        <v>0.003052771547163381</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003930242773900448</v>
+        <v>0.003930242773900446</v>
       </c>
     </row>
   </sheetData>
@@ -6455,13 +6455,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003215643166054652</v>
+        <v>0.003215643166054651</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004204832243140856</v>
+        <v>0.004204832243140854</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003220363522803527</v>
+        <v>0.003220363522803526</v>
       </c>
       <c r="E2" t="n">
         <v>0.004575096058140739</v>
@@ -6470,22 +6470,22 @@
         <v>0.003004845352592803</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003226978404483939</v>
+        <v>0.003226978404483938</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003213621122412073</v>
+        <v>0.003213621122412072</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003223005504339001</v>
+        <v>0.003223005504339</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006421756938305441</v>
+        <v>0.006421756938305444</v>
       </c>
       <c r="K2" t="n">
         <v>0.005141716654790789</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003208924434615767</v>
+        <v>0.003208924434615765</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002847710809293304</v>
+        <v>0.002847710809293303</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004521312051545852</v>
+        <v>0.00452131205154585</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002880954703516275</v>
+        <v>0.002880954703516272</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00513184672751392</v>
+        <v>0.005131846727513922</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00253985624352216</v>
+        <v>0.002539856243522159</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002928081511774461</v>
+        <v>0.002928081511774462</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002838979604706328</v>
+        <v>0.002838979604706327</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00289983213148247</v>
+        <v>0.002899832131482468</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008428400071860676</v>
+        <v>0.008428400071860673</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006099572380608515</v>
+        <v>0.006099572380608516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002803221122173233</v>
+        <v>0.002803221122173234</v>
       </c>
     </row>
     <row r="4">
@@ -6544,25 +6544,25 @@
         <v>0.001658617299312176</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001672829017706385</v>
+        <v>0.001672829017706384</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001672829017706386</v>
+        <v>0.001672829017706384</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001732991227983438</v>
+        <v>0.001732991227983436</v>
       </c>
       <c r="H4" t="n">
         <v>0.001592400462959637</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001686260535163116</v>
+        <v>0.001686260535163115</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002201147515084295</v>
+        <v>0.002201147515084296</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001756198256489102</v>
+        <v>0.001756198256489103</v>
       </c>
       <c r="L4" t="n">
         <v>0.001534947548318659</v>
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0035297398054345</v>
+        <v>0.003529739805434503</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004778657304738778</v>
+        <v>0.004778657304738775</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004241884049549726</v>
+        <v>0.004241884049549724</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004778657996629293</v>
+        <v>0.004778657996629287</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004778657996629293</v>
+        <v>0.004778657996629287</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005519557633638426</v>
+        <v>0.005519557633638396</v>
       </c>
       <c r="H5" t="n">
         <v>0.003456411551883649</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004778625299529739</v>
+        <v>0.004778625299529738</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0135496857445836</v>
+        <v>0.01354968574458359</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005799922470691443</v>
+        <v>0.005799922470691447</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003796846683325568</v>
+        <v>0.003796846683325571</v>
       </c>
     </row>
     <row r="6">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002076904827208111</v>
+        <v>0.002076904827208112</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001856838002243022</v>
+        <v>0.001856838002243016</v>
       </c>
       <c r="D6" t="n">
         <v>0.001834100208864326</v>
@@ -6627,19 +6627,19 @@
         <v>0.001834997017836608</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001862159721775488</v>
+        <v>0.001862159721775487</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002204597356829297</v>
+        <v>0.002204597356829299</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002080688688280497</v>
+        <v>0.002080688688280498</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002157866664008982</v>
+        <v>0.002157866664008981</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002398516261499357</v>
+        <v>0.002398516261499358</v>
       </c>
       <c r="K6" t="n">
         <v>0.001934283883871002</v>
@@ -6664,13 +6664,13 @@
         <v>0.001926606910307658</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001953904437868826</v>
+        <v>0.001953904437868825</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001953904437868826</v>
+        <v>0.001953904437868825</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002001004236342898</v>
+        <v>0.002001004236342895</v>
       </c>
       <c r="H7" t="n">
         <v>0.001860413471319096</v>
@@ -6682,7 +6682,7 @@
         <v>0.002469160523443756</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002024211264848562</v>
+        <v>0.002024211264848563</v>
       </c>
       <c r="L7" t="n">
         <v>0.001802960556678118</v>
@@ -6701,31 +6701,31 @@
         <v>0.002727415538843544</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002795368374271506</v>
+        <v>0.002795368374271507</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002601662108426562</v>
+        <v>0.002601662108426561</v>
       </c>
       <c r="F8" t="n">
         <v>0.002282138611308844</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002774379955976618</v>
+        <v>0.002774379955976617</v>
       </c>
       <c r="H8" t="n">
         <v>0.002633789190952758</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002727649263156298</v>
+        <v>0.002727649263156297</v>
       </c>
       <c r="J8" t="n">
         <v>0.003242626624927091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002329148595412141</v>
+        <v>0.002329148595412142</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00305673567765328</v>
+        <v>0.003056735677653281</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002525066865324685</v>
+        <v>0.002525066865324682</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002899783366465592</v>
+        <v>0.002899783366465589</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002872108336016506</v>
+        <v>0.002872108336016504</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003238733913965832</v>
+        <v>0.003238733913965829</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002899784013965038</v>
+        <v>0.002899784013965036</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002946482054076872</v>
+        <v>0.002946482054076869</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002805891289053075</v>
+        <v>0.002805891289053071</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002899751361256552</v>
+        <v>0.002899751361256549</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003414638341177736</v>
+        <v>0.003414638341177733</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002799505108926259</v>
+        <v>0.002799505108926257</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002748438374412096</v>
+        <v>0.002748438374412094</v>
       </c>
     </row>
   </sheetData>
@@ -6854,31 +6854,31 @@
         <v>0.003214710680266873</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004145411597873765</v>
+        <v>0.004145411597873766</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003209807518519086</v>
+        <v>0.003209807518519088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004490760380663935</v>
+        <v>0.004490760380663937</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002998219266907862</v>
+        <v>0.00299821926690786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003217673185359122</v>
+        <v>0.003217673185359123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003207312905098313</v>
+        <v>0.003207312905098312</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003219494091119707</v>
+        <v>0.003219494091119706</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006279170278597155</v>
+        <v>0.006279170278597153</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005128546506273251</v>
+        <v>0.00512854650627325</v>
       </c>
       <c r="L2" t="n">
         <v>0.003206831528932706</v>
@@ -6894,34 +6894,34 @@
         <v>0.002882193064797535</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004445215636119886</v>
+        <v>0.004445215636119887</v>
       </c>
       <c r="D3" t="n">
         <v>0.002847311018586508</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005014691866308063</v>
+        <v>0.005014691866308064</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002550975143642922</v>
+        <v>0.002550975143642923</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002903284323694667</v>
+        <v>0.002903284323694666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002835074653206049</v>
+        <v>0.00283507465320605</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002916091881825302</v>
+        <v>0.002916091881825304</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008135145414388376</v>
+        <v>0.008135145414388379</v>
       </c>
       <c r="K3" t="n">
         <v>0.006062415319233375</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002829023796733392</v>
+        <v>0.002829023796733391</v>
       </c>
     </row>
     <row r="4">
@@ -6934,10 +6934,10 @@
         <v>0.001665978221700064</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00170036740566568</v>
+        <v>0.001700367405665681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00161059475419298</v>
+        <v>0.001610594754192979</v>
       </c>
       <c r="E4" t="n">
         <v>0.001708142905622427</v>
@@ -6946,19 +6946,19 @@
         <v>0.001708142905622427</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001699118673792907</v>
+        <v>0.001699118673792908</v>
       </c>
       <c r="H4" t="n">
         <v>0.001591733950020264</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00171795938489587</v>
+        <v>0.001717959384895871</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002066839691214417</v>
+        <v>0.002066839691214416</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00171041193725447</v>
+        <v>0.001710411937254469</v>
       </c>
       <c r="L4" t="n">
         <v>0.001581215682469504</v>
@@ -6974,34 +6974,34 @@
         <v>0.004516166389581052</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005345060379768549</v>
+        <v>0.005345060379768552</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003594692507619692</v>
+        <v>0.003594692507619684</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005345060966302622</v>
+        <v>0.005345060966302623</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005345060966302622</v>
+        <v>0.005345060966302623</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00508059310102479</v>
+        <v>0.00508059310102481</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003523174810743975</v>
+        <v>0.003523174810743974</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005345043392344141</v>
+        <v>0.005345043392344147</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01150066245081313</v>
+        <v>0.01150066245081316</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005044888929111152</v>
+        <v>0.005044888929111159</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004336205006692496</v>
+        <v>0.004336205006692495</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001846088879961301</v>
+        <v>0.0018460888799613</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00189378620983301</v>
+        <v>0.001893786209833011</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001786224950562277</v>
+        <v>0.001786224950562276</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001871650602062757</v>
+        <v>0.00187165060206276</v>
       </c>
       <c r="F6" t="n">
         <v>0.001897469943451652</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001879229332054146</v>
+        <v>0.001879229332054144</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002081403758817222</v>
+        <v>0.002081403758817221</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001898070043157107</v>
+        <v>0.001898070043157108</v>
       </c>
       <c r="J6" t="n">
         <v>0.002267055108216658</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00189171595064552</v>
+        <v>0.001891715950645518</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001760539617977193</v>
+        <v>0.001760539617977192</v>
       </c>
     </row>
     <row r="7">
@@ -7051,22 +7051,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001929670827897963</v>
+        <v>0.001929670827897961</v>
       </c>
       <c r="C7" t="n">
         <v>0.001981668978518182</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001874263862239574</v>
+        <v>0.001874263862239573</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00198129412063662</v>
+        <v>0.001981294120636619</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00198129412063662</v>
+        <v>0.001981294120636619</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001962811279990809</v>
+        <v>0.001962811279990808</v>
       </c>
       <c r="H7" t="n">
         <v>0.001855426556218163</v>
@@ -7078,10 +7078,10 @@
         <v>0.002330532297412316</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001974104543452368</v>
+        <v>0.001974104543452369</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001844908288667403</v>
+        <v>0.001844908288667402</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002238706934723842</v>
+        <v>0.002238706934723843</v>
       </c>
       <c r="C8" t="n">
         <v>0.002743835148368797</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002730704573151584</v>
+        <v>0.002730704573151582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002619863112837659</v>
+        <v>0.00261986311283766</v>
       </c>
       <c r="F8" t="n">
         <v>0.002304866897727432</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002725218946476201</v>
+        <v>0.002725218946476202</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002617834222703471</v>
+        <v>0.002617834222703469</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002744059657579166</v>
+        <v>0.00274405965757916</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003093029063592709</v>
+        <v>0.003093029063592711</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002274719040876708</v>
+        <v>0.002274719040876707</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003080900458758792</v>
+        <v>0.003080900458758791</v>
       </c>
     </row>
     <row r="9">
@@ -7134,19 +7134,19 @@
         <v>0.002509563677681524</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002833800034965051</v>
+        <v>0.002833800034965052</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00272641860152668</v>
+        <v>0.002726418601526681</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003147957854784479</v>
+        <v>0.00314795785478448</v>
       </c>
       <c r="F9" t="n">
         <v>0.002833800580077867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002814942336437677</v>
+        <v>0.002814942336437679</v>
       </c>
       <c r="H9" t="n">
         <v>0.002707557612665033</v>
@@ -7155,13 +7155,13 @@
         <v>0.00283378304754064</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003182663353859185</v>
+        <v>0.003182663353859187</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002662100242985069</v>
+        <v>0.00266210024298507</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002697039345114274</v>
+        <v>0.002697039345114275</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003333764615640639</v>
+        <v>0.003333764615640636</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004305636536421015</v>
+        <v>0.004305636536421013</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00336994078055834</v>
+        <v>0.003369940780558339</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004679293738153963</v>
+        <v>0.004679293738153959</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003099094920471436</v>
+        <v>0.003099094920471433</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003364115777519693</v>
+        <v>0.00336411577751969</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003444868960484029</v>
+        <v>0.003444868960484028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003320153419634593</v>
+        <v>0.00332015341963459</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006567523343194638</v>
+        <v>0.006567523343194635</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005253593245341213</v>
+        <v>0.005253593245341214</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0035127079105199</v>
+        <v>0.003512707910519896</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003113167376202742</v>
+        <v>0.00311316737620274</v>
       </c>
       <c r="C3" t="n">
         <v>0.004644534031788726</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003369896767311412</v>
+        <v>0.003369896767311413</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005260071314640132</v>
+        <v>0.005260071314640134</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002651659497713975</v>
+        <v>0.002651659497713977</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003329432401450826</v>
+        <v>0.003329432401450827</v>
       </c>
       <c r="H3" t="n">
         <v>0.003906776234635582</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003016421429894609</v>
+        <v>0.003016421429894605</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008784087089888761</v>
+        <v>0.008784087089888754</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006277610019182539</v>
+        <v>0.006277610019182534</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00438928354848065</v>
+        <v>0.004389283548480653</v>
       </c>
     </row>
     <row r="4">
@@ -7327,10 +7327,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001982135937500986</v>
+        <v>0.001982135937500984</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00178810953455541</v>
+        <v>0.001788109534555411</v>
       </c>
       <c r="D4" t="n">
         <v>0.002390762362104511</v>
@@ -7342,10 +7342,10 @@
         <v>0.001797874329016416</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002324295453462977</v>
+        <v>0.002324295453462981</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003238042539382402</v>
+        <v>0.003238042539382405</v>
       </c>
       <c r="I4" t="n">
         <v>0.001823998723044318</v>
@@ -7357,7 +7357,7 @@
         <v>0.001972411546727126</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003984061078879816</v>
+        <v>0.003984061078879814</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009008781181152614</v>
+        <v>0.009008781181152605</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006318792913879012</v>
+        <v>0.006318792913878987</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0159221220928038</v>
+        <v>0.01592212209280383</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006318793862146942</v>
+        <v>0.006318793862146921</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006318793862146942</v>
+        <v>0.006318793862146919</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01529414194409578</v>
+        <v>0.01529414194409581</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03283614201364849</v>
+        <v>0.0328361420136485</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00631865677304483</v>
+        <v>0.006318656773044812</v>
       </c>
       <c r="J5" t="n">
         <v>0.02266249183747317</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008901274452282653</v>
+        <v>0.008901274452282656</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01491678953838664</v>
+        <v>0.01491678953838673</v>
       </c>
     </row>
     <row r="6">
@@ -7410,34 +7410,34 @@
         <v>0.002179532889210556</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002002949085431504</v>
+        <v>0.0020029490854315</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002597527100312774</v>
+        <v>0.002597527100312778</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001979641509422266</v>
+        <v>0.001979641509422268</v>
       </c>
       <c r="F6" t="n">
         <v>0.002019427668433774</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002899515085608041</v>
+        <v>0.002899515085608043</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003843135344646683</v>
+        <v>0.003843135344646686</v>
       </c>
       <c r="I6" t="n">
         <v>0.002399218355189378</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003250382325925786</v>
+        <v>0.003250382325925784</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002161375431811003</v>
+        <v>0.002161375431811012</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004195036754236521</v>
+        <v>0.004195036754236522</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002321772345122811</v>
+        <v>0.002321772345122813</v>
       </c>
       <c r="C7" t="n">
         <v>0.002163771271500339</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002730373416501154</v>
+        <v>0.002730373416501157</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002163259189186971</v>
+        <v>0.002163259189186972</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002163259189186971</v>
+        <v>0.002163259189186972</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002663931861084808</v>
+        <v>0.00266393186108481</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003577678947004226</v>
+        <v>0.00357767894700423</v>
       </c>
       <c r="I7" t="n">
         <v>0.002163635130666148</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003004631039965789</v>
+        <v>0.003004631039965792</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002312047954348954</v>
+        <v>0.002312047954348956</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004323697486501624</v>
+        <v>0.004323697486501629</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002705697830994263</v>
+        <v>0.002705697830994265</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00311529261397275</v>
+        <v>0.003115292613972748</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00380003536546637</v>
+        <v>0.003800035365466369</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002959997325273075</v>
+        <v>0.002959997325273077</v>
       </c>
       <c r="F8" t="n">
         <v>0.002565409736627639</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003615801530601492</v>
+        <v>0.003615801530601494</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004529548616520951</v>
+        <v>0.004529548616520956</v>
       </c>
       <c r="I8" t="n">
         <v>0.003115504800182833</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003956612325889724</v>
+        <v>0.003956612325889727</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00268542358551524</v>
+        <v>0.002685423585515243</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00586883234569832</v>
+        <v>0.005868832345698322</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003280530795224134</v>
+        <v>0.003280530795224136</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003528702325679451</v>
+        <v>0.003528702325679456</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004095329920521958</v>
+        <v>0.004095329920521963</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0039974173440719</v>
+        <v>0.003997417344071905</v>
       </c>
       <c r="F9" t="n">
         <v>0.003528702801891243</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004028862915263926</v>
+        <v>0.00402886291526393</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004942610001183351</v>
+        <v>0.004942610001183352</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003528566184845262</v>
+        <v>0.003528566184845263</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004369562094144902</v>
+        <v>0.004369562094144907</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00344164104719902</v>
+        <v>0.003441641047199021</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005688628540680755</v>
+        <v>0.005688628540680758</v>
       </c>
     </row>
   </sheetData>
@@ -7646,10 +7646,10 @@
         <v>0.003254608689755522</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004249300094794617</v>
+        <v>0.004249300094794618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003313787470446778</v>
+        <v>0.00331378747044678</v>
       </c>
       <c r="E2" t="n">
         <v>0.004622436617758555</v>
@@ -7658,22 +7658,22 @@
         <v>0.003044477335541314</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003291598240156113</v>
+        <v>0.003291598240156114</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003267825792714177</v>
+        <v>0.003267825792714176</v>
       </c>
       <c r="I2" t="n">
         <v>0.003266560593487213</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006491748482747523</v>
+        <v>0.006491748482747527</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005175453599208445</v>
+        <v>0.005175453599208447</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003531616834838164</v>
+        <v>0.003531616834838165</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002856992721139215</v>
+        <v>0.002856992721139216</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004565067450681304</v>
+        <v>0.004565067450681306</v>
       </c>
       <c r="D3" t="n">
         <v>0.003276285621341519</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005180053711979069</v>
+        <v>0.005180053711979067</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0025753386451422</v>
+        <v>0.002575338645142202</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003119767113576118</v>
+        <v>0.003119767113576119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002958342234828694</v>
+        <v>0.002958342234828697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002941790837901491</v>
+        <v>0.002941790837901493</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0085888941684876</v>
+        <v>0.008588894168487607</v>
       </c>
       <c r="K3" t="n">
         <v>0.006091614994039317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004823223345308512</v>
+        <v>0.004823223345308513</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00158966879877007</v>
+        <v>0.001589668798770071</v>
       </c>
       <c r="C4" t="n">
         <v>0.001697346435791132</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002258120350261934</v>
+        <v>0.002258120350261933</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001705672474938691</v>
+        <v>0.001705672474938692</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001705672474938691</v>
+        <v>0.001705672474938692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002006993624745017</v>
+        <v>0.002006993624745016</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001751672372334782</v>
+        <v>0.001751672372334784</v>
       </c>
       <c r="I4" t="n">
         <v>0.001721494015698828</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002388731941127122</v>
+        <v>0.002388731941127124</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001722465707114861</v>
+        <v>0.001722465707114863</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004683600440482077</v>
+        <v>0.004683600440482074</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002862746223428651</v>
+        <v>0.002862746223428648</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004986614649047353</v>
+        <v>0.004986614649047357</v>
       </c>
       <c r="D5" t="n">
         <v>0.01309497938122142</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004986615361698404</v>
+        <v>0.004986615361698405</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004986615361698404</v>
+        <v>0.004986615361698405</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009618782259095592</v>
+        <v>0.009618782259095564</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005786410141118958</v>
+        <v>0.005786410141118959</v>
       </c>
       <c r="I5" t="n">
         <v>0.004986527821359553</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01714742855563598</v>
+        <v>0.01714742855563599</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004908182280815284</v>
+        <v>0.004908182280815286</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06184767397722278</v>
+        <v>0.06184767397722265</v>
       </c>
     </row>
     <row r="6">
@@ -7803,13 +7803,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002107830261148198</v>
+        <v>0.0021078302611482</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001894273498523833</v>
+        <v>0.001894273498523829</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002454409052363983</v>
+        <v>0.002454409052363982</v>
       </c>
       <c r="E6" t="n">
         <v>0.001872029314962922</v>
@@ -7818,7 +7818,7 @@
         <v>0.001904350846885517</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002525155087123148</v>
+        <v>0.002525155087123144</v>
       </c>
       <c r="H6" t="n">
         <v>0.002287839639104569</v>
@@ -7827,13 +7827,13 @@
         <v>0.002239655478076956</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002595127359961902</v>
+        <v>0.002595127359961903</v>
       </c>
       <c r="K6" t="n">
         <v>0.00190122858922489</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004884967253075812</v>
+        <v>0.00488496725307581</v>
       </c>
     </row>
     <row r="7">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00187892780585298</v>
+        <v>0.001878927805852979</v>
       </c>
       <c r="C7" t="n">
         <v>0.002010839850469531</v>
@@ -7852,28 +7852,28 @@
         <v>0.002547355806748642</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002010389995268589</v>
+        <v>0.00201038999526859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002010389995268589</v>
+        <v>0.00201038999526859</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002296252631827927</v>
+        <v>0.002296252631827925</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002040931379417693</v>
+        <v>0.002040931379417694</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002010753022781736</v>
+        <v>0.002010753022781738</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002677990948210032</v>
+        <v>0.002677990948210033</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002011724714197771</v>
+        <v>0.00201172471419777</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004972859447564983</v>
+        <v>0.004972859447564981</v>
       </c>
     </row>
     <row r="8">
@@ -7883,34 +7883,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00221442102026912</v>
+        <v>0.002214421020269122</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002837939110830002</v>
+        <v>0.002837939110830006</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003476785649108142</v>
+        <v>0.003476785649108146</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002703433758207015</v>
+        <v>0.002703433758207018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002361671890245763</v>
+        <v>0.002361671890245766</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003123657779735663</v>
+        <v>0.003123657779735666</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002868336527325403</v>
+        <v>0.002868336527325408</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002838158170689472</v>
+        <v>0.002838158170689476</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003505492770084178</v>
+        <v>0.003505492770084181</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002338080411983372</v>
+        <v>0.002338080411983373</v>
       </c>
       <c r="L8" t="n">
         <v>0.006314107742225449</v>
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002601688879224656</v>
+        <v>0.002601688879224657</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003054807978317224</v>
+        <v>0.003054807978317223</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003591347741992147</v>
+        <v>0.003591347741992148</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003425474887665324</v>
+        <v>0.003425474887665323</v>
       </c>
       <c r="F9" t="n">
         <v>0.003054808558472293</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003340220759675623</v>
+        <v>0.003340220759675622</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003084899507265386</v>
+        <v>0.003084899507265385</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003054721150629429</v>
+        <v>0.00305472115062943</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003721959076057724</v>
+        <v>0.003721959076057723</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002869584321213532</v>
+        <v>0.002869584321213529</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00601682757541268</v>
+        <v>0.006016827575412677</v>
       </c>
     </row>
   </sheetData>
